--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -3392,7 +3392,7 @@
     <t>ProFX6v3</t>
   </si>
   <si>
-    <t>6-channel USB mixer, USB-B; 2-band EQ on channels 1-2 only (80Hz/120Hz); 24 GigFX effects; dual stereo USB return; no sub/control-room outputs</t>
+    <t>6-channel USB mixer, USB-B; 2-band EQ on channels 1-2 only (80Hz/12kHz); 24 GigFX effects; dual stereo USB return; no sub/control-room outputs</t>
   </si>
   <si>
     <t>https://mackie.com/en/products/mixers/profxv3-series/ProFX6v3.html</t>
@@ -6553,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -6630,7 +6630,7 @@
         <v>24</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -6710,7 +6710,7 @@
         <v>32</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>2</v>
@@ -7231,7 +7231,7 @@
         <v>16</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -7809,7 +7809,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>277</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>24</v>
       </c>
       <c r="Y69" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="AA69" t="s">
         <v>48</v>
@@ -11641,6 +11641,9 @@
       <c r="F70">
         <v>2</v>
       </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
       <c r="H70">
         <v>1</v>
       </c>
@@ -11669,7 +11672,7 @@
         <v>24</v>
       </c>
       <c r="Y70" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="AA70" t="s">
         <v>48</v>
@@ -11838,7 +11841,7 @@
         <v>2</v>
       </c>
       <c r="P72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72" t="s">
         <v>48</v>
@@ -11850,7 +11853,7 @@
         <v>24</v>
       </c>
       <c r="Y72" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="AA72" t="s">
         <v>48</v>
@@ -11908,6 +11911,9 @@
       <c r="F73">
         <v>1</v>
       </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
       <c r="H73">
         <v>1</v>
       </c>
@@ -11927,7 +11933,7 @@
         <v>24</v>
       </c>
       <c r="Y73" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
       <c r="AA73" t="s">
         <v>48</v>
@@ -12260,7 +12266,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="77" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>470</v>
       </c>
@@ -12758,7 +12764,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="83" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>507</v>
       </c>
@@ -12882,7 +12888,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="85" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>507</v>
       </c>
@@ -12938,7 +12944,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="86" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>507</v>
       </c>
@@ -15025,7 +15031,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="117" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>657</v>
       </c>
@@ -15090,7 +15096,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="118" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>657</v>
       </c>
@@ -15108,6 +15114,9 @@
       </c>
       <c r="F118">
         <v>4</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -15661,7 +15670,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>683</v>
       </c>
@@ -16001,7 +16010,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="131" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>683</v>
       </c>
@@ -16205,7 +16214,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="134" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>736</v>
       </c>
@@ -17849,6 +17858,9 @@
       <c r="E153">
         <v>1</v>
       </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
       <c r="N153">
         <v>2</v>
       </c>
@@ -18212,7 +18224,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="158" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>877</v>
       </c>
@@ -18747,7 +18759,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="166" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>882</v>
       </c>
@@ -18758,10 +18770,7 @@
         <v>379</v>
       </c>
       <c r="D166">
-        <v>99.99</v>
-      </c>
-      <c r="G166">
-        <v>2</v>
+        <v>119.99</v>
       </c>
       <c r="P166">
         <v>1</v>
@@ -18793,8 +18802,11 @@
       <c r="AP166" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="167" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AQ166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>882</v>
       </c>
@@ -18813,9 +18825,6 @@
       <c r="F167">
         <v>1</v>
       </c>
-      <c r="G167">
-        <v>2</v>
-      </c>
       <c r="H167">
         <v>1</v>
       </c>
@@ -18857,6 +18866,9 @@
       </c>
       <c r="AP167" t="s">
         <v>932</v>
+      </c>
+      <c r="AQ167">
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:45" x14ac:dyDescent="0.25">
@@ -19303,7 +19315,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="174" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>965</v>
       </c>
@@ -19590,7 +19602,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="178" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>965</v>
       </c>
@@ -20777,7 +20789,7 @@
         <v>4</v>
       </c>
       <c r="G193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N193">
         <v>2</v>
@@ -20887,7 +20899,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="195" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1045</v>
       </c>
@@ -21031,7 +21043,7 @@
         <v>8</v>
       </c>
       <c r="G197">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H197">
         <v>2</v>
@@ -21105,7 +21117,7 @@
         <v>12</v>
       </c>
       <c r="G198">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H198" t="s">
         <v>65</v>
@@ -21179,7 +21191,7 @@
         <v>18</v>
       </c>
       <c r="G199">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H199">
         <v>2</v>
@@ -21188,7 +21200,7 @@
         <v>2</v>
       </c>
       <c r="O199" t="s">
-        <v>637</v>
+        <v>123</v>
       </c>
       <c r="P199">
         <v>1</v>
@@ -21256,7 +21268,7 @@
         <v>2</v>
       </c>
       <c r="G200">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H200">
         <v>2</v>
@@ -21324,7 +21336,7 @@
         <v>2</v>
       </c>
       <c r="G201">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H201">
         <v>2</v>
@@ -21401,10 +21413,10 @@
         <v>4</v>
       </c>
       <c r="F202">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G202">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H202">
         <v>2</v>
@@ -21481,7 +21493,7 @@
         <v>2</v>
       </c>
       <c r="G203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H203">
         <v>2</v>
@@ -21558,10 +21570,10 @@
         <v>7</v>
       </c>
       <c r="F204">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G204">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H204">
         <v>2</v>
@@ -21638,7 +21650,7 @@
         <v>2</v>
       </c>
       <c r="G205">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H205">
         <v>2</v>
@@ -21718,7 +21730,7 @@
         <v>2</v>
       </c>
       <c r="G206">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H206">
         <v>2</v>
@@ -21795,7 +21807,7 @@
         <v>2</v>
       </c>
       <c r="G207">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H207">
         <v>2</v>
@@ -21872,7 +21884,7 @@
         <v>2</v>
       </c>
       <c r="G208">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H208">
         <v>2</v>
@@ -21949,7 +21961,7 @@
         <v>2</v>
       </c>
       <c r="G209">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H209">
         <v>2</v>
@@ -22234,7 +22246,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="213" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1138</v>
       </c>
@@ -22489,7 +22501,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="216" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1158</v>
       </c>
@@ -23017,7 +23029,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="222" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1158</v>
       </c>
@@ -23085,7 +23097,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="223" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1158</v>
       </c>
@@ -25456,7 +25468,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="252" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1347</v>
       </c>
@@ -26420,7 +26432,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="263" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1353</v>
       </c>
@@ -27082,7 +27094,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="273" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1469</v>
       </c>
@@ -27141,7 +27153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1469</v>
       </c>
@@ -27158,13 +27170,10 @@
         <v>1</v>
       </c>
       <c r="G274">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N274">
-        <v>1</v>
-      </c>
-      <c r="O274">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P274">
         <v>1</v>
@@ -27203,7 +27212,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="275" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1469</v>
       </c>
@@ -27268,7 +27277,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="276" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1469</v>
       </c>
@@ -27285,7 +27294,7 @@
         <v>235</v>
       </c>
       <c r="G276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N276">
         <v>2</v>
@@ -27327,7 +27336,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="277" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1469</v>
       </c>
@@ -27374,7 +27383,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="278" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1469</v>
       </c>
@@ -27394,7 +27403,7 @@
         <v>1</v>
       </c>
       <c r="G278">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H278">
         <v>1</v>
@@ -27430,7 +27439,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="279" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1469</v>
       </c>
@@ -27447,7 +27456,7 @@
         <v>2</v>
       </c>
       <c r="G279">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H279">
         <v>1</v>
@@ -28629,7 +28638,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="295" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1536</v>
       </c>
@@ -28968,6 +28977,9 @@
       <c r="AP299" t="s">
         <v>1595</v>
       </c>
+      <c r="AQ299">
+        <v>2</v>
+      </c>
       <c r="AS299" t="s">
         <v>1596</v>
       </c>
@@ -28989,7 +29001,7 @@
         <v>16</v>
       </c>
       <c r="G300">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H300">
         <v>2</v>
@@ -29038,6 +29050,9 @@
       </c>
       <c r="AP300" t="s">
         <v>1600</v>
+      </c>
+      <c r="AQ300">
+        <v>2</v>
       </c>
       <c r="AS300" t="s">
         <v>1601</v>
@@ -29063,7 +29078,7 @@
         <v>16</v>
       </c>
       <c r="G301">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H301">
         <v>2</v>
@@ -30453,7 +30468,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="319" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1665</v>
       </c>
@@ -30462,6 +30477,9 @@
       </c>
       <c r="C319" t="s">
         <v>203</v>
+      </c>
+      <c r="D319">
+        <v>1249</v>
       </c>
       <c r="E319">
         <v>2</v>
@@ -31730,7 +31748,7 @@
         <v>1</v>
       </c>
       <c r="G334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H334">
         <v>1</v>
@@ -31798,7 +31816,7 @@
         <v>2</v>
       </c>
       <c r="G335">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H335">
         <v>1</v>
@@ -31866,7 +31884,7 @@
         <v>2</v>
       </c>
       <c r="G336">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H336">
         <v>1</v>
@@ -31909,6 +31927,9 @@
       </c>
       <c r="AP336" t="s">
         <v>1764</v>
+      </c>
+      <c r="AQ336">
+        <v>2</v>
       </c>
       <c r="AS336" t="s">
         <v>1765</v>
@@ -32472,7 +32493,7 @@
         <v>4</v>
       </c>
       <c r="G345">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N345">
         <v>2</v>
@@ -32527,6 +32548,9 @@
       </c>
       <c r="AP345" t="s">
         <v>1794</v>
+      </c>
+      <c r="AQ345">
+        <v>4</v>
       </c>
       <c r="AS345" t="s">
         <v>1795</v>
@@ -32552,7 +32576,7 @@
         <v>4</v>
       </c>
       <c r="G346">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N346">
         <v>2</v>
@@ -32604,6 +32628,9 @@
       </c>
       <c r="AP346" t="s">
         <v>1798</v>
+      </c>
+      <c r="AQ346">
+        <v>4</v>
       </c>
       <c r="AS346" t="s">
         <v>1795</v>
@@ -32629,7 +32656,7 @@
         <v>8</v>
       </c>
       <c r="G347">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N347">
         <v>2</v>
@@ -32681,6 +32708,9 @@
       </c>
       <c r="AP347" t="s">
         <v>1801</v>
+      </c>
+      <c r="AQ347">
+        <v>4</v>
       </c>
       <c r="AS347" t="s">
         <v>1795</v>
@@ -32706,7 +32736,7 @@
         <v>8</v>
       </c>
       <c r="G348">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N348">
         <v>2</v>
@@ -32761,6 +32791,9 @@
       </c>
       <c r="AP348" t="s">
         <v>1805</v>
+      </c>
+      <c r="AQ348">
+        <v>4</v>
       </c>
       <c r="AS348" t="s">
         <v>1795</v>
@@ -33001,6 +33034,9 @@
       <c r="F352">
         <v>2</v>
       </c>
+      <c r="G352">
+        <v>1</v>
+      </c>
       <c r="H352">
         <v>1</v>
       </c>
@@ -33158,6 +33194,9 @@
       <c r="F354">
         <v>4</v>
       </c>
+      <c r="G354">
+        <v>1</v>
+      </c>
       <c r="H354">
         <v>2</v>
       </c>
@@ -33321,6 +33360,9 @@
       <c r="F356">
         <v>4</v>
       </c>
+      <c r="G356">
+        <v>1</v>
+      </c>
       <c r="H356">
         <v>2</v>
       </c>
@@ -33379,7 +33421,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="357" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1752</v>
       </c>
@@ -33444,7 +33486,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="358" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1752</v>
       </c>
@@ -34186,7 +34228,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="369" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1853</v>
       </c>
@@ -34224,7 +34266,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="370" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1853</v>
       </c>
@@ -34343,6 +34385,9 @@
       <c r="E372">
         <v>6</v>
       </c>
+      <c r="G372">
+        <v>1</v>
+      </c>
       <c r="N372">
         <v>2</v>
       </c>
@@ -34383,7 +34428,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="373" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1853</v>
       </c>
@@ -34451,7 +34496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1853</v>
       </c>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5319" uniqueCount="1926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5324" uniqueCount="1929">
   <si>
     <t>Brand</t>
   </si>
@@ -5087,6 +5087,9 @@
     <t>https://www.uaudio.com/products/apollo-twin-x-usb</t>
   </si>
   <si>
+    <t>[ASR](https://www.audiosciencereview.com/forum/index.php?threads/universal-audio-apollo-twin-x-review-audio-interface.20456/)</t>
+  </si>
+  <si>
     <t>Apollo x16 Gen2</t>
   </si>
   <si>
@@ -5771,6 +5774,9 @@
     <t>https://zoomcorp.com/en/us/audio-interface/audio-interfaces/u-24/</t>
   </si>
   <si>
+    <t>[Manufacturer](https://zoomcorp.com/en/us/audio-interface/audio-interfaces/u-24/)</t>
+  </si>
+  <si>
     <t>U-44</t>
   </si>
   <si>
@@ -5778,6 +5784,9 @@
   </si>
   <si>
     <t>https://zoomcorp.com/en/us/audio-interface/audio-interfaces/u-44/</t>
+  </si>
+  <si>
+    <t>[Manufacturer](https://zoomcorp.com/en/us/audio-interface/audio-interfaces/u-44/)</t>
   </si>
   <si>
     <t>UAC-232</t>
@@ -19315,7 +19324,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>965</v>
       </c>
@@ -19390,6 +19399,9 @@
       </c>
       <c r="AP174" t="s">
         <v>976</v>
+      </c>
+      <c r="AS174" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="175" spans="1:45" x14ac:dyDescent="0.25">
@@ -19602,7 +19614,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>965</v>
       </c>
@@ -19671,6 +19683,9 @@
       </c>
       <c r="AP178" t="s">
         <v>976</v>
+      </c>
+      <c r="AS178" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="179" spans="1:45" x14ac:dyDescent="0.25">
@@ -30468,7 +30483,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="319" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1665</v>
       </c>
@@ -30522,6 +30537,9 @@
       </c>
       <c r="AP319" t="s">
         <v>1688</v>
+      </c>
+      <c r="AS319" t="s">
+        <v>1689</v>
       </c>
     </row>
     <row r="320" spans="1:45" x14ac:dyDescent="0.25">
@@ -30529,7 +30547,7 @@
         <v>1665</v>
       </c>
       <c r="B320" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="C320" t="s">
         <v>228</v>
@@ -30580,16 +30598,16 @@
         <v>54</v>
       </c>
       <c r="AN320" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="AO320" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="AP320" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="AS320" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="321" spans="1:45" x14ac:dyDescent="0.25">
@@ -30597,7 +30615,7 @@
         <v>1665</v>
       </c>
       <c r="B321" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="C321" t="s">
         <v>228</v>
@@ -30621,7 +30639,7 @@
         <v>24</v>
       </c>
       <c r="Y321" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="AB321" t="s">
         <v>1667</v>
@@ -30639,16 +30657,16 @@
         <v>54</v>
       </c>
       <c r="AN321" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="AO321" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="AP321" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="AS321" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="322" spans="1:45" x14ac:dyDescent="0.25">
@@ -30656,7 +30674,7 @@
         <v>1665</v>
       </c>
       <c r="B322" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="C322" t="s">
         <v>203</v>
@@ -30725,22 +30743,22 @@
         <v>129</v>
       </c>
       <c r="AI322" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="AM322" t="s">
         <v>54</v>
       </c>
       <c r="AN322" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="AO322" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="AP322" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="AS322" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="323" spans="1:45" x14ac:dyDescent="0.25">
@@ -30748,7 +30766,7 @@
         <v>1665</v>
       </c>
       <c r="B323" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="C323" t="s">
         <v>203</v>
@@ -30826,22 +30844,22 @@
         <v>243</v>
       </c>
       <c r="AI323" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="AM323" t="s">
         <v>54</v>
       </c>
       <c r="AN323" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="AO323" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="AP323" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="AS323" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="324" spans="1:45" x14ac:dyDescent="0.25">
@@ -30849,7 +30867,7 @@
         <v>1665</v>
       </c>
       <c r="B324" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="C324" t="s">
         <v>228</v>
@@ -30924,22 +30942,22 @@
         <v>243</v>
       </c>
       <c r="AI324" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="AM324" t="s">
         <v>54</v>
       </c>
       <c r="AN324" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="AO324" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="AP324" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="AS324" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="325" spans="1:45" x14ac:dyDescent="0.25">
@@ -30947,7 +30965,7 @@
         <v>1665</v>
       </c>
       <c r="B325" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C325" t="s">
         <v>228</v>
@@ -31025,22 +31043,22 @@
         <v>243</v>
       </c>
       <c r="AI325" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="AM325" t="s">
         <v>54</v>
       </c>
       <c r="AN325" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="AO325" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="AP325" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="AS325" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="326" spans="1:45" x14ac:dyDescent="0.25">
@@ -31048,7 +31066,7 @@
         <v>1665</v>
       </c>
       <c r="B326" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="C326" t="s">
         <v>295</v>
@@ -31096,10 +31114,10 @@
         <v>124</v>
       </c>
       <c r="AH326" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AI326" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AK326" t="s">
         <v>819</v>
@@ -31108,16 +31126,16 @@
         <v>54</v>
       </c>
       <c r="AN326" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="AO326" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="AP326" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="AS326" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="327" spans="1:45" x14ac:dyDescent="0.25">
@@ -31125,7 +31143,7 @@
         <v>1665</v>
       </c>
       <c r="B327" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="C327" t="s">
         <v>269</v>
@@ -31179,10 +31197,10 @@
         <v>52</v>
       </c>
       <c r="AH327" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AI327" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AK327" t="s">
         <v>819</v>
@@ -31191,16 +31209,16 @@
         <v>280</v>
       </c>
       <c r="AN327" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="AO327" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="AP327" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="AS327" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="328" spans="1:45" x14ac:dyDescent="0.25">
@@ -31208,7 +31226,7 @@
         <v>1665</v>
       </c>
       <c r="B328" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="C328" t="s">
         <v>295</v>
@@ -31262,10 +31280,10 @@
         <v>110</v>
       </c>
       <c r="AH328" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="AI328" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AK328" t="s">
         <v>819</v>
@@ -31274,16 +31292,16 @@
         <v>280</v>
       </c>
       <c r="AN328" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="AO328" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="AP328" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="AS328" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="329" spans="1:45" x14ac:dyDescent="0.25">
@@ -31291,7 +31309,7 @@
         <v>1665</v>
       </c>
       <c r="B329" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="C329" t="s">
         <v>269</v>
@@ -31342,10 +31360,10 @@
         <v>52</v>
       </c>
       <c r="AH329" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AI329" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AK329" t="s">
         <v>819</v>
@@ -31354,16 +31372,16 @@
         <v>280</v>
       </c>
       <c r="AN329" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="AO329" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="AP329" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="AS329" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="330" spans="1:45" x14ac:dyDescent="0.25">
@@ -31371,7 +31389,7 @@
         <v>1665</v>
       </c>
       <c r="B330" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="C330" t="s">
         <v>269</v>
@@ -31428,10 +31446,10 @@
         <v>52</v>
       </c>
       <c r="AH330" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AI330" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AK330" t="s">
         <v>819</v>
@@ -31440,16 +31458,16 @@
         <v>280</v>
       </c>
       <c r="AN330" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="AO330" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="AP330" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="AS330" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="331" spans="1:45" x14ac:dyDescent="0.25">
@@ -31457,7 +31475,7 @@
         <v>1665</v>
       </c>
       <c r="B331" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="C331" t="s">
         <v>269</v>
@@ -31520,10 +31538,10 @@
         <v>52</v>
       </c>
       <c r="AH331" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AI331" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AK331" t="s">
         <v>819</v>
@@ -31532,16 +31550,16 @@
         <v>54</v>
       </c>
       <c r="AN331" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="AO331" t="s">
         <v>385</v>
       </c>
       <c r="AP331" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="AS331" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="332" spans="1:45" x14ac:dyDescent="0.25">
@@ -31549,7 +31567,7 @@
         <v>1665</v>
       </c>
       <c r="B332" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="C332" t="s">
         <v>269</v>
@@ -31603,10 +31621,10 @@
         <v>110</v>
       </c>
       <c r="AH332" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AI332" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AK332" t="s">
         <v>819</v>
@@ -31615,13 +31633,13 @@
         <v>280</v>
       </c>
       <c r="AO332" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="AP332" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="AS332" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="333" spans="1:45" x14ac:dyDescent="0.25">
@@ -31629,7 +31647,7 @@
         <v>1665</v>
       </c>
       <c r="B333" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="C333" t="s">
         <v>255</v>
@@ -31674,7 +31692,7 @@
         <v>235</v>
       </c>
       <c r="V333" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="W333">
         <v>192</v>
@@ -31716,24 +31734,24 @@
         <v>289</v>
       </c>
       <c r="AN333" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="AO333" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="AP333" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="AS333" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="334" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B334" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C334" t="s">
         <v>379</v>
@@ -31784,24 +31802,24 @@
         <v>280</v>
       </c>
       <c r="AN334" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="AO334" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="AP334" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="AS334" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="335" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B335" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="C335" t="s">
         <v>379</v>
@@ -31852,24 +31870,24 @@
         <v>280</v>
       </c>
       <c r="AN335" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="AO335" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="AP335" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="AS335" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="336" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B336" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="C336" t="s">
         <v>379</v>
@@ -31920,27 +31938,27 @@
         <v>280</v>
       </c>
       <c r="AN336" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="AO336" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AP336" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="AQ336">
         <v>2</v>
       </c>
       <c r="AS336" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="337" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B337" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C337" t="s">
         <v>47</v>
@@ -31997,24 +32015,24 @@
         <v>54</v>
       </c>
       <c r="AN337" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="AO337" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="AP337" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="AS337" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="338" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B338" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="C338" t="s">
         <v>47</v>
@@ -32071,24 +32089,24 @@
         <v>54</v>
       </c>
       <c r="AN338" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="AO338" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="AP338" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="AS338" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="339" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B339" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="C339" t="s">
         <v>47</v>
@@ -32133,24 +32151,24 @@
         <v>54</v>
       </c>
       <c r="AN339" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="AO339" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="AP339" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="AS339" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="340" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B340" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="C340" t="s">
         <v>47</v>
@@ -32192,24 +32210,24 @@
         <v>54</v>
       </c>
       <c r="AN340" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="AO340" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="AP340" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AS340" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="341" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B341" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="C341" t="s">
         <v>47</v>
@@ -32263,21 +32281,21 @@
         <v>54</v>
       </c>
       <c r="AO341" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="AP341" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AS341" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="342" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B342" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C342" t="s">
         <v>47</v>
@@ -32328,21 +32346,21 @@
         <v>54</v>
       </c>
       <c r="AO342" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="AP342" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AS342" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="343" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B343" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="C343" t="s">
         <v>47</v>
@@ -32393,24 +32411,24 @@
         <v>54</v>
       </c>
       <c r="AN343" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="AO343" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="AP343" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AS343" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="344" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B344" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="C344" t="s">
         <v>47</v>
@@ -32464,21 +32482,21 @@
         <v>54</v>
       </c>
       <c r="AO344" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="AP344" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AS344" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="345" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B345" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="C345" t="s">
         <v>47</v>
@@ -32526,7 +32544,7 @@
         <v>48</v>
       </c>
       <c r="AD345" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="AG345" t="s">
         <v>1190</v>
@@ -32541,27 +32559,27 @@
         <v>54</v>
       </c>
       <c r="AN345" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="AO345" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="AP345" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="AQ345">
         <v>4</v>
       </c>
       <c r="AS345" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="346" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B346" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="C346" t="s">
         <v>47</v>
@@ -32609,7 +32627,7 @@
         <v>48</v>
       </c>
       <c r="AD346" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="AF346" t="s">
         <v>1190</v>
@@ -32624,24 +32642,24 @@
         <v>54</v>
       </c>
       <c r="AO346" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="AP346" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="AQ346">
         <v>4</v>
       </c>
       <c r="AS346" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="347" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B347" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="C347" t="s">
         <v>47</v>
@@ -32689,7 +32707,7 @@
         <v>48</v>
       </c>
       <c r="AD347" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="AG347" t="s">
         <v>1190</v>
@@ -32704,24 +32722,24 @@
         <v>54</v>
       </c>
       <c r="AO347" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="AP347" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="AQ347">
         <v>4</v>
       </c>
       <c r="AS347" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="348" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B348" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="C348" t="s">
         <v>47</v>
@@ -32769,7 +32787,7 @@
         <v>48</v>
       </c>
       <c r="AD348" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="AF348" t="s">
         <v>1190</v>
@@ -32784,27 +32802,27 @@
         <v>54</v>
       </c>
       <c r="AN348" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="AO348" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="AP348" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="AQ348">
         <v>4</v>
       </c>
       <c r="AS348" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="349" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B349" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="C349" t="s">
         <v>203</v>
@@ -32834,7 +32852,7 @@
         <v>24</v>
       </c>
       <c r="Y349" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="AF349" t="s">
         <v>360</v>
@@ -32846,24 +32864,24 @@
         <v>54</v>
       </c>
       <c r="AN349" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="AO349" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="AP349" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="AS349" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="350" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B350" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="C350" t="s">
         <v>295</v>
@@ -32926,24 +32944,24 @@
         <v>54</v>
       </c>
       <c r="AN350" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="AO350" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="AP350" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="AS350" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="351" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B351" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="C351" t="s">
         <v>295</v>
@@ -33003,24 +33021,24 @@
         <v>54</v>
       </c>
       <c r="AN351" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="AO351" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="AP351" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="AS351" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="352" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B352" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="C352" t="s">
         <v>269</v>
@@ -33056,7 +33074,7 @@
         <v>32</v>
       </c>
       <c r="Y352" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="AB352" t="s">
         <v>73</v>
@@ -33074,7 +33092,7 @@
         <v>1366</v>
       </c>
       <c r="AI352" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="AK352" t="s">
         <v>264</v>
@@ -33083,24 +33101,24 @@
         <v>54</v>
       </c>
       <c r="AN352" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="AO352" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="AP352" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="AS352" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="353" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B353" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="C353" t="s">
         <v>269</v>
@@ -33133,7 +33151,7 @@
         <v>32</v>
       </c>
       <c r="Y353" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="Z353" t="s">
         <v>270</v>
@@ -33163,24 +33181,24 @@
         <v>54</v>
       </c>
       <c r="AN353" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="AO353" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="AP353" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="AS353" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="354" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B354" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="C354" t="s">
         <v>269</v>
@@ -33216,7 +33234,7 @@
         <v>32</v>
       </c>
       <c r="Y354" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="AB354" t="s">
         <v>73</v>
@@ -33234,7 +33252,7 @@
         <v>1366</v>
       </c>
       <c r="AI354" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="AK354" t="s">
         <v>264</v>
@@ -33243,24 +33261,24 @@
         <v>54</v>
       </c>
       <c r="AN354" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="AO354" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="AP354" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="AS354" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="355" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B355" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="C355" t="s">
         <v>269</v>
@@ -33296,7 +33314,7 @@
         <v>32</v>
       </c>
       <c r="Y355" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="Z355" t="s">
         <v>270</v>
@@ -33308,7 +33326,7 @@
         <v>73</v>
       </c>
       <c r="AC355" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="AD355">
         <v>54</v>
@@ -33329,24 +33347,24 @@
         <v>54</v>
       </c>
       <c r="AN355" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="AO355" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="AP355" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="AS355" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="356" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B356" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C356" t="s">
         <v>255</v>
@@ -33382,7 +33400,7 @@
         <v>32</v>
       </c>
       <c r="Y356" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="AB356" t="s">
         <v>73</v>
@@ -33400,7 +33418,7 @@
         <v>1366</v>
       </c>
       <c r="AI356" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="AK356" t="s">
         <v>264</v>
@@ -33409,24 +33427,24 @@
         <v>54</v>
       </c>
       <c r="AN356" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="AO356" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="AP356" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="AS356" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="357" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B357" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C357" t="s">
         <v>379</v>
@@ -33477,21 +33495,21 @@
         <v>54</v>
       </c>
       <c r="AN357" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="AO357" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="AP357" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="358" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B358" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="C358" t="s">
         <v>379</v>
@@ -33536,18 +33554,18 @@
         <v>54</v>
       </c>
       <c r="AO358" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AP358" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="359" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B359" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="C359" t="s">
         <v>295</v>
@@ -33592,10 +33610,10 @@
         <v>48</v>
       </c>
       <c r="AD359" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="AK359" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="AM359" t="s">
         <v>258</v>
@@ -33604,18 +33622,18 @@
         <v>740</v>
       </c>
       <c r="AP359" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="AS359" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="360" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B360" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="C360" t="s">
         <v>295</v>
@@ -33657,7 +33675,7 @@
         <v>48</v>
       </c>
       <c r="AD360" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="AK360">
         <v>-120</v>
@@ -33666,21 +33684,21 @@
         <v>761</v>
       </c>
       <c r="AO360" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="AP360" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="AS360" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="361" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B361" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="C361" t="s">
         <v>295</v>
@@ -33722,30 +33740,30 @@
         <v>48</v>
       </c>
       <c r="AD361" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="AK361" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="AM361" t="s">
         <v>258</v>
       </c>
       <c r="AO361" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="AP361" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="AS361" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="362" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B362" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="C362" t="s">
         <v>47</v>
@@ -33793,7 +33811,7 @@
         <v>73</v>
       </c>
       <c r="AD362" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="AK362" t="s">
         <v>264</v>
@@ -33802,21 +33820,21 @@
         <v>54</v>
       </c>
       <c r="AO362" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="AP362" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="AS362" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="363" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B363" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="C363" t="s">
         <v>47</v>
@@ -33873,21 +33891,21 @@
         <v>280</v>
       </c>
       <c r="AO363" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="AP363" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="AS363" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="364" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B364" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C364" t="s">
         <v>47</v>
@@ -33935,30 +33953,30 @@
         <v>48</v>
       </c>
       <c r="AD364" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="AK364">
         <v>-128</v>
       </c>
       <c r="AM364" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="AO364" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="AP364" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="AS364" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="365" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B365" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="C365" t="s">
         <v>47</v>
@@ -34009,27 +34027,27 @@
         <v>48</v>
       </c>
       <c r="AK365" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="AM365" t="s">
         <v>258</v>
       </c>
       <c r="AO365" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="AP365" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="AS365" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="366" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B366" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="C366" t="s">
         <v>47</v>
@@ -34074,30 +34092,30 @@
         <v>73</v>
       </c>
       <c r="AD366" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="AK366" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="AM366" t="s">
         <v>289</v>
       </c>
       <c r="AO366" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="AP366" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="AS366" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="367" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B367" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="C367" t="s">
         <v>47</v>
@@ -34142,30 +34160,30 @@
         <v>48</v>
       </c>
       <c r="AD367" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="AK367">
         <v>-128</v>
       </c>
       <c r="AM367" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="AO367" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="AP367" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="AS367" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="368" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B368" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="C368" t="s">
         <v>47</v>
@@ -34219,21 +34237,21 @@
         <v>761</v>
       </c>
       <c r="AO368" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="AP368" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="AS368" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="369" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B369" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="C369" t="s">
         <v>379</v>
@@ -34257,21 +34275,21 @@
         <v>54</v>
       </c>
       <c r="AN369" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="AO369" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="AP369" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="370" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B370" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="C370" t="s">
         <v>379</v>
@@ -34307,18 +34325,18 @@
         <v>258</v>
       </c>
       <c r="AO370" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="AP370" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="371" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B371" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C371" t="s">
         <v>379</v>
@@ -34351,7 +34369,7 @@
         <v>48</v>
       </c>
       <c r="AD371" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="AK371">
         <v>-125</v>
@@ -34360,21 +34378,21 @@
         <v>761</v>
       </c>
       <c r="AO371" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="AP371" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="AS371" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="372" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B372" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="C372" t="s">
         <v>379</v>
@@ -34413,27 +34431,27 @@
         <v>70</v>
       </c>
       <c r="AK372" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="AM372" t="s">
         <v>54</v>
       </c>
       <c r="AO372" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="AP372" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="AS372" t="s">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="373" spans="1:44" x14ac:dyDescent="0.25">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="373" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B373" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="C373" t="s">
         <v>295</v>
@@ -34475,7 +34493,7 @@
         <v>48</v>
       </c>
       <c r="AD373" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="AK373">
         <v>-119.5</v>
@@ -34487,21 +34505,24 @@
         <v>1429</v>
       </c>
       <c r="AO373" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="AP373" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="AR373">
         <v>2</v>
       </c>
-    </row>
-    <row r="374" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS373" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="374" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B374" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C374" t="s">
         <v>295</v>
@@ -34555,7 +34576,7 @@
         <v>48</v>
       </c>
       <c r="AD374" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="AK374">
         <v>-119.5</v>
@@ -34567,21 +34588,24 @@
         <v>1429</v>
       </c>
       <c r="AO374" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="AP374" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="AR374">
         <v>2</v>
+      </c>
+      <c r="AS374" t="s">
+        <v>1922</v>
       </c>
     </row>
     <row r="375" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B375" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="C375" t="s">
         <v>295</v>
@@ -34632,13 +34656,13 @@
         <v>280</v>
       </c>
       <c r="AO375" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="AP375" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="AS375" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
     </row>
   </sheetData>
@@ -34660,7 +34684,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -34713,7 +34737,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="B8">
         <v>216</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -482,7 +482,7 @@
     <t>-6 to +63</t>
   </si>
   <si>
-    <t>Compact broadcast mixer: 4 mono mic/line channels (XLR mic or 1/4" TRS line, separate gain ranges: mic -6 to +63 dB, line -10 to +26 dB) + 2 telco channels (XLR in, clean-feed XLR out) + 4 stereo channels (7 stereo sources incl. USB return ST6); 3-band EQ on mono channels; fader-start/remote logic I/O; Audition bus; Mix B bus; stereo USB audio CODEC (bi-directional); main program outputs on XLR; RCA outputs counted: Mix B L/R, CRM speakers L/R, Audition L/R, mono PGM; separate aux output (1/4" TRS); EX MON stereo RCA input; 3 headphone outputs (operator + 2 guest) with talk button</t>
+    <t>Compact broadcast mixer: 4 mono mic/line channels (XLR mic or 1/4" TRS line, separate gain ranges: mic -6 to +63 dB, line -10 to +26 dB) + 2 telco channels (XLR in, clean-feed XLR out) + 4 stereo channels (7 stereo sources incl. USB return ST6); 3-band EQ on mono channels; fader-start/remote logic I/O; Audition bus; Mix B bus; stereo USB audio CODEC (bi-directional); main program outputs on XLR; RCA outputs counted: Mix B L/R, CRM speakers L/R, Audition L/R, mono PGM; separate aux output (1/4" TRS); EX MON stereo RCA input; 3 headphone outputs (operator + 2 guest) with talk button; inputs counted: ST1/ST5/ST7 on 1/4" jacks, ST2 and EX MON on RCA; connector type of ST3/ST4 not published</t>
   </si>
   <si>
     <t>https://www.allen-heath.com/hardware/xb-series/xb-142/</t>
@@ -1907,7 +1907,7 @@
     <t>XENYX X2222USB</t>
   </si>
   <si>
-    <t>22-input 2-bus analog mixer, 8 mono mic/line ch + 7 stereo line pairs, 2 subgroups, 3 aux sends/returns, tap tempo FX, CD/Tape RCA I/O, built-in 24-bit Multi-FX (16 presets), USB version not stated by manufacturer</t>
+    <t>22-input 2-bus analog mixer, 8 mono mic/line ch + 4 stereo ch + 3 stereo aux returns, 2 subgroups, 3 aux sends/returns, tap tempo FX, CD/Tape RCA I/O, built-in 24-bit Multi-FX (16 presets), USB version not stated by manufacturer</t>
   </si>
   <si>
     <t>https://www.behringer.com/en/products/0601-ADA</t>
@@ -6783,6 +6783,9 @@
       <c r="E8">
         <v>16</v>
       </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
       <c r="G8">
         <v>4</v>
       </c>
@@ -6857,6 +6860,9 @@
       <c r="E9">
         <v>16</v>
       </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
       <c r="G9">
         <v>4</v>
       </c>
@@ -6931,6 +6937,9 @@
       <c r="E10">
         <v>24</v>
       </c>
+      <c r="F10">
+        <v>24</v>
+      </c>
       <c r="G10">
         <v>4</v>
       </c>
@@ -7005,6 +7014,9 @@
       <c r="E11">
         <v>24</v>
       </c>
+      <c r="F11">
+        <v>24</v>
+      </c>
       <c r="G11">
         <v>4</v>
       </c>
@@ -7079,6 +7091,9 @@
       <c r="E12">
         <v>32</v>
       </c>
+      <c r="F12">
+        <v>32</v>
+      </c>
       <c r="G12">
         <v>4</v>
       </c>
@@ -7153,6 +7168,9 @@
       <c r="E13">
         <v>32</v>
       </c>
+      <c r="F13">
+        <v>32</v>
+      </c>
       <c r="G13">
         <v>4</v>
       </c>
@@ -7826,7 +7844,7 @@
         <v>4</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -7851,6 +7869,9 @@
       </c>
       <c r="AP22" t="s">
         <v>155</v>
+      </c>
+      <c r="AQ22">
+        <v>4</v>
       </c>
       <c r="AR22">
         <v>7</v>
@@ -8021,7 +8042,7 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N25">
         <v>2</v>
@@ -8095,7 +8116,7 @@
         <v>6</v>
       </c>
       <c r="G26">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N26">
         <v>2</v>
@@ -8163,7 +8184,7 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -8237,7 +8258,7 @@
         <v>10</v>
       </c>
       <c r="G28">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N28">
         <v>2</v>
@@ -8305,7 +8326,7 @@
         <v>16</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -8379,7 +8400,7 @@
         <v>16</v>
       </c>
       <c r="G30">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N30">
         <v>2</v>
@@ -8527,7 +8548,7 @@
         <v>4</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>2</v>
@@ -8601,7 +8622,7 @@
         <v>4</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H33">
         <v>2</v>
@@ -8678,7 +8699,7 @@
         <v>2</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>2</v>
@@ -13551,7 +13572,7 @@
         <v>2</v>
       </c>
       <c r="G96">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N96">
         <v>2</v>
@@ -13597,6 +13618,9 @@
       </c>
       <c r="AP96" t="s">
         <v>565</v>
+      </c>
+      <c r="AQ96">
+        <v>2</v>
       </c>
       <c r="AS96" t="s">
         <v>566</v>
@@ -13619,7 +13643,7 @@
         <v>4</v>
       </c>
       <c r="G97">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N97">
         <v>2</v>
@@ -13662,6 +13686,9 @@
       </c>
       <c r="AP97" t="s">
         <v>569</v>
+      </c>
+      <c r="AQ97">
+        <v>2</v>
       </c>
       <c r="AS97" t="s">
         <v>570</v>
@@ -13855,6 +13882,12 @@
       <c r="AP100" t="s">
         <v>584</v>
       </c>
+      <c r="AQ100">
+        <v>2</v>
+      </c>
+      <c r="AR100">
+        <v>2</v>
+      </c>
       <c r="AS100" t="s">
         <v>585</v>
       </c>
@@ -13920,6 +13953,9 @@
       <c r="AP101" t="s">
         <v>589</v>
       </c>
+      <c r="AQ101">
+        <v>2</v>
+      </c>
       <c r="AR101" t="s">
         <v>65</v>
       </c>
@@ -13941,7 +13977,7 @@
         <v>4</v>
       </c>
       <c r="G102">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N102">
         <v>2</v>
@@ -14012,7 +14048,7 @@
         <v>4</v>
       </c>
       <c r="G103">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N103">
         <v>2</v>
@@ -14083,10 +14119,10 @@
         <v>47</v>
       </c>
       <c r="E104">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G104">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N104">
         <v>2</v>
@@ -14157,7 +14193,7 @@
         <v>6</v>
       </c>
       <c r="G105">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N105">
         <v>2</v>
@@ -14225,7 +14261,7 @@
         <v>8</v>
       </c>
       <c r="G106">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N106">
         <v>2</v>
@@ -14293,7 +14329,7 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N107">
         <v>2</v>
@@ -14432,7 +14468,7 @@
         <v>6</v>
       </c>
       <c r="G109">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N109">
         <v>2</v>
@@ -14574,7 +14610,7 @@
         <v>6</v>
       </c>
       <c r="G111">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N111">
         <v>2</v>
@@ -14648,7 +14684,7 @@
         <v>8</v>
       </c>
       <c r="G112">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N112">
         <v>2</v>
@@ -14722,7 +14758,7 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N113">
         <v>2</v>
@@ -24687,6 +24723,9 @@
       <c r="AP242" t="s">
         <v>1305</v>
       </c>
+      <c r="AQ242">
+        <v>2</v>
+      </c>
       <c r="AS242" t="s">
         <v>1306</v>
       </c>
@@ -24707,11 +24746,8 @@
       <c r="E243">
         <v>12</v>
       </c>
-      <c r="F243">
-        <v>12</v>
-      </c>
       <c r="G243">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H243">
         <v>2</v>
@@ -24766,6 +24802,9 @@
       </c>
       <c r="AP243" t="s">
         <v>1309</v>
+      </c>
+      <c r="AQ243">
+        <v>2</v>
       </c>
       <c r="AS243" t="s">
         <v>1310</v>
@@ -24788,7 +24827,7 @@
         <v>4</v>
       </c>
       <c r="G244">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H244">
         <v>2</v>
@@ -24840,6 +24879,9 @@
       </c>
       <c r="AP244" t="s">
         <v>1313</v>
+      </c>
+      <c r="AQ244">
+        <v>2</v>
       </c>
       <c r="AS244" t="s">
         <v>1314</v>
@@ -27762,6 +27804,9 @@
       <c r="AP284" t="s">
         <v>1518</v>
       </c>
+      <c r="AQ284">
+        <v>2</v>
+      </c>
       <c r="AS284" t="s">
         <v>1519</v>
       </c>
@@ -27786,7 +27831,7 @@
         <v>1</v>
       </c>
       <c r="G285">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H285">
         <v>1</v>
@@ -27829,6 +27874,9 @@
       </c>
       <c r="AP285" t="s">
         <v>1522</v>
+      </c>
+      <c r="AQ285">
+        <v>2</v>
       </c>
       <c r="AS285" t="s">
         <v>1523</v>
@@ -27904,6 +27952,9 @@
       <c r="AP286" t="s">
         <v>1526</v>
       </c>
+      <c r="AQ286">
+        <v>2</v>
+      </c>
       <c r="AS286" t="s">
         <v>1519</v>
       </c>
@@ -27927,9 +27978,6 @@
       <c r="F287">
         <v>10</v>
       </c>
-      <c r="G287">
-        <v>2</v>
-      </c>
       <c r="H287">
         <v>2</v>
       </c>
@@ -27977,6 +28025,9 @@
       </c>
       <c r="AP287" t="s">
         <v>1531</v>
+      </c>
+      <c r="AQ287">
+        <v>2</v>
       </c>
       <c r="AS287" t="s">
         <v>1532</v>
@@ -29245,7 +29296,7 @@
       <c r="E304">
         <v>16</v>
       </c>
-      <c r="F304">
+      <c r="G304">
         <v>8</v>
       </c>
       <c r="N304">
@@ -29313,7 +29364,7 @@
       <c r="E305">
         <v>24</v>
       </c>
-      <c r="F305">
+      <c r="G305">
         <v>8</v>
       </c>
       <c r="N305">
@@ -32108,6 +32159,9 @@
       <c r="AP339" t="s">
         <v>1774</v>
       </c>
+      <c r="AQ339">
+        <v>4</v>
+      </c>
       <c r="AS339" t="s">
         <v>1775</v>
       </c>
@@ -32167,6 +32221,9 @@
       <c r="AP340" t="s">
         <v>1778</v>
       </c>
+      <c r="AQ340">
+        <v>4</v>
+      </c>
       <c r="AS340" t="s">
         <v>1775</v>
       </c>
@@ -32235,6 +32292,9 @@
       <c r="AP341" t="s">
         <v>1778</v>
       </c>
+      <c r="AQ341">
+        <v>4</v>
+      </c>
       <c r="AS341" t="s">
         <v>1781</v>
       </c>
@@ -32253,10 +32313,10 @@
         <v>6</v>
       </c>
       <c r="F342">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G342">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N342">
         <v>2</v>
@@ -32299,6 +32359,9 @@
       </c>
       <c r="AP342" t="s">
         <v>1778</v>
+      </c>
+      <c r="AQ342">
+        <v>4</v>
       </c>
       <c r="AS342" t="s">
         <v>1781</v>
@@ -32368,6 +32431,9 @@
       <c r="AP343" t="s">
         <v>1778</v>
       </c>
+      <c r="AQ343">
+        <v>4</v>
+      </c>
       <c r="AS343" t="s">
         <v>1786</v>
       </c>
@@ -32392,7 +32458,7 @@
         <v>12</v>
       </c>
       <c r="G344">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N344">
         <v>2</v>
@@ -32435,6 +32501,9 @@
       </c>
       <c r="AP344" t="s">
         <v>1778</v>
+      </c>
+      <c r="AQ344">
+        <v>4</v>
       </c>
       <c r="AS344" t="s">
         <v>1786</v>
@@ -33727,7 +33796,7 @@
         <v>8</v>
       </c>
       <c r="G362">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H362" t="s">
         <v>65</v>
@@ -33773,6 +33842,9 @@
       </c>
       <c r="AP362" t="s">
         <v>1866</v>
+      </c>
+      <c r="AQ362">
+        <v>4</v>
       </c>
       <c r="AS362" t="s">
         <v>1867</v>
@@ -33798,7 +33870,7 @@
         <v>16</v>
       </c>
       <c r="G363">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H363">
         <v>2</v>
@@ -33844,6 +33916,9 @@
       </c>
       <c r="AP363" t="s">
         <v>1870</v>
+      </c>
+      <c r="AQ363">
+        <v>4</v>
       </c>
       <c r="AS363" t="s">
         <v>1871</v>
@@ -33915,6 +33990,9 @@
       </c>
       <c r="AP364" t="s">
         <v>1875</v>
+      </c>
+      <c r="AQ364">
+        <v>4</v>
       </c>
       <c r="AS364" t="s">
         <v>1876</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5299" uniqueCount="1930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5299" uniqueCount="1929">
   <si>
     <t>Brand</t>
   </si>
@@ -185,7 +185,7 @@
     <t>macOS/Windows</t>
   </si>
   <si>
-    <t>10-in digital mixer+USB IF, 7-inch touchscreen, 16x16 SD card multitrack recording, Bluetooth; 5 non-combo XLR inputs accept mic or line level (counted in Mic Preamps and Line Inputs)</t>
+    <t>12-in/8-out digital mixer+USB IF, 7-inch touchscreen, 16x16 SD card multitrack recording, Bluetooth; 5 non-combo XLR inputs accept mic or line level (counted in Mic Preamps and Line Inputs)</t>
   </si>
   <si>
     <t>https://www.allen-heath.com/hardware/cq/cq-12t/</t>
@@ -554,7 +554,7 @@
     <t>10 mono mic/line channels (separate XLR mic + 1/4" TRS line jack per channel, not a combo jack) + 3 stereo channels = 16 channels total. Same shared platform as ZED-12FX/22FX: built-in USB 1.1 class-compliant, 2-in/2-out stereo audio interface (16-bit, 32/44.1/48kHz). 4 Aux buses (3 external + 1 internal FX send). Onboard 24-bit/48kHz digital FX processor, 16 reverb/delay/modulation types. Mic preamp gain -6 to +63dB. Two of three stereo channels have RCA/phono return input; the third takes USB return. Main out = XLR L/R + separate mono jack (mono jack counted in Analog Line Output along with 3 Aux sends). RCA Output = Alt Out L/R + Rec Out L/R. Headphone jacks: one 1/4" + one 3.5mm. No USD price on manufacturer page; non-official retailer listings show roughly $590-940.</t>
   </si>
   <si>
-    <t>https://www.allen-heath.com/hardware/zed-series/zed-16fx/</t>
+    <t>https://www.allen-heath.com/hardware/zed-series/zed-mid/zed-16fx/</t>
   </si>
   <si>
     <t>ZED-18</t>
@@ -569,7 +569,7 @@
     <t>16 mono mic/line channels (separate XLR mic + 1/4" TRS line jack per channel, not a combo jack) + 3 stereo channels = 22 channels total. Same shared platform as ZED-12FX/16FX: built-in USB 1.1 class-compliant, 2-in/2-out stereo audio interface (16-bit, 32/44.1/48kHz). 4 Aux buses (3 external + 1 internal FX send). Onboard 24-bit/48kHz digital FX processor, 16 reverb/delay/modulation types. Mic preamp gain -6 to +63dB. Two of three stereo channels have RCA/phono return input; the third takes USB return. Main out = XLR L/R + separate mono jack (mono jack counted in Analog Line Output along with 3 Aux sends). RCA Output = Alt Out L/R + Rec Out L/R. Headphone jacks: one 1/4" + one 3.5mm. No USD price on manufacturer page; non-official retailer listing (Sweetwater) shows roughly $1,300.</t>
   </si>
   <si>
-    <t>https://www.allen-heath.com/hardware/zed-series/zed-22fx/</t>
+    <t>https://www.allen-heath.com/hardware/zed-series/zed-mid/zed-22fx/</t>
   </si>
   <si>
     <t>ZED-24</t>
@@ -5351,7 +5351,7 @@
     <t>10ch analog mixer+USB IF, D-PRE preamp, 1knobcompressor, 3-band EQ</t>
   </si>
   <si>
-    <t>https://usa.yamaha.com/products/proaudio/mixers/mg_series_xu_xuf/index.html</t>
+    <t>https://usa.yamaha.com/products/proaudio/mixers/mg_series_xu_model/index.html</t>
   </si>
   <si>
     <t>[Manufacturer](https://data.yamaha.com/files/download/other_assets/2/1507032/MG10XU_technical_specifications_En_B0.pdf)</t>
@@ -5361,9 +5361,6 @@
   </si>
   <si>
     <t>10ch analog mixer+USB IF, D-PRE preamp, 1-knob compressor, 3-band EQ, fader-type STEREO OUT master level control (base MG10XU uses a rotary STEREO LEVEL knob instead)</t>
-  </si>
-  <si>
-    <t>https://usa.yamaha.com/products/proaudio/mixers/mg_series_xu_model/index.html</t>
   </si>
   <si>
     <t>MG12XU</t>
@@ -7900,7 +7897,7 @@
         <v>4</v>
       </c>
       <c r="G23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>2</v>
@@ -7974,7 +7971,7 @@
         <v>4</v>
       </c>
       <c r="G24">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H24">
         <v>2</v>
@@ -8477,7 +8474,7 @@
         <v>4</v>
       </c>
       <c r="G31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -10409,7 +10406,7 @@
         <v>338</v>
       </c>
       <c r="AE55">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AF55">
         <v>119</v>
@@ -14785,7 +14782,7 @@
         <v>2</v>
       </c>
       <c r="P113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V113" t="s">
         <v>48</v>
@@ -22651,7 +22648,7 @@
         <v>2</v>
       </c>
       <c r="O218">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P218">
         <v>1</v>
@@ -25053,7 +25050,7 @@
         <v>2</v>
       </c>
       <c r="P246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R246">
         <v>1</v>
@@ -32264,7 +32261,7 @@
         <v>1780</v>
       </c>
       <c r="AP340" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="AQ340">
         <v>4</v>
@@ -32278,7 +32275,7 @@
         <v>1754</v>
       </c>
       <c r="B341" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C341" t="s">
         <v>47</v>
@@ -32332,16 +32329,16 @@
         <v>54</v>
       </c>
       <c r="AO341" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="AP341" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="AQ341">
         <v>4</v>
       </c>
       <c r="AS341" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="342" spans="1:45" x14ac:dyDescent="0.25">
@@ -32349,7 +32346,7 @@
         <v>1754</v>
       </c>
       <c r="B342" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="C342" t="s">
         <v>47</v>
@@ -32400,16 +32397,16 @@
         <v>54</v>
       </c>
       <c r="AO342" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="AP342" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="AQ342">
         <v>4</v>
       </c>
       <c r="AS342" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="343" spans="1:45" x14ac:dyDescent="0.25">
@@ -32417,7 +32414,7 @@
         <v>1754</v>
       </c>
       <c r="B343" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="C343" t="s">
         <v>47</v>
@@ -32438,7 +32435,7 @@
         <v>2</v>
       </c>
       <c r="O343">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P343">
         <v>1</v>
@@ -32471,16 +32468,16 @@
         <v>1764</v>
       </c>
       <c r="AO343" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="AP343" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="AQ343">
         <v>4</v>
       </c>
       <c r="AS343" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="344" spans="1:45" x14ac:dyDescent="0.25">
@@ -32488,7 +32485,7 @@
         <v>1754</v>
       </c>
       <c r="B344" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="C344" t="s">
         <v>47</v>
@@ -32509,7 +32506,7 @@
         <v>2</v>
       </c>
       <c r="O344">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P344">
         <v>1</v>
@@ -32542,16 +32539,16 @@
         <v>54</v>
       </c>
       <c r="AO344" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="AP344" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="AQ344">
         <v>4</v>
       </c>
       <c r="AS344" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="345" spans="1:45" x14ac:dyDescent="0.25">
@@ -32559,7 +32556,7 @@
         <v>1754</v>
       </c>
       <c r="B345" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C345" t="s">
         <v>47</v>
@@ -32607,7 +32604,7 @@
         <v>48</v>
       </c>
       <c r="AD345" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="AG345" t="s">
         <v>1190</v>
@@ -32622,19 +32619,19 @@
         <v>54</v>
       </c>
       <c r="AN345" t="s">
+        <v>1793</v>
+      </c>
+      <c r="AO345" t="s">
         <v>1794</v>
       </c>
-      <c r="AO345" t="s">
+      <c r="AP345" t="s">
         <v>1795</v>
-      </c>
-      <c r="AP345" t="s">
-        <v>1796</v>
       </c>
       <c r="AQ345">
         <v>4</v>
       </c>
       <c r="AS345" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="346" spans="1:45" x14ac:dyDescent="0.25">
@@ -32642,7 +32639,7 @@
         <v>1754</v>
       </c>
       <c r="B346" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="C346" t="s">
         <v>47</v>
@@ -32690,7 +32687,7 @@
         <v>48</v>
       </c>
       <c r="AD346" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="AF346" t="s">
         <v>1190</v>
@@ -32705,16 +32702,16 @@
         <v>54</v>
       </c>
       <c r="AO346" t="s">
+        <v>1798</v>
+      </c>
+      <c r="AP346" t="s">
         <v>1799</v>
-      </c>
-      <c r="AP346" t="s">
-        <v>1800</v>
       </c>
       <c r="AQ346">
         <v>4</v>
       </c>
       <c r="AS346" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="347" spans="1:45" x14ac:dyDescent="0.25">
@@ -32722,7 +32719,7 @@
         <v>1754</v>
       </c>
       <c r="B347" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="C347" t="s">
         <v>47</v>
@@ -32770,7 +32767,7 @@
         <v>48</v>
       </c>
       <c r="AD347" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="AG347" t="s">
         <v>1190</v>
@@ -32785,16 +32782,16 @@
         <v>54</v>
       </c>
       <c r="AO347" t="s">
+        <v>1801</v>
+      </c>
+      <c r="AP347" t="s">
         <v>1802</v>
-      </c>
-      <c r="AP347" t="s">
-        <v>1803</v>
       </c>
       <c r="AQ347">
         <v>4</v>
       </c>
       <c r="AS347" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="348" spans="1:45" x14ac:dyDescent="0.25">
@@ -32802,7 +32799,7 @@
         <v>1754</v>
       </c>
       <c r="B348" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C348" t="s">
         <v>47</v>
@@ -32850,7 +32847,7 @@
         <v>48</v>
       </c>
       <c r="AD348" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="AF348" t="s">
         <v>1190</v>
@@ -32865,19 +32862,19 @@
         <v>54</v>
       </c>
       <c r="AN348" t="s">
+        <v>1804</v>
+      </c>
+      <c r="AO348" t="s">
         <v>1805</v>
       </c>
-      <c r="AO348" t="s">
+      <c r="AP348" t="s">
         <v>1806</v>
-      </c>
-      <c r="AP348" t="s">
-        <v>1807</v>
       </c>
       <c r="AQ348">
         <v>4</v>
       </c>
       <c r="AS348" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="349" spans="1:45" x14ac:dyDescent="0.25">
@@ -32885,7 +32882,7 @@
         <v>1754</v>
       </c>
       <c r="B349" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="C349" t="s">
         <v>205</v>
@@ -32915,7 +32912,7 @@
         <v>24</v>
       </c>
       <c r="Y349" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="AF349" t="s">
         <v>362</v>
@@ -32927,16 +32924,16 @@
         <v>54</v>
       </c>
       <c r="AN349" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AO349" t="s">
         <v>1810</v>
       </c>
-      <c r="AO349" t="s">
+      <c r="AP349" t="s">
         <v>1811</v>
       </c>
-      <c r="AP349" t="s">
+      <c r="AS349" t="s">
         <v>1812</v>
-      </c>
-      <c r="AS349" t="s">
-        <v>1813</v>
       </c>
     </row>
     <row r="350" spans="1:45" x14ac:dyDescent="0.25">
@@ -32944,7 +32941,7 @@
         <v>1754</v>
       </c>
       <c r="B350" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C350" t="s">
         <v>297</v>
@@ -33007,16 +33004,16 @@
         <v>54</v>
       </c>
       <c r="AN350" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AO350" t="s">
         <v>1815</v>
       </c>
-      <c r="AO350" t="s">
+      <c r="AP350" t="s">
         <v>1816</v>
       </c>
-      <c r="AP350" t="s">
+      <c r="AS350" t="s">
         <v>1817</v>
-      </c>
-      <c r="AS350" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="351" spans="1:45" x14ac:dyDescent="0.25">
@@ -33024,7 +33021,7 @@
         <v>1754</v>
       </c>
       <c r="B351" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C351" t="s">
         <v>297</v>
@@ -33084,16 +33081,16 @@
         <v>54</v>
       </c>
       <c r="AN351" t="s">
+        <v>1814</v>
+      </c>
+      <c r="AO351" t="s">
         <v>1815</v>
       </c>
-      <c r="AO351" t="s">
-        <v>1816</v>
-      </c>
       <c r="AP351" t="s">
+        <v>1819</v>
+      </c>
+      <c r="AS351" t="s">
         <v>1820</v>
-      </c>
-      <c r="AS351" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="352" spans="1:45" x14ac:dyDescent="0.25">
@@ -33101,7 +33098,7 @@
         <v>1754</v>
       </c>
       <c r="B352" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="C352" t="s">
         <v>271</v>
@@ -33137,7 +33134,7 @@
         <v>32</v>
       </c>
       <c r="Y352" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="AB352" t="s">
         <v>73</v>
@@ -33155,7 +33152,7 @@
         <v>1366</v>
       </c>
       <c r="AI352" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="AK352" t="s">
         <v>266</v>
@@ -33164,16 +33161,16 @@
         <v>54</v>
       </c>
       <c r="AN352" t="s">
+        <v>1824</v>
+      </c>
+      <c r="AO352" t="s">
         <v>1825</v>
       </c>
-      <c r="AO352" t="s">
+      <c r="AP352" t="s">
         <v>1826</v>
       </c>
-      <c r="AP352" t="s">
+      <c r="AS352" t="s">
         <v>1827</v>
-      </c>
-      <c r="AS352" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="353" spans="1:45" x14ac:dyDescent="0.25">
@@ -33181,7 +33178,7 @@
         <v>1754</v>
       </c>
       <c r="B353" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="C353" t="s">
         <v>271</v>
@@ -33214,7 +33211,7 @@
         <v>32</v>
       </c>
       <c r="Y353" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="Z353" t="s">
         <v>272</v>
@@ -33244,16 +33241,16 @@
         <v>54</v>
       </c>
       <c r="AN353" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AO353" t="s">
         <v>1831</v>
       </c>
-      <c r="AO353" t="s">
+      <c r="AP353" t="s">
         <v>1832</v>
       </c>
-      <c r="AP353" t="s">
+      <c r="AS353" t="s">
         <v>1833</v>
-      </c>
-      <c r="AS353" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="354" spans="1:45" x14ac:dyDescent="0.25">
@@ -33261,7 +33258,7 @@
         <v>1754</v>
       </c>
       <c r="B354" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="C354" t="s">
         <v>271</v>
@@ -33297,7 +33294,7 @@
         <v>32</v>
       </c>
       <c r="Y354" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="AB354" t="s">
         <v>73</v>
@@ -33315,7 +33312,7 @@
         <v>1366</v>
       </c>
       <c r="AI354" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="AK354" t="s">
         <v>266</v>
@@ -33324,16 +33321,16 @@
         <v>54</v>
       </c>
       <c r="AN354" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="AO354" t="s">
+        <v>1835</v>
+      </c>
+      <c r="AP354" t="s">
         <v>1836</v>
       </c>
-      <c r="AP354" t="s">
+      <c r="AS354" t="s">
         <v>1837</v>
-      </c>
-      <c r="AS354" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="355" spans="1:45" x14ac:dyDescent="0.25">
@@ -33341,7 +33338,7 @@
         <v>1754</v>
       </c>
       <c r="B355" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="C355" t="s">
         <v>271</v>
@@ -33377,7 +33374,7 @@
         <v>32</v>
       </c>
       <c r="Y355" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="Z355" t="s">
         <v>272</v>
@@ -33389,7 +33386,7 @@
         <v>73</v>
       </c>
       <c r="AC355" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="AD355">
         <v>54</v>
@@ -33410,16 +33407,16 @@
         <v>54</v>
       </c>
       <c r="AN355" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="AO355" t="s">
+        <v>1840</v>
+      </c>
+      <c r="AP355" t="s">
         <v>1841</v>
       </c>
-      <c r="AP355" t="s">
+      <c r="AS355" t="s">
         <v>1842</v>
-      </c>
-      <c r="AS355" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="356" spans="1:45" x14ac:dyDescent="0.25">
@@ -33427,7 +33424,7 @@
         <v>1754</v>
       </c>
       <c r="B356" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="C356" t="s">
         <v>257</v>
@@ -33463,7 +33460,7 @@
         <v>32</v>
       </c>
       <c r="Y356" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="AB356" t="s">
         <v>73</v>
@@ -33481,7 +33478,7 @@
         <v>1366</v>
       </c>
       <c r="AI356" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="AK356" t="s">
         <v>266</v>
@@ -33490,16 +33487,16 @@
         <v>54</v>
       </c>
       <c r="AN356" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="AO356" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AP356" t="s">
         <v>1845</v>
       </c>
-      <c r="AP356" t="s">
+      <c r="AS356" t="s">
         <v>1846</v>
-      </c>
-      <c r="AS356" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="357" spans="1:42" x14ac:dyDescent="0.25">
@@ -33507,7 +33504,7 @@
         <v>1754</v>
       </c>
       <c r="B357" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="C357" t="s">
         <v>381</v>
@@ -33558,13 +33555,13 @@
         <v>54</v>
       </c>
       <c r="AN357" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AO357" t="s">
         <v>1849</v>
       </c>
-      <c r="AO357" t="s">
+      <c r="AP357" t="s">
         <v>1850</v>
-      </c>
-      <c r="AP357" t="s">
-        <v>1851</v>
       </c>
     </row>
     <row r="358" spans="1:42" x14ac:dyDescent="0.25">
@@ -33572,7 +33569,7 @@
         <v>1754</v>
       </c>
       <c r="B358" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="C358" t="s">
         <v>381</v>
@@ -33617,18 +33614,18 @@
         <v>54</v>
       </c>
       <c r="AO358" t="s">
+        <v>1852</v>
+      </c>
+      <c r="AP358" t="s">
         <v>1853</v>
-      </c>
-      <c r="AP358" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="359" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B359" t="s">
         <v>1855</v>
-      </c>
-      <c r="B359" t="s">
-        <v>1856</v>
       </c>
       <c r="C359" t="s">
         <v>297</v>
@@ -33673,10 +33670,10 @@
         <v>48</v>
       </c>
       <c r="AD359" t="s">
+        <v>1856</v>
+      </c>
+      <c r="AK359" t="s">
         <v>1857</v>
-      </c>
-      <c r="AK359" t="s">
-        <v>1858</v>
       </c>
       <c r="AM359" t="s">
         <v>260</v>
@@ -33685,18 +33682,18 @@
         <v>742</v>
       </c>
       <c r="AP359" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AS359" t="s">
         <v>1859</v>
-      </c>
-      <c r="AS359" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="360" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B360" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="C360" t="s">
         <v>297</v>
@@ -33738,7 +33735,7 @@
         <v>48</v>
       </c>
       <c r="AD360" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="AK360">
         <v>-120</v>
@@ -33747,21 +33744,21 @@
         <v>763</v>
       </c>
       <c r="AO360" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="AP360" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AS360" t="s">
         <v>1859</v>
-      </c>
-      <c r="AS360" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="361" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B361" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="C361" t="s">
         <v>297</v>
@@ -33803,30 +33800,30 @@
         <v>48</v>
       </c>
       <c r="AD361" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="AK361" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="AM361" t="s">
         <v>260</v>
       </c>
       <c r="AO361" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="AP361" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AS361" t="s">
         <v>1859</v>
-      </c>
-      <c r="AS361" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="362" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B362" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="C362" t="s">
         <v>47</v>
@@ -33874,7 +33871,7 @@
         <v>73</v>
       </c>
       <c r="AD362" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="AK362" t="s">
         <v>266</v>
@@ -33883,24 +33880,24 @@
         <v>54</v>
       </c>
       <c r="AO362" t="s">
+        <v>1867</v>
+      </c>
+      <c r="AP362" t="s">
         <v>1868</v>
-      </c>
-      <c r="AP362" t="s">
-        <v>1869</v>
       </c>
       <c r="AQ362">
         <v>4</v>
       </c>
       <c r="AS362" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="363" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B363" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="C363" t="s">
         <v>47</v>
@@ -33957,24 +33954,24 @@
         <v>282</v>
       </c>
       <c r="AO363" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AP363" t="s">
         <v>1872</v>
-      </c>
-      <c r="AP363" t="s">
-        <v>1873</v>
       </c>
       <c r="AQ363">
         <v>4</v>
       </c>
       <c r="AS363" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="364" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B364" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="C364" t="s">
         <v>47</v>
@@ -34022,33 +34019,33 @@
         <v>48</v>
       </c>
       <c r="AD364" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="AK364">
         <v>-128</v>
       </c>
       <c r="AM364" t="s">
+        <v>1875</v>
+      </c>
+      <c r="AO364" t="s">
         <v>1876</v>
       </c>
-      <c r="AO364" t="s">
+      <c r="AP364" t="s">
         <v>1877</v>
-      </c>
-      <c r="AP364" t="s">
-        <v>1878</v>
       </c>
       <c r="AQ364">
         <v>4</v>
       </c>
       <c r="AS364" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="365" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B365" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="C365" t="s">
         <v>47</v>
@@ -34099,27 +34096,27 @@
         <v>48</v>
       </c>
       <c r="AK365" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="AM365" t="s">
         <v>260</v>
       </c>
       <c r="AO365" t="s">
+        <v>1880</v>
+      </c>
+      <c r="AP365" t="s">
         <v>1881</v>
       </c>
-      <c r="AP365" t="s">
+      <c r="AS365" t="s">
         <v>1882</v>
-      </c>
-      <c r="AS365" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="366" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B366" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="C366" t="s">
         <v>47</v>
@@ -34164,30 +34161,30 @@
         <v>73</v>
       </c>
       <c r="AD366" t="s">
+        <v>1884</v>
+      </c>
+      <c r="AK366" t="s">
         <v>1885</v>
-      </c>
-      <c r="AK366" t="s">
-        <v>1886</v>
       </c>
       <c r="AM366" t="s">
         <v>291</v>
       </c>
       <c r="AO366" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AP366" t="s">
         <v>1887</v>
       </c>
-      <c r="AP366" t="s">
+      <c r="AS366" t="s">
         <v>1888</v>
-      </c>
-      <c r="AS366" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="367" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B367" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="C367" t="s">
         <v>47</v>
@@ -34232,30 +34229,30 @@
         <v>48</v>
       </c>
       <c r="AD367" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="AK367">
         <v>-128</v>
       </c>
       <c r="AM367" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="AO367" t="s">
+        <v>1890</v>
+      </c>
+      <c r="AP367" t="s">
         <v>1891</v>
       </c>
-      <c r="AP367" t="s">
+      <c r="AS367" t="s">
         <v>1892</v>
-      </c>
-      <c r="AS367" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="368" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B368" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C368" t="s">
         <v>47</v>
@@ -34309,21 +34306,21 @@
         <v>763</v>
       </c>
       <c r="AO368" t="s">
+        <v>1894</v>
+      </c>
+      <c r="AP368" t="s">
         <v>1895</v>
       </c>
-      <c r="AP368" t="s">
+      <c r="AS368" t="s">
         <v>1896</v>
-      </c>
-      <c r="AS368" t="s">
-        <v>1897</v>
       </c>
     </row>
     <row r="369" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B369" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="C369" t="s">
         <v>381</v>
@@ -34347,21 +34344,21 @@
         <v>54</v>
       </c>
       <c r="AN369" t="s">
+        <v>1898</v>
+      </c>
+      <c r="AO369" t="s">
         <v>1899</v>
       </c>
-      <c r="AO369" t="s">
+      <c r="AP369" t="s">
         <v>1900</v>
-      </c>
-      <c r="AP369" t="s">
-        <v>1901</v>
       </c>
     </row>
     <row r="370" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B370" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="C370" t="s">
         <v>381</v>
@@ -34397,18 +34394,18 @@
         <v>260</v>
       </c>
       <c r="AO370" t="s">
+        <v>1902</v>
+      </c>
+      <c r="AP370" t="s">
         <v>1903</v>
-      </c>
-      <c r="AP370" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="371" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B371" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="C371" t="s">
         <v>381</v>
@@ -34441,7 +34438,7 @@
         <v>48</v>
       </c>
       <c r="AD371" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="AK371">
         <v>-125</v>
@@ -34450,21 +34447,21 @@
         <v>763</v>
       </c>
       <c r="AO371" t="s">
+        <v>1906</v>
+      </c>
+      <c r="AP371" t="s">
         <v>1907</v>
       </c>
-      <c r="AP371" t="s">
+      <c r="AS371" t="s">
         <v>1908</v>
-      </c>
-      <c r="AS371" t="s">
-        <v>1909</v>
       </c>
     </row>
     <row r="372" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B372" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="C372" t="s">
         <v>381</v>
@@ -34503,27 +34500,27 @@
         <v>70</v>
       </c>
       <c r="AK372" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="AM372" t="s">
         <v>54</v>
       </c>
       <c r="AO372" t="s">
+        <v>1911</v>
+      </c>
+      <c r="AP372" t="s">
         <v>1912</v>
       </c>
-      <c r="AP372" t="s">
+      <c r="AS372" t="s">
         <v>1913</v>
-      </c>
-      <c r="AS372" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="373" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B373" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C373" t="s">
         <v>297</v>
@@ -34565,7 +34562,7 @@
         <v>48</v>
       </c>
       <c r="AD373" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="AK373">
         <v>-119.5</v>
@@ -34577,24 +34574,24 @@
         <v>1429</v>
       </c>
       <c r="AO373" t="s">
+        <v>1916</v>
+      </c>
+      <c r="AP373" t="s">
         <v>1917</v>
       </c>
-      <c r="AP373" t="s">
+      <c r="AR373">
+        <v>2</v>
+      </c>
+      <c r="AS373" t="s">
         <v>1918</v>
-      </c>
-      <c r="AR373">
-        <v>2</v>
-      </c>
-      <c r="AS373" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="374" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B374" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="C374" t="s">
         <v>297</v>
@@ -34648,7 +34645,7 @@
         <v>48</v>
       </c>
       <c r="AD374" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="AK374">
         <v>-119.5</v>
@@ -34660,24 +34657,24 @@
         <v>1429</v>
       </c>
       <c r="AO374" t="s">
+        <v>1920</v>
+      </c>
+      <c r="AP374" t="s">
         <v>1921</v>
       </c>
-      <c r="AP374" t="s">
+      <c r="AR374">
+        <v>2</v>
+      </c>
+      <c r="AS374" t="s">
         <v>1922</v>
-      </c>
-      <c r="AR374">
-        <v>2</v>
-      </c>
-      <c r="AS374" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="375" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B375" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C375" t="s">
         <v>297</v>
@@ -34728,13 +34725,13 @@
         <v>282</v>
       </c>
       <c r="AO375" t="s">
+        <v>1924</v>
+      </c>
+      <c r="AP375" t="s">
         <v>1925</v>
       </c>
-      <c r="AP375" t="s">
+      <c r="AS375" t="s">
         <v>1926</v>
-      </c>
-      <c r="AS375" t="s">
-        <v>1927</v>
       </c>
     </row>
   </sheetData>
@@ -34756,7 +34753,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -34809,7 +34806,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B8">
         <v>216</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -488,7 +488,7 @@
     <t>-6 to +63</t>
   </si>
   <si>
-    <t>Compact broadcast mixer: 4 mono mic/line channels (XLR mic or 1/4" TRS line, separate gain ranges: mic -6 to +63 dB, line -10 to +26 dB) + 2 telco channels (XLR in, clean-feed XLR out) + 4 stereo channels (7 stereo sources incl. USB return ST6); 3-band EQ on mono channels; fader-start/remote logic I/O; Audition bus; Mix B bus; stereo USB audio CODEC (bi-directional); main program outputs on XLR; RCA outputs counted: Mix B L/R, CRM speakers L/R, Audition L/R, mono PGM; separate aux output (1/4" TRS); EX MON stereo RCA input; 3 headphone outputs (operator + 2 guest) with talk button; inputs counted: ST1/ST5/ST7 on 1/4" jacks, ST2 and EX MON on RCA; connector type of ST3/ST4 not published</t>
+    <t>Compact broadcast mixer: 4 mono mic/line channels (XLR mic or 1/4" TRS line, separate gain ranges: mic -6 to +63 dB, line -10 to +26 dB) + 2 telco channels (XLR in, clean-feed XLR out) + 4 stereo channels (7 stereo sources incl. USB return ST6); 3-band EQ on mono channels; fader-start/remote logic I/O; Audition bus; Mix B bus; stereo USB audio CODEC (bi-directional); main program outputs on XLR; RCA outputs counted: Mix B L/R, CRM speakers L/R, Audition L/R, mono PGM; separate aux output (1/4" TRS); EX MON stereo RCA input; 3 headphone outputs (operator + 2 guest) with talk button; inputs counted: ST1/ST3/ST5/ST7 on 1/4" jacks, ST2/ST4 and EX MON on RCA</t>
   </si>
   <si>
     <t>https://www.allen-heath.com/hardware/xb-series/xb-142/</t>
@@ -7850,7 +7850,7 @@
         <v>4</v>
       </c>
       <c r="G22">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -7877,7 +7877,7 @@
         <v>157</v>
       </c>
       <c r="AQ22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR22">
         <v>7</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5299" uniqueCount="1929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5269" uniqueCount="1918">
   <si>
     <t>Brand</t>
   </si>
@@ -4839,39 +4839,6 @@
   </si>
   <si>
     <t>[Manufacturer](https://tascam.com/us/product/model_2400)</t>
-  </si>
-  <si>
-    <t>SERIES 102i</t>
-  </si>
-  <si>
-    <t>-95.9dB (0.0016%)</t>
-  </si>
-  <si>
-    <t>-97.1dB (0.0014%)</t>
-  </si>
-  <si>
-    <t>Steinberg Cubase LE/Cubasis LE, IK Multimedia AmpliTube, iZotope Neutron Elements, IK Multimedia T-RackS</t>
-  </si>
-  <si>
-    <t>10-in/2-out desktop USB interface; 2 combo inputs switchable mic/line/instrument; 1 S/MUX optical expansion port (8ch @48kHz, up to 10 total inputs); UAC2.0 compliant, dual headphone amps</t>
-  </si>
-  <si>
-    <t>https://tascam.com/us/product/series_102i</t>
-  </si>
-  <si>
-    <t>[ASR](https://www.audiosciencereview.com/forum/index.php?threads/tascam-102i-review-audio-interface.24832/) / [Manufacturer](https://tascam.com/us/product/series_102i/spec)</t>
-  </si>
-  <si>
-    <t>SERIES 208i</t>
-  </si>
-  <si>
-    <t>20-in/8-out desktop USB interface; 4 combo inputs switchable mic/line/instrument; 2 S/MUX optical expansion ports (16ch total @48kHz, up to 20 total inputs); word clock BNC in/out; 8-bus mixer DSP, dual headphone amps</t>
-  </si>
-  <si>
-    <t>https://tascam.com/us/product/series_208i</t>
-  </si>
-  <si>
-    <t>[AV Watch](https://av.watch.impress.co.jp/docs/series/dal/1226048.html) / [Manufacturer](https://tascam.com/us/product/series_208i/spec)</t>
   </si>
   <si>
     <t>Sonicview 16XP</t>
@@ -6174,7 +6141,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AS375"/>
+  <dimension ref="A1:AS373"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -7836,7 +7803,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -9903,7 +9870,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>279</v>
       </c>
@@ -12314,7 +12281,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>472</v>
       </c>
@@ -12812,7 +12779,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>509</v>
       </c>
@@ -12939,7 +12906,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>509</v>
       </c>
@@ -12995,7 +12962,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>509</v>
       </c>
@@ -15097,7 +15064,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>659</v>
       </c>
@@ -15162,7 +15129,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>659</v>
       </c>
@@ -15733,7 +15700,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="126" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>685</v>
       </c>
@@ -16073,7 +16040,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>685</v>
       </c>
@@ -16277,7 +16244,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>738</v>
       </c>
@@ -18296,7 +18263,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>879</v>
       </c>
@@ -18831,7 +18798,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>884</v>
       </c>
@@ -18878,7 +18845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>884</v>
       </c>
@@ -20875,7 +20842,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1044</v>
       </c>
@@ -22222,7 +22189,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1138</v>
       </c>
@@ -22477,7 +22444,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1158</v>
       </c>
@@ -23017,7 +22984,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1158</v>
       </c>
@@ -23088,7 +23055,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1158</v>
       </c>
@@ -25465,7 +25432,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="252" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1347</v>
       </c>
@@ -26432,7 +26399,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="263" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1353</v>
       </c>
@@ -27094,7 +27061,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="273" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1469</v>
       </c>
@@ -27153,7 +27120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1469</v>
       </c>
@@ -27212,7 +27179,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="275" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1469</v>
       </c>
@@ -27277,7 +27244,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="276" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1469</v>
       </c>
@@ -27336,7 +27303,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1469</v>
       </c>
@@ -27383,7 +27350,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="278" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1469</v>
       </c>
@@ -27439,7 +27406,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="279" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1469</v>
       </c>
@@ -28650,7 +28617,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="295" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1536</v>
       </c>
@@ -29155,23 +29122,20 @@
         <v>1607</v>
       </c>
       <c r="C302" t="s">
-        <v>271</v>
+        <v>47</v>
       </c>
       <c r="E302">
-        <v>2</v>
-      </c>
-      <c r="F302">
-        <v>2</v>
-      </c>
-      <c r="I302">
-        <v>8</v>
-      </c>
-      <c r="J302">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="G302">
+        <v>24</v>
       </c>
       <c r="N302">
         <v>2</v>
       </c>
+      <c r="O302">
+        <v>16</v>
+      </c>
       <c r="P302">
         <v>2</v>
       </c>
@@ -29179,55 +29143,43 @@
         <v>48</v>
       </c>
       <c r="W302">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="X302">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y302" t="s">
         <v>49</v>
       </c>
-      <c r="Z302" t="s">
-        <v>48</v>
-      </c>
       <c r="AB302" t="s">
         <v>73</v>
       </c>
       <c r="AC302" t="s">
         <v>48</v>
       </c>
-      <c r="AD302">
-        <v>58</v>
-      </c>
-      <c r="AE302">
-        <v>109</v>
-      </c>
-      <c r="AF302">
-        <v>110</v>
-      </c>
-      <c r="AH302" t="s">
+      <c r="AG302">
+        <v>108</v>
+      </c>
+      <c r="AJ302" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL302">
+        <v>-128</v>
+      </c>
+      <c r="AM302" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO302" t="s">
         <v>1608</v>
       </c>
-      <c r="AI302" t="s">
+      <c r="AP302" t="s">
         <v>1609</v>
       </c>
-      <c r="AL302">
-        <v>-129</v>
-      </c>
-      <c r="AM302" t="s">
-        <v>282</v>
-      </c>
-      <c r="AN302" t="s">
+      <c r="AQ302">
+        <v>4</v>
+      </c>
+      <c r="AS302" t="s">
         <v>1610</v>
-      </c>
-      <c r="AO302" t="s">
-        <v>1611</v>
-      </c>
-      <c r="AP302" t="s">
-        <v>1612</v>
-      </c>
-      <c r="AS302" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="303" spans="1:45" x14ac:dyDescent="0.25">
@@ -29235,29 +29187,23 @@
         <v>1576</v>
       </c>
       <c r="B303" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="C303" t="s">
-        <v>257</v>
+        <v>47</v>
       </c>
       <c r="E303">
-        <v>4</v>
-      </c>
-      <c r="F303">
-        <v>4</v>
-      </c>
-      <c r="I303">
+        <v>24</v>
+      </c>
+      <c r="G303">
+        <v>32</v>
+      </c>
+      <c r="N303">
+        <v>2</v>
+      </c>
+      <c r="O303">
         <v>16</v>
       </c>
-      <c r="J303">
-        <v>2</v>
-      </c>
-      <c r="N303">
-        <v>2</v>
-      </c>
-      <c r="O303">
-        <v>6</v>
-      </c>
       <c r="P303">
         <v>2</v>
       </c>
@@ -29265,55 +29211,43 @@
         <v>48</v>
       </c>
       <c r="W303">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="X303">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y303" t="s">
         <v>49</v>
       </c>
-      <c r="Z303" t="s">
-        <v>48</v>
-      </c>
       <c r="AB303" t="s">
         <v>73</v>
       </c>
       <c r="AC303" t="s">
         <v>48</v>
       </c>
-      <c r="AD303">
-        <v>58</v>
-      </c>
-      <c r="AE303">
-        <v>109</v>
-      </c>
-      <c r="AF303">
-        <v>110</v>
-      </c>
-      <c r="AH303" t="s">
-        <v>1608</v>
-      </c>
-      <c r="AI303" t="s">
-        <v>1609</v>
+      <c r="AG303">
+        <v>108</v>
+      </c>
+      <c r="AJ303" t="s">
+        <v>53</v>
       </c>
       <c r="AL303">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="AM303" t="s">
-        <v>282</v>
-      </c>
-      <c r="AN303" t="s">
-        <v>1610</v>
+        <v>54</v>
       </c>
       <c r="AO303" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="AP303" t="s">
-        <v>1616</v>
+        <v>1613</v>
+      </c>
+      <c r="AQ303">
+        <v>4</v>
       </c>
       <c r="AS303" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="304" spans="1:45" x14ac:dyDescent="0.25">
@@ -29321,67 +29255,55 @@
         <v>1576</v>
       </c>
       <c r="B304" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="C304" t="s">
-        <v>47</v>
-      </c>
-      <c r="E304">
-        <v>16</v>
+        <v>257</v>
+      </c>
+      <c r="D304">
+        <v>999</v>
       </c>
       <c r="G304">
         <v>24</v>
       </c>
-      <c r="N304">
-        <v>2</v>
-      </c>
       <c r="O304">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P304">
-        <v>2</v>
-      </c>
-      <c r="V304" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="W304">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="X304">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y304" t="s">
         <v>49</v>
       </c>
-      <c r="AB304" t="s">
-        <v>73</v>
+      <c r="Z304" t="s">
+        <v>272</v>
       </c>
       <c r="AC304" t="s">
         <v>48</v>
       </c>
-      <c r="AG304">
-        <v>108</v>
+      <c r="AG304" t="s">
+        <v>923</v>
       </c>
       <c r="AJ304" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL304">
-        <v>-128</v>
+        <v>161</v>
       </c>
       <c r="AM304" t="s">
-        <v>54</v>
+        <v>291</v>
       </c>
       <c r="AO304" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="AP304" t="s">
-        <v>1620</v>
-      </c>
-      <c r="AQ304">
-        <v>4</v>
+        <v>1617</v>
       </c>
       <c r="AS304" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="305" spans="1:45" x14ac:dyDescent="0.25">
@@ -29389,25 +29311,28 @@
         <v>1576</v>
       </c>
       <c r="B305" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="C305" t="s">
-        <v>47</v>
+        <v>271</v>
+      </c>
+      <c r="D305">
+        <v>299</v>
       </c>
       <c r="E305">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G305">
-        <v>32</v>
-      </c>
-      <c r="N305">
+        <v>8</v>
+      </c>
+      <c r="H305">
         <v>2</v>
       </c>
       <c r="O305">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V305" t="s">
         <v>48</v>
@@ -29416,40 +29341,40 @@
         <v>96</v>
       </c>
       <c r="X305">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y305" t="s">
         <v>49</v>
       </c>
+      <c r="Z305" t="s">
+        <v>25</v>
+      </c>
       <c r="AB305" t="s">
         <v>73</v>
       </c>
       <c r="AC305" t="s">
         <v>48</v>
       </c>
-      <c r="AG305">
-        <v>108</v>
+      <c r="AD305">
+        <v>56</v>
       </c>
       <c r="AJ305" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL305">
-        <v>-128</v>
+        <v>1259</v>
+      </c>
+      <c r="AK305">
+        <v>-125</v>
       </c>
       <c r="AM305" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
       <c r="AO305" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="AP305" t="s">
-        <v>1624</v>
-      </c>
-      <c r="AQ305">
-        <v>4</v>
+        <v>1621</v>
       </c>
       <c r="AS305" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="306" spans="1:45" x14ac:dyDescent="0.25">
@@ -29457,25 +29382,34 @@
         <v>1576</v>
       </c>
       <c r="B306" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="C306" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="D306">
-        <v>999</v>
-      </c>
-      <c r="G306">
-        <v>24</v>
-      </c>
-      <c r="O306">
-        <v>24</v>
+        <v>119</v>
+      </c>
+      <c r="E306">
+        <v>2</v>
+      </c>
+      <c r="F306">
+        <v>2</v>
+      </c>
+      <c r="H306">
+        <v>2</v>
+      </c>
+      <c r="N306">
+        <v>2</v>
       </c>
       <c r="P306">
         <v>1</v>
       </c>
+      <c r="V306" t="s">
+        <v>48</v>
+      </c>
       <c r="W306">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="X306">
         <v>24</v>
@@ -29484,28 +29418,40 @@
         <v>49</v>
       </c>
       <c r="Z306" t="s">
-        <v>272</v>
+        <v>48</v>
+      </c>
+      <c r="AA306" t="s">
+        <v>48</v>
       </c>
       <c r="AC306" t="s">
         <v>48</v>
       </c>
-      <c r="AG306" t="s">
-        <v>923</v>
-      </c>
-      <c r="AJ306" t="s">
-        <v>161</v>
+      <c r="AD306" t="s">
+        <v>368</v>
+      </c>
+      <c r="AH306" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AI306" t="s">
+        <v>446</v>
+      </c>
+      <c r="AL306" t="s">
+        <v>266</v>
       </c>
       <c r="AM306" t="s">
-        <v>291</v>
+        <v>282</v>
+      </c>
+      <c r="AN306" t="s">
+        <v>1625</v>
       </c>
       <c r="AO306" t="s">
+        <v>1626</v>
+      </c>
+      <c r="AP306" t="s">
         <v>1627</v>
       </c>
-      <c r="AP306" t="s">
+      <c r="AS306" t="s">
         <v>1628</v>
-      </c>
-      <c r="AS306" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="307" spans="1:45" x14ac:dyDescent="0.25">
@@ -29513,34 +29459,37 @@
         <v>1576</v>
       </c>
       <c r="B307" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C307" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="D307">
-        <v>299</v>
+        <v>199</v>
       </c>
       <c r="E307">
-        <v>8</v>
-      </c>
-      <c r="G307">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="F307">
+        <v>4</v>
       </c>
       <c r="H307">
         <v>2</v>
       </c>
+      <c r="N307">
+        <v>2</v>
+      </c>
       <c r="O307">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V307" t="s">
         <v>48</v>
       </c>
       <c r="W307">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="X307">
         <v>24</v>
@@ -29549,57 +29498,69 @@
         <v>49</v>
       </c>
       <c r="Z307" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB307" t="s">
-        <v>73</v>
+        <v>48</v>
+      </c>
+      <c r="AA307" t="s">
+        <v>48</v>
       </c>
       <c r="AC307" t="s">
         <v>48</v>
       </c>
-      <c r="AD307">
-        <v>56</v>
-      </c>
-      <c r="AJ307" t="s">
-        <v>1259</v>
-      </c>
-      <c r="AK307">
-        <v>-125</v>
+      <c r="AD307" t="s">
+        <v>368</v>
+      </c>
+      <c r="AF307" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG307" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH307" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AI307" t="s">
+        <v>446</v>
+      </c>
+      <c r="AL307" t="s">
+        <v>266</v>
       </c>
       <c r="AM307" t="s">
-        <v>282</v>
+        <v>54</v>
+      </c>
+      <c r="AN307" t="s">
+        <v>1625</v>
       </c>
       <c r="AO307" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AP307" t="s">
         <v>1631</v>
       </c>
-      <c r="AP307" t="s">
+      <c r="AS307" t="s">
         <v>1632</v>
-      </c>
-      <c r="AS307" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="308" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1576</v>
+        <v>1633</v>
       </c>
       <c r="B308" t="s">
         <v>1634</v>
       </c>
       <c r="C308" t="s">
-        <v>297</v>
+        <v>381</v>
       </c>
       <c r="D308">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="E308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N308">
         <v>2</v>
@@ -29619,61 +29580,61 @@
       <c r="Y308" t="s">
         <v>49</v>
       </c>
-      <c r="Z308" t="s">
-        <v>48</v>
-      </c>
       <c r="AA308" t="s">
         <v>48</v>
       </c>
       <c r="AC308" t="s">
         <v>48</v>
       </c>
-      <c r="AD308" t="s">
-        <v>368</v>
+      <c r="AD308">
+        <v>58</v>
+      </c>
+      <c r="AE308">
+        <v>118</v>
+      </c>
+      <c r="AF308">
+        <v>115</v>
       </c>
       <c r="AH308" t="s">
+        <v>289</v>
+      </c>
+      <c r="AI308" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK308">
+        <v>-130.5</v>
+      </c>
+      <c r="AM308" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO308" t="s">
         <v>1635</v>
       </c>
-      <c r="AI308" t="s">
-        <v>446</v>
-      </c>
-      <c r="AL308" t="s">
-        <v>266</v>
-      </c>
-      <c r="AM308" t="s">
-        <v>282</v>
-      </c>
-      <c r="AN308" t="s">
+      <c r="AP308" t="s">
         <v>1636</v>
       </c>
-      <c r="AO308" t="s">
+      <c r="AS308" t="s">
         <v>1637</v>
-      </c>
-      <c r="AP308" t="s">
-        <v>1638</v>
-      </c>
-      <c r="AS308" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="309" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1576</v>
+        <v>1633</v>
       </c>
       <c r="B309" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="C309" t="s">
         <v>297</v>
       </c>
       <c r="D309">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="E309">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F309">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H309">
         <v>2</v>
@@ -29681,11 +29642,8 @@
       <c r="N309">
         <v>2</v>
       </c>
-      <c r="O309">
-        <v>2</v>
-      </c>
       <c r="P309">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V309" t="s">
         <v>48</v>
@@ -29699,75 +29657,75 @@
       <c r="Y309" t="s">
         <v>49</v>
       </c>
-      <c r="Z309" t="s">
-        <v>48</v>
-      </c>
       <c r="AA309" t="s">
         <v>48</v>
       </c>
       <c r="AC309" t="s">
         <v>48</v>
       </c>
-      <c r="AD309" t="s">
-        <v>368</v>
-      </c>
-      <c r="AF309" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG309" t="s">
-        <v>52</v>
+      <c r="AD309">
+        <v>58</v>
+      </c>
+      <c r="AE309">
+        <v>115</v>
+      </c>
+      <c r="AF309">
+        <v>115</v>
       </c>
       <c r="AH309" t="s">
-        <v>1635</v>
+        <v>289</v>
       </c>
       <c r="AI309" t="s">
-        <v>446</v>
-      </c>
-      <c r="AL309" t="s">
-        <v>266</v>
+        <v>81</v>
+      </c>
+      <c r="AK309">
+        <v>-130.5</v>
       </c>
       <c r="AM309" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN309" t="s">
-        <v>1636</v>
+        <v>260</v>
       </c>
       <c r="AO309" t="s">
+        <v>1639</v>
+      </c>
+      <c r="AP309" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AS309" t="s">
         <v>1641</v>
-      </c>
-      <c r="AP309" t="s">
-        <v>1642</v>
-      </c>
-      <c r="AS309" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="310" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1644</v>
+        <v>1633</v>
       </c>
       <c r="B310" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="C310" t="s">
         <v>381</v>
       </c>
       <c r="D310">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="E310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N310">
         <v>2</v>
       </c>
       <c r="P310">
+        <v>1</v>
+      </c>
+      <c r="R310">
+        <v>1</v>
+      </c>
+      <c r="T310">
         <v>1</v>
       </c>
       <c r="V310" t="s">
@@ -29792,7 +29750,7 @@
         <v>58</v>
       </c>
       <c r="AE310">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AF310">
         <v>115</v>
@@ -29810,33 +29768,33 @@
         <v>260</v>
       </c>
       <c r="AO310" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="AP310" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="AS310" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="311" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1644</v>
+        <v>1633</v>
       </c>
       <c r="B311" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="C311" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="D311">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="E311">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F311">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H311">
         <v>2</v>
@@ -29844,8 +29802,11 @@
       <c r="N311">
         <v>2</v>
       </c>
+      <c r="O311">
+        <v>2</v>
+      </c>
       <c r="P311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V311" t="s">
         <v>48</v>
@@ -29887,33 +29848,33 @@
         <v>260</v>
       </c>
       <c r="AO311" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="AP311" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="AS311" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="312" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1644</v>
+        <v>1633</v>
       </c>
       <c r="B312" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="C312" t="s">
-        <v>381</v>
+        <v>271</v>
       </c>
       <c r="D312">
-        <v>199</v>
+        <v>449</v>
       </c>
       <c r="E312">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F312">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H312">
         <v>2</v>
@@ -29921,11 +29882,17 @@
       <c r="N312">
         <v>2</v>
       </c>
+      <c r="O312">
+        <v>6</v>
+      </c>
       <c r="P312">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q312">
+        <v>8</v>
       </c>
       <c r="R312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T312">
         <v>1</v>
@@ -29934,7 +29901,7 @@
         <v>48</v>
       </c>
       <c r="W312">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="X312">
         <v>24</v>
@@ -29970,45 +29937,42 @@
         <v>260</v>
       </c>
       <c r="AO312" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="AP312" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="AS312" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="313" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1644</v>
+        <v>1654</v>
       </c>
       <c r="B313" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="C313" t="s">
         <v>271</v>
       </c>
       <c r="D313">
-        <v>259</v>
+        <v>499</v>
       </c>
       <c r="E313">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F313">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N313">
         <v>2</v>
       </c>
-      <c r="O313">
-        <v>2</v>
-      </c>
       <c r="P313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V313" t="s">
         <v>48</v>
@@ -30020,34 +29984,34 @@
         <v>24</v>
       </c>
       <c r="Y313" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA313" t="s">
-        <v>48</v>
+        <v>408</v>
+      </c>
+      <c r="AB313" t="s">
+        <v>1656</v>
       </c>
       <c r="AC313" t="s">
         <v>48</v>
       </c>
-      <c r="AD313">
-        <v>58</v>
+      <c r="AD313" t="s">
+        <v>812</v>
       </c>
       <c r="AE313">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AF313">
         <v>115</v>
       </c>
       <c r="AH313" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AI313" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK313">
-        <v>-130.5</v>
+        <v>244</v>
       </c>
       <c r="AM313" t="s">
-        <v>260</v>
+        <v>54</v>
+      </c>
+      <c r="AN313" t="s">
+        <v>1657</v>
       </c>
       <c r="AO313" t="s">
         <v>1658</v>
@@ -30061,7 +30025,7 @@
     </row>
     <row r="314" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1644</v>
+        <v>1654</v>
       </c>
       <c r="B314" t="s">
         <v>1661</v>
@@ -30070,73 +30034,61 @@
         <v>271</v>
       </c>
       <c r="D314">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="E314">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F314">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H314">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N314">
         <v>2</v>
       </c>
-      <c r="O314">
-        <v>6</v>
-      </c>
       <c r="P314">
-        <v>2</v>
-      </c>
-      <c r="Q314">
-        <v>8</v>
-      </c>
-      <c r="R314">
-        <v>2</v>
-      </c>
-      <c r="T314">
         <v>1</v>
       </c>
       <c r="V314" t="s">
         <v>48</v>
       </c>
       <c r="W314">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="X314">
         <v>24</v>
       </c>
       <c r="Y314" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA314" t="s">
-        <v>48</v>
+        <v>216</v>
+      </c>
+      <c r="AB314" t="s">
+        <v>1656</v>
       </c>
       <c r="AC314" t="s">
         <v>48</v>
       </c>
-      <c r="AD314">
-        <v>58</v>
-      </c>
-      <c r="AE314">
-        <v>115</v>
+      <c r="AD314" t="s">
+        <v>812</v>
       </c>
       <c r="AF314">
         <v>115</v>
       </c>
+      <c r="AG314" t="s">
+        <v>362</v>
+      </c>
       <c r="AH314" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AI314" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK314">
-        <v>-130.5</v>
+        <v>244</v>
       </c>
       <c r="AM314" t="s">
-        <v>260</v>
+        <v>1349</v>
+      </c>
+      <c r="AN314" t="s">
+        <v>1657</v>
       </c>
       <c r="AO314" t="s">
         <v>1662</v>
@@ -30150,16 +30102,16 @@
     </row>
     <row r="315" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B315" t="s">
         <v>1665</v>
       </c>
-      <c r="B315" t="s">
-        <v>1666</v>
-      </c>
       <c r="C315" t="s">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="D315">
-        <v>499</v>
+        <v>1499</v>
       </c>
       <c r="E315">
         <v>2</v>
@@ -30170,7 +30122,19 @@
       <c r="H315">
         <v>1</v>
       </c>
+      <c r="I315">
+        <v>8</v>
+      </c>
+      <c r="J315">
+        <v>1</v>
+      </c>
+      <c r="L315">
+        <v>1</v>
+      </c>
       <c r="N315">
+        <v>2</v>
+      </c>
+      <c r="O315">
         <v>2</v>
       </c>
       <c r="P315">
@@ -30188,8 +30152,11 @@
       <c r="Y315" t="s">
         <v>408</v>
       </c>
+      <c r="AA315" t="s">
+        <v>48</v>
+      </c>
       <c r="AB315" t="s">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="AC315" t="s">
         <v>48</v>
@@ -30197,46 +30164,46 @@
       <c r="AD315" t="s">
         <v>812</v>
       </c>
-      <c r="AE315">
-        <v>118</v>
+      <c r="AE315" t="s">
+        <v>1666</v>
       </c>
       <c r="AF315">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="AH315" t="s">
-        <v>274</v>
-      </c>
-      <c r="AI315" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+      <c r="AJ315" t="s">
+        <v>986</v>
       </c>
       <c r="AM315" t="s">
         <v>54</v>
       </c>
       <c r="AN315" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AO315" t="s">
         <v>1668</v>
       </c>
-      <c r="AO315" t="s">
+      <c r="AP315" t="s">
         <v>1669</v>
       </c>
-      <c r="AP315" t="s">
+      <c r="AS315" t="s">
         <v>1670</v>
-      </c>
-      <c r="AS315" t="s">
-        <v>1671</v>
       </c>
     </row>
     <row r="316" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B316" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="C316" t="s">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="D316">
-        <v>499</v>
+        <v>1699</v>
       </c>
       <c r="E316">
         <v>2</v>
@@ -30247,7 +30214,19 @@
       <c r="H316">
         <v>1</v>
       </c>
+      <c r="I316">
+        <v>8</v>
+      </c>
+      <c r="J316">
+        <v>1</v>
+      </c>
+      <c r="L316">
+        <v>1</v>
+      </c>
       <c r="N316">
+        <v>2</v>
+      </c>
+      <c r="O316">
         <v>2</v>
       </c>
       <c r="P316">
@@ -30263,10 +30242,13 @@
         <v>24</v>
       </c>
       <c r="Y316" t="s">
-        <v>216</v>
+        <v>408</v>
+      </c>
+      <c r="AA316" t="s">
+        <v>48</v>
       </c>
       <c r="AB316" t="s">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="AC316" t="s">
         <v>48</v>
@@ -30274,46 +30256,46 @@
       <c r="AD316" t="s">
         <v>812</v>
       </c>
+      <c r="AE316" t="s">
+        <v>1666</v>
+      </c>
       <c r="AF316">
-        <v>115</v>
-      </c>
-      <c r="AG316" t="s">
-        <v>362</v>
+        <v>129</v>
       </c>
       <c r="AH316" t="s">
-        <v>274</v>
-      </c>
-      <c r="AI316" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+      <c r="AJ316" t="s">
+        <v>986</v>
       </c>
       <c r="AM316" t="s">
-        <v>1349</v>
+        <v>54</v>
       </c>
       <c r="AN316" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="AO316" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="AP316" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="AS316" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="317" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B317" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="C317" t="s">
         <v>205</v>
       </c>
       <c r="D317">
-        <v>1499</v>
+        <v>1249</v>
       </c>
       <c r="E317">
         <v>2</v>
@@ -30352,13 +30334,10 @@
         <v>24</v>
       </c>
       <c r="Y317" t="s">
-        <v>408</v>
-      </c>
-      <c r="AA317" t="s">
-        <v>48</v>
+        <v>1554</v>
       </c>
       <c r="AB317" t="s">
-        <v>1667</v>
+        <v>1674</v>
       </c>
       <c r="AC317" t="s">
         <v>48</v>
@@ -30366,76 +30345,61 @@
       <c r="AD317" t="s">
         <v>812</v>
       </c>
-      <c r="AE317" t="s">
-        <v>1677</v>
+      <c r="AE317">
+        <v>123</v>
       </c>
       <c r="AF317">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AH317" t="s">
         <v>245</v>
       </c>
-      <c r="AJ317" t="s">
-        <v>986</v>
+      <c r="AI317" t="s">
+        <v>985</v>
       </c>
       <c r="AM317" t="s">
-        <v>54</v>
+        <v>1349</v>
       </c>
       <c r="AN317" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AO317" t="s">
+        <v>1676</v>
+      </c>
+      <c r="AP317" t="s">
+        <v>1677</v>
+      </c>
+      <c r="AS317" t="s">
         <v>1678</v>
-      </c>
-      <c r="AO317" t="s">
-        <v>1679</v>
-      </c>
-      <c r="AP317" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AS317" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="318" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B318" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="C318" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D318">
-        <v>1699</v>
-      </c>
-      <c r="E318">
-        <v>2</v>
-      </c>
-      <c r="F318">
-        <v>2</v>
-      </c>
-      <c r="H318">
-        <v>1</v>
-      </c>
-      <c r="I318">
-        <v>8</v>
-      </c>
-      <c r="J318">
-        <v>1</v>
-      </c>
-      <c r="L318">
+        <v>4999</v>
+      </c>
+      <c r="G318">
+        <v>16</v>
+      </c>
+      <c r="M318">
         <v>1</v>
       </c>
       <c r="N318">
         <v>2</v>
       </c>
       <c r="O318">
-        <v>2</v>
-      </c>
-      <c r="P318">
-        <v>1</v>
-      </c>
-      <c r="V318" t="s">
-        <v>48</v>
+        <v>16</v>
+      </c>
+      <c r="U318">
+        <v>1</v>
       </c>
       <c r="W318">
         <v>192</v>
@@ -30446,88 +30410,58 @@
       <c r="Y318" t="s">
         <v>408</v>
       </c>
-      <c r="AA318" t="s">
-        <v>48</v>
-      </c>
       <c r="AB318" t="s">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="AC318" t="s">
         <v>48</v>
       </c>
-      <c r="AD318" t="s">
-        <v>812</v>
-      </c>
       <c r="AE318" t="s">
-        <v>1677</v>
+        <v>329</v>
       </c>
       <c r="AF318">
-        <v>129</v>
-      </c>
-      <c r="AH318" t="s">
-        <v>245</v>
-      </c>
-      <c r="AJ318" t="s">
-        <v>986</v>
+        <v>133</v>
+      </c>
+      <c r="AI318" t="s">
+        <v>354</v>
       </c>
       <c r="AM318" t="s">
         <v>54</v>
       </c>
       <c r="AN318" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="AO318" t="s">
+        <v>1681</v>
+      </c>
+      <c r="AP318" t="s">
+        <v>1682</v>
+      </c>
+      <c r="AS318" t="s">
         <v>1683</v>
-      </c>
-      <c r="AP318" t="s">
-        <v>1680</v>
-      </c>
-      <c r="AS318" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="319" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B319" t="s">
         <v>1684</v>
       </c>
       <c r="C319" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D319">
-        <v>1249</v>
-      </c>
-      <c r="E319">
-        <v>2</v>
-      </c>
-      <c r="F319">
-        <v>2</v>
-      </c>
-      <c r="H319">
-        <v>1</v>
-      </c>
-      <c r="I319">
-        <v>8</v>
-      </c>
-      <c r="J319">
-        <v>1</v>
-      </c>
-      <c r="L319">
+        <v>4999</v>
+      </c>
+      <c r="M319">
         <v>1</v>
       </c>
       <c r="N319">
         <v>2</v>
       </c>
-      <c r="O319">
-        <v>2</v>
-      </c>
-      <c r="P319">
-        <v>1</v>
-      </c>
-      <c r="V319" t="s">
-        <v>48</v>
+      <c r="U319">
+        <v>1</v>
       </c>
       <c r="W319">
         <v>192</v>
@@ -30536,72 +30470,87 @@
         <v>24</v>
       </c>
       <c r="Y319" t="s">
-        <v>1554</v>
+        <v>1685</v>
       </c>
       <c r="AB319" t="s">
-        <v>1685</v>
+        <v>1656</v>
       </c>
       <c r="AC319" t="s">
         <v>48</v>
       </c>
-      <c r="AD319" t="s">
-        <v>812</v>
-      </c>
-      <c r="AE319">
-        <v>123</v>
-      </c>
       <c r="AF319">
-        <v>127</v>
-      </c>
-      <c r="AH319" t="s">
-        <v>245</v>
+        <v>133</v>
       </c>
       <c r="AI319" t="s">
-        <v>985</v>
+        <v>354</v>
       </c>
       <c r="AM319" t="s">
-        <v>1349</v>
+        <v>54</v>
       </c>
       <c r="AN319" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AO319" t="s">
         <v>1686</v>
       </c>
-      <c r="AO319" t="s">
+      <c r="AP319" t="s">
         <v>1687</v>
       </c>
-      <c r="AP319" t="s">
+      <c r="AS319" t="s">
         <v>1688</v>
-      </c>
-      <c r="AS319" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="320" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B320" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="C320" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="D320">
-        <v>4999</v>
-      </c>
-      <c r="G320">
-        <v>16</v>
-      </c>
-      <c r="M320">
+        <v>2299</v>
+      </c>
+      <c r="E320">
+        <v>4</v>
+      </c>
+      <c r="F320">
+        <v>4</v>
+      </c>
+      <c r="H320">
+        <v>2</v>
+      </c>
+      <c r="I320">
+        <v>8</v>
+      </c>
+      <c r="J320">
+        <v>1</v>
+      </c>
+      <c r="L320">
         <v>1</v>
       </c>
       <c r="N320">
         <v>2</v>
       </c>
       <c r="O320">
-        <v>16</v>
-      </c>
-      <c r="U320">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="P320">
+        <v>2</v>
+      </c>
+      <c r="Q320">
+        <v>8</v>
+      </c>
+      <c r="R320">
+        <v>1</v>
+      </c>
+      <c r="T320">
+        <v>1</v>
+      </c>
+      <c r="V320" t="s">
+        <v>48</v>
       </c>
       <c r="W320">
         <v>192</v>
@@ -30613,19 +30562,19 @@
         <v>408</v>
       </c>
       <c r="AB320" t="s">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="AC320" t="s">
         <v>48</v>
       </c>
-      <c r="AE320" t="s">
-        <v>329</v>
+      <c r="AD320" t="s">
+        <v>812</v>
       </c>
       <c r="AF320">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="AI320" t="s">
-        <v>354</v>
+        <v>1690</v>
       </c>
       <c r="AM320" t="s">
         <v>54</v>
@@ -30645,25 +30594,58 @@
     </row>
     <row r="321" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B321" t="s">
         <v>1695</v>
       </c>
       <c r="C321" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="D321">
-        <v>4999</v>
-      </c>
-      <c r="M321">
+        <v>2499</v>
+      </c>
+      <c r="E321">
+        <v>2</v>
+      </c>
+      <c r="F321">
+        <v>2</v>
+      </c>
+      <c r="G321">
+        <v>6</v>
+      </c>
+      <c r="H321">
+        <v>2</v>
+      </c>
+      <c r="I321">
+        <v>8</v>
+      </c>
+      <c r="J321">
+        <v>2</v>
+      </c>
+      <c r="K321">
         <v>1</v>
       </c>
       <c r="N321">
         <v>2</v>
       </c>
-      <c r="U321">
-        <v>1</v>
+      <c r="O321">
+        <v>6</v>
+      </c>
+      <c r="P321">
+        <v>2</v>
+      </c>
+      <c r="Q321">
+        <v>8</v>
+      </c>
+      <c r="R321">
+        <v>2</v>
+      </c>
+      <c r="S321">
+        <v>1</v>
+      </c>
+      <c r="V321" t="s">
+        <v>48</v>
       </c>
       <c r="W321">
         <v>192</v>
@@ -30672,19 +30654,28 @@
         <v>24</v>
       </c>
       <c r="Y321" t="s">
-        <v>1696</v>
+        <v>408</v>
       </c>
       <c r="AB321" t="s">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="AC321" t="s">
         <v>48</v>
       </c>
+      <c r="AD321" t="s">
+        <v>812</v>
+      </c>
+      <c r="AE321" t="s">
+        <v>1666</v>
+      </c>
       <c r="AF321">
-        <v>133</v>
+        <v>130</v>
+      </c>
+      <c r="AH321" t="s">
+        <v>245</v>
       </c>
       <c r="AI321" t="s">
-        <v>354</v>
+        <v>1690</v>
       </c>
       <c r="AM321" t="s">
         <v>54</v>
@@ -30693,33 +30684,33 @@
         <v>1691</v>
       </c>
       <c r="AO321" t="s">
+        <v>1696</v>
+      </c>
+      <c r="AP321" t="s">
         <v>1697</v>
       </c>
-      <c r="AP321" t="s">
+      <c r="AS321" t="s">
         <v>1698</v>
-      </c>
-      <c r="AS321" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="322" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B322" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="C322" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D322">
-        <v>2299</v>
+        <v>3699</v>
       </c>
       <c r="E322">
         <v>4</v>
       </c>
-      <c r="F322">
-        <v>4</v>
+      <c r="G322">
+        <v>8</v>
       </c>
       <c r="H322">
         <v>2</v>
@@ -30728,16 +30719,16 @@
         <v>8</v>
       </c>
       <c r="J322">
-        <v>1</v>
-      </c>
-      <c r="L322">
+        <v>2</v>
+      </c>
+      <c r="K322">
         <v>1</v>
       </c>
       <c r="N322">
         <v>2</v>
       </c>
       <c r="O322">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P322">
         <v>2</v>
@@ -30746,9 +30737,9 @@
         <v>8</v>
       </c>
       <c r="R322">
-        <v>1</v>
-      </c>
-      <c r="T322">
+        <v>2</v>
+      </c>
+      <c r="S322">
         <v>1</v>
       </c>
       <c r="V322" t="s">
@@ -30764,7 +30755,7 @@
         <v>408</v>
       </c>
       <c r="AB322" t="s">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="AC322" t="s">
         <v>48</v>
@@ -30772,49 +30763,55 @@
       <c r="AD322" t="s">
         <v>812</v>
       </c>
+      <c r="AE322" t="s">
+        <v>1666</v>
+      </c>
       <c r="AF322">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="AH322" t="s">
+        <v>245</v>
       </c>
       <c r="AI322" t="s">
-        <v>1701</v>
+        <v>1690</v>
       </c>
       <c r="AM322" t="s">
         <v>54</v>
       </c>
       <c r="AN322" t="s">
+        <v>1691</v>
+      </c>
+      <c r="AO322" t="s">
+        <v>1700</v>
+      </c>
+      <c r="AP322" t="s">
+        <v>1701</v>
+      </c>
+      <c r="AS322" t="s">
         <v>1702</v>
-      </c>
-      <c r="AO322" t="s">
-        <v>1703</v>
-      </c>
-      <c r="AP322" t="s">
-        <v>1704</v>
-      </c>
-      <c r="AS322" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="323" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B323" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="C323" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D323">
-        <v>2499</v>
+        <v>4399</v>
       </c>
       <c r="E323">
-        <v>2</v>
-      </c>
-      <c r="F323">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F323" t="s">
+        <v>869</v>
       </c>
       <c r="G323">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H323">
         <v>2</v>
@@ -30825,14 +30822,14 @@
       <c r="J323">
         <v>2</v>
       </c>
-      <c r="K323">
+      <c r="L323">
         <v>1</v>
       </c>
       <c r="N323">
         <v>2</v>
       </c>
       <c r="O323">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P323">
         <v>2</v>
@@ -30843,7 +30840,7 @@
       <c r="R323">
         <v>2</v>
       </c>
-      <c r="S323">
+      <c r="T323">
         <v>1</v>
       </c>
       <c r="V323" t="s">
@@ -30859,7 +30856,7 @@
         <v>408</v>
       </c>
       <c r="AB323" t="s">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="AC323" t="s">
         <v>48</v>
@@ -30868,7 +30865,7 @@
         <v>812</v>
       </c>
       <c r="AE323" t="s">
-        <v>1677</v>
+        <v>1666</v>
       </c>
       <c r="AF323">
         <v>130</v>
@@ -30877,71 +30874,47 @@
         <v>245</v>
       </c>
       <c r="AI323" t="s">
-        <v>1701</v>
+        <v>1690</v>
       </c>
       <c r="AM323" t="s">
         <v>54</v>
       </c>
       <c r="AN323" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="AO323" t="s">
+        <v>1705</v>
+      </c>
+      <c r="AP323" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AS323" t="s">
         <v>1707</v>
-      </c>
-      <c r="AP323" t="s">
-        <v>1708</v>
-      </c>
-      <c r="AS323" t="s">
-        <v>1709</v>
       </c>
     </row>
     <row r="324" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B324" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="C324" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
       <c r="D324">
-        <v>3699</v>
+        <v>174</v>
       </c>
       <c r="E324">
-        <v>4</v>
-      </c>
-      <c r="G324">
-        <v>8</v>
-      </c>
-      <c r="H324">
-        <v>2</v>
-      </c>
-      <c r="I324">
-        <v>8</v>
-      </c>
-      <c r="J324">
-        <v>2</v>
-      </c>
-      <c r="K324">
+        <v>1</v>
+      </c>
+      <c r="F324">
         <v>1</v>
       </c>
       <c r="N324">
         <v>2</v>
       </c>
-      <c r="O324">
-        <v>8</v>
-      </c>
       <c r="P324">
-        <v>2</v>
-      </c>
-      <c r="Q324">
-        <v>8</v>
-      </c>
-      <c r="R324">
-        <v>2</v>
-      </c>
-      <c r="S324">
         <v>1</v>
       </c>
       <c r="V324" t="s">
@@ -30954,95 +30927,71 @@
         <v>24</v>
       </c>
       <c r="Y324" t="s">
-        <v>408</v>
-      </c>
-      <c r="AB324" t="s">
-        <v>1667</v>
+        <v>49</v>
+      </c>
+      <c r="Z324" t="s">
+        <v>781</v>
+      </c>
+      <c r="AA324" t="s">
+        <v>48</v>
       </c>
       <c r="AC324" t="s">
         <v>48</v>
       </c>
       <c r="AD324" t="s">
-        <v>812</v>
-      </c>
-      <c r="AE324" t="s">
-        <v>1677</v>
-      </c>
-      <c r="AF324">
-        <v>130</v>
+        <v>346</v>
+      </c>
+      <c r="AG324" t="s">
+        <v>124</v>
       </c>
       <c r="AH324" t="s">
-        <v>245</v>
+        <v>1709</v>
       </c>
       <c r="AI324" t="s">
-        <v>1701</v>
+        <v>1710</v>
+      </c>
+      <c r="AK324" t="s">
+        <v>821</v>
       </c>
       <c r="AM324" t="s">
         <v>54</v>
       </c>
       <c r="AN324" t="s">
-        <v>1702</v>
+        <v>1711</v>
       </c>
       <c r="AO324" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="AP324" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="AS324" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="325" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B325" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="C325" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="D325">
-        <v>4399</v>
+        <v>249</v>
       </c>
       <c r="E325">
-        <v>8</v>
-      </c>
-      <c r="F325" t="s">
-        <v>869</v>
-      </c>
-      <c r="G325">
-        <v>8</v>
-      </c>
-      <c r="H325">
-        <v>2</v>
-      </c>
-      <c r="I325">
-        <v>8</v>
-      </c>
-      <c r="J325">
-        <v>2</v>
-      </c>
-      <c r="L325">
+        <v>1</v>
+      </c>
+      <c r="F325">
         <v>1</v>
       </c>
       <c r="N325">
         <v>2</v>
       </c>
-      <c r="O325">
-        <v>8</v>
-      </c>
       <c r="P325">
-        <v>2</v>
-      </c>
-      <c r="Q325">
-        <v>8</v>
-      </c>
-      <c r="R325">
-        <v>2</v>
-      </c>
-      <c r="T325">
         <v>1</v>
       </c>
       <c r="V325" t="s">
@@ -31055,34 +31004,43 @@
         <v>24</v>
       </c>
       <c r="Y325" t="s">
-        <v>408</v>
+        <v>49</v>
+      </c>
+      <c r="Z325" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA325" t="s">
+        <v>48</v>
       </c>
       <c r="AB325" t="s">
-        <v>1667</v>
+        <v>73</v>
       </c>
       <c r="AC325" t="s">
         <v>48</v>
       </c>
       <c r="AD325" t="s">
-        <v>812</v>
+        <v>346</v>
       </c>
       <c r="AE325" t="s">
-        <v>1677</v>
-      </c>
-      <c r="AF325">
-        <v>130</v>
+        <v>124</v>
+      </c>
+      <c r="AG325" t="s">
+        <v>52</v>
       </c>
       <c r="AH325" t="s">
-        <v>245</v>
+        <v>1709</v>
       </c>
       <c r="AI325" t="s">
-        <v>1701</v>
+        <v>1710</v>
+      </c>
+      <c r="AK325" t="s">
+        <v>821</v>
       </c>
       <c r="AM325" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
       <c r="AN325" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
       <c r="AO325" t="s">
         <v>1716</v>
@@ -31091,27 +31049,27 @@
         <v>1717</v>
       </c>
       <c r="AS325" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="326" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B326" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="C326" t="s">
         <v>297</v>
       </c>
       <c r="D326">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="E326">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F326">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N326">
         <v>2</v>
@@ -31132,10 +31090,13 @@
         <v>49</v>
       </c>
       <c r="Z326" t="s">
-        <v>781</v>
+        <v>48</v>
       </c>
       <c r="AA326" t="s">
         <v>48</v>
+      </c>
+      <c r="AB326" t="s">
+        <v>73</v>
       </c>
       <c r="AC326" t="s">
         <v>48</v>
@@ -31143,52 +31104,55 @@
       <c r="AD326" t="s">
         <v>346</v>
       </c>
-      <c r="AG326" t="s">
-        <v>124</v>
+      <c r="AE326">
+        <v>112</v>
+      </c>
+      <c r="AF326">
+        <v>110</v>
       </c>
       <c r="AH326" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="AI326" t="s">
-        <v>1721</v>
+        <v>1710</v>
       </c>
       <c r="AK326" t="s">
         <v>821</v>
       </c>
       <c r="AM326" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
       <c r="AN326" t="s">
-        <v>1722</v>
+        <v>1711</v>
       </c>
       <c r="AO326" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="AP326" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="AS326" t="s">
-        <v>1725</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="327" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B327" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="C327" t="s">
         <v>271</v>
       </c>
       <c r="D327">
-        <v>249</v>
+        <v>374</v>
       </c>
       <c r="E327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N327">
         <v>2</v>
@@ -31214,9 +31178,6 @@
       <c r="AA327" t="s">
         <v>48</v>
       </c>
-      <c r="AB327" t="s">
-        <v>73</v>
-      </c>
       <c r="AC327" t="s">
         <v>48</v>
       </c>
@@ -31226,14 +31187,14 @@
       <c r="AE327" t="s">
         <v>124</v>
       </c>
-      <c r="AG327" t="s">
+      <c r="AF327" t="s">
         <v>52</v>
       </c>
       <c r="AH327" t="s">
-        <v>1720</v>
+        <v>1709</v>
       </c>
       <c r="AI327" t="s">
-        <v>1721</v>
+        <v>1710</v>
       </c>
       <c r="AK327" t="s">
         <v>821</v>
@@ -31242,13 +31203,13 @@
         <v>282</v>
       </c>
       <c r="AN327" t="s">
-        <v>1722</v>
+        <v>1711</v>
       </c>
       <c r="AO327" t="s">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="AP327" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="AS327" t="s">
         <v>1725</v>
@@ -31256,21 +31217,27 @@
     </row>
     <row r="328" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B328" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="C328" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="D328">
-        <v>249</v>
+        <v>349</v>
       </c>
       <c r="E328">
         <v>2</v>
       </c>
       <c r="F328">
+        <v>2</v>
+      </c>
+      <c r="G328">
+        <v>2</v>
+      </c>
+      <c r="H328">
         <v>2</v>
       </c>
       <c r="N328">
@@ -31292,13 +31259,10 @@
         <v>49</v>
       </c>
       <c r="Z328" t="s">
-        <v>48</v>
+        <v>272</v>
       </c>
       <c r="AA328" t="s">
         <v>48</v>
-      </c>
-      <c r="AB328" t="s">
-        <v>73</v>
       </c>
       <c r="AC328" t="s">
         <v>48</v>
@@ -31306,17 +31270,17 @@
       <c r="AD328" t="s">
         <v>346</v>
       </c>
-      <c r="AE328">
-        <v>112</v>
-      </c>
-      <c r="AF328">
-        <v>110</v>
+      <c r="AE328" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF328" t="s">
+        <v>52</v>
       </c>
       <c r="AH328" t="s">
-        <v>1730</v>
+        <v>1709</v>
       </c>
       <c r="AI328" t="s">
-        <v>1721</v>
+        <v>1710</v>
       </c>
       <c r="AK328" t="s">
         <v>821</v>
@@ -31325,30 +31289,30 @@
         <v>282</v>
       </c>
       <c r="AN328" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="AO328" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="AP328" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="AS328" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="329" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B329" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="C329" t="s">
         <v>271</v>
       </c>
       <c r="D329">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E329">
         <v>2</v>
@@ -31356,8 +31320,17 @@
       <c r="F329">
         <v>2</v>
       </c>
+      <c r="G329">
+        <v>2</v>
+      </c>
+      <c r="H329" t="s">
+        <v>65</v>
+      </c>
       <c r="N329">
         <v>2</v>
+      </c>
+      <c r="O329">
+        <v>4</v>
       </c>
       <c r="P329">
         <v>1</v>
@@ -31380,6 +31353,9 @@
       <c r="AA329" t="s">
         <v>48</v>
       </c>
+      <c r="AB329" t="s">
+        <v>73</v>
+      </c>
       <c r="AC329" t="s">
         <v>48</v>
       </c>
@@ -31389,64 +31365,64 @@
       <c r="AE329" t="s">
         <v>124</v>
       </c>
-      <c r="AF329" t="s">
+      <c r="AG329" t="s">
         <v>52</v>
       </c>
       <c r="AH329" t="s">
-        <v>1720</v>
+        <v>1709</v>
       </c>
       <c r="AI329" t="s">
-        <v>1721</v>
+        <v>1710</v>
       </c>
       <c r="AK329" t="s">
         <v>821</v>
       </c>
       <c r="AM329" t="s">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="AN329" t="s">
-        <v>1722</v>
+        <v>1711</v>
       </c>
       <c r="AO329" t="s">
-        <v>1734</v>
+        <v>387</v>
       </c>
       <c r="AP329" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="AS329" t="s">
-        <v>1736</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="330" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B330" t="s">
-        <v>1737</v>
+        <v>1733</v>
       </c>
       <c r="C330" t="s">
         <v>271</v>
       </c>
       <c r="D330">
-        <v>349</v>
+        <v>589</v>
       </c>
       <c r="E330">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F330">
-        <v>2</v>
-      </c>
-      <c r="G330">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H330">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N330">
         <v>2</v>
       </c>
+      <c r="O330">
+        <v>4</v>
+      </c>
       <c r="P330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V330" t="s">
         <v>48</v>
@@ -31458,12 +31434,9 @@
         <v>24</v>
       </c>
       <c r="Y330" t="s">
-        <v>49</v>
+        <v>345</v>
       </c>
       <c r="Z330" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA330" t="s">
         <v>48</v>
       </c>
       <c r="AC330" t="s">
@@ -31472,17 +31445,17 @@
       <c r="AD330" t="s">
         <v>346</v>
       </c>
-      <c r="AE330" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF330" t="s">
-        <v>52</v>
+      <c r="AE330">
+        <v>112</v>
+      </c>
+      <c r="AF330">
+        <v>110</v>
       </c>
       <c r="AH330" t="s">
-        <v>1720</v>
+        <v>1709</v>
       </c>
       <c r="AI330" t="s">
-        <v>1721</v>
+        <v>1710</v>
       </c>
       <c r="AK330" t="s">
         <v>821</v>
@@ -31490,67 +31463,79 @@
       <c r="AM330" t="s">
         <v>282</v>
       </c>
-      <c r="AN330" t="s">
-        <v>1738</v>
-      </c>
       <c r="AO330" t="s">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="AP330" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="AS330" t="s">
-        <v>1741</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="331" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>1665</v>
+        <v>1654</v>
       </c>
       <c r="B331" t="s">
-        <v>1742</v>
+        <v>1736</v>
       </c>
       <c r="C331" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D331">
-        <v>369</v>
+        <v>999</v>
       </c>
       <c r="E331">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F331">
-        <v>2</v>
-      </c>
-      <c r="G331">
-        <v>2</v>
-      </c>
-      <c r="H331" t="s">
-        <v>65</v>
+        <v>8</v>
+      </c>
+      <c r="H331">
+        <v>2</v>
+      </c>
+      <c r="I331">
+        <v>16</v>
+      </c>
+      <c r="J331">
+        <v>2</v>
+      </c>
+      <c r="L331" t="s">
+        <v>237</v>
       </c>
       <c r="N331">
         <v>2</v>
       </c>
       <c r="O331">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P331">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q331">
+        <v>16</v>
+      </c>
+      <c r="R331">
+        <v>2</v>
+      </c>
+      <c r="T331" t="s">
+        <v>237</v>
       </c>
       <c r="V331" t="s">
-        <v>48</v>
+        <v>1737</v>
       </c>
       <c r="W331">
         <v>192</v>
       </c>
       <c r="X331">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y331" t="s">
         <v>49</v>
       </c>
       <c r="Z331" t="s">
-        <v>48</v>
+        <v>272</v>
       </c>
       <c r="AA331" t="s">
         <v>48</v>
@@ -31561,70 +31546,67 @@
       <c r="AC331" t="s">
         <v>48</v>
       </c>
-      <c r="AD331" t="s">
-        <v>346</v>
-      </c>
-      <c r="AE331" t="s">
-        <v>124</v>
-      </c>
-      <c r="AG331" t="s">
-        <v>52</v>
+      <c r="AD331">
+        <v>60</v>
+      </c>
+      <c r="AE331">
+        <v>116</v>
+      </c>
+      <c r="AF331">
+        <v>119</v>
       </c>
       <c r="AH331" t="s">
-        <v>1720</v>
+        <v>487</v>
       </c>
       <c r="AI331" t="s">
-        <v>1721</v>
-      </c>
-      <c r="AK331" t="s">
-        <v>821</v>
+        <v>1738</v>
       </c>
       <c r="AM331" t="s">
-        <v>54</v>
+        <v>291</v>
       </c>
       <c r="AN331" t="s">
-        <v>1722</v>
+        <v>1739</v>
       </c>
       <c r="AO331" t="s">
-        <v>387</v>
+        <v>1740</v>
       </c>
       <c r="AP331" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="AS331" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="332" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>1665</v>
+        <v>1743</v>
       </c>
       <c r="B332" t="s">
         <v>1744</v>
       </c>
       <c r="C332" t="s">
-        <v>271</v>
+        <v>381</v>
       </c>
       <c r="D332">
-        <v>589</v>
+        <v>159</v>
       </c>
       <c r="E332">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F332">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G332">
+        <v>2</v>
       </c>
       <c r="H332">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N332">
         <v>2</v>
       </c>
-      <c r="O332">
-        <v>4</v>
-      </c>
       <c r="P332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V332" t="s">
         <v>48</v>
@@ -31636,109 +31618,76 @@
         <v>24</v>
       </c>
       <c r="Y332" t="s">
-        <v>345</v>
-      </c>
-      <c r="Z332" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="AA332" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB332" t="s">
+        <v>73</v>
       </c>
       <c r="AC332" t="s">
         <v>48</v>
-      </c>
-      <c r="AD332" t="s">
-        <v>346</v>
-      </c>
-      <c r="AE332">
-        <v>112</v>
-      </c>
-      <c r="AF332">
-        <v>110</v>
-      </c>
-      <c r="AH332" t="s">
-        <v>1720</v>
-      </c>
-      <c r="AI332" t="s">
-        <v>1721</v>
-      </c>
-      <c r="AK332" t="s">
-        <v>821</v>
       </c>
       <c r="AM332" t="s">
         <v>282</v>
       </c>
+      <c r="AN332" t="s">
+        <v>1745</v>
+      </c>
       <c r="AO332" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="AP332" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="AS332" t="s">
-        <v>1741</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="333" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>1665</v>
+        <v>1743</v>
       </c>
       <c r="B333" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="C333" t="s">
-        <v>257</v>
+        <v>381</v>
       </c>
       <c r="D333">
-        <v>999</v>
+        <v>199</v>
       </c>
       <c r="E333">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F333">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="G333">
+        <v>3</v>
       </c>
       <c r="H333">
-        <v>2</v>
-      </c>
-      <c r="I333">
-        <v>16</v>
-      </c>
-      <c r="J333">
-        <v>2</v>
-      </c>
-      <c r="L333" t="s">
-        <v>237</v>
+        <v>1</v>
       </c>
       <c r="N333">
         <v>2</v>
       </c>
-      <c r="O333">
-        <v>6</v>
-      </c>
       <c r="P333">
         <v>2</v>
       </c>
-      <c r="Q333">
-        <v>16</v>
-      </c>
-      <c r="R333">
-        <v>2</v>
-      </c>
-      <c r="T333" t="s">
-        <v>237</v>
-      </c>
       <c r="V333" t="s">
-        <v>1748</v>
+        <v>48</v>
       </c>
       <c r="W333">
         <v>192</v>
       </c>
       <c r="X333">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y333" t="s">
         <v>49</v>
       </c>
-      <c r="Z333" t="s">
-        <v>272</v>
-      </c>
       <c r="AA333" t="s">
         <v>48</v>
       </c>
@@ -31748,58 +31697,46 @@
       <c r="AC333" t="s">
         <v>48</v>
       </c>
-      <c r="AD333">
-        <v>60</v>
-      </c>
-      <c r="AE333">
-        <v>116</v>
-      </c>
-      <c r="AF333">
-        <v>119</v>
-      </c>
-      <c r="AH333" t="s">
-        <v>487</v>
-      </c>
-      <c r="AI333" t="s">
-        <v>1749</v>
-      </c>
       <c r="AM333" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AN333" t="s">
+        <v>1745</v>
+      </c>
+      <c r="AO333" t="s">
         <v>1750</v>
       </c>
-      <c r="AO333" t="s">
+      <c r="AP333" t="s">
         <v>1751</v>
       </c>
-      <c r="AP333" t="s">
-        <v>1752</v>
+      <c r="AQ333">
+        <v>2</v>
       </c>
       <c r="AS333" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="334" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B334" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
       <c r="C334" t="s">
         <v>381</v>
       </c>
       <c r="D334">
-        <v>159</v>
+        <v>499</v>
       </c>
       <c r="E334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G334">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H334">
         <v>1</v>
@@ -31808,13 +31745,13 @@
         <v>2</v>
       </c>
       <c r="P334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V334" t="s">
         <v>48</v>
       </c>
       <c r="W334">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="X334">
         <v>24</v>
@@ -31835,185 +31772,200 @@
         <v>282</v>
       </c>
       <c r="AN334" t="s">
+        <v>1753</v>
+      </c>
+      <c r="AO334" t="s">
+        <v>1754</v>
+      </c>
+      <c r="AP334" t="s">
+        <v>1755</v>
+      </c>
+      <c r="AQ334">
+        <v>2</v>
+      </c>
+      <c r="AS334" t="s">
         <v>1756</v>
-      </c>
-      <c r="AO334" t="s">
-        <v>1757</v>
-      </c>
-      <c r="AP334" t="s">
-        <v>1758</v>
-      </c>
-      <c r="AS334" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="335" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B335" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
       <c r="C335" t="s">
-        <v>381</v>
-      </c>
-      <c r="D335">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="E335">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F335">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G335">
-        <v>3</v>
-      </c>
-      <c r="H335">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N335">
         <v>2</v>
       </c>
+      <c r="O335">
+        <v>6</v>
+      </c>
       <c r="P335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V335" t="s">
         <v>48</v>
       </c>
       <c r="W335">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="X335">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y335" t="s">
         <v>49</v>
       </c>
-      <c r="AA335" t="s">
+      <c r="Z335" t="s">
         <v>48</v>
       </c>
       <c r="AB335" t="s">
         <v>73</v>
       </c>
-      <c r="AC335" t="s">
-        <v>48</v>
+      <c r="AD335">
+        <v>64</v>
+      </c>
+      <c r="AF335">
+        <v>110</v>
+      </c>
+      <c r="AG335">
+        <v>106</v>
+      </c>
+      <c r="AJ335" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AL335">
+        <v>-126</v>
       </c>
       <c r="AM335" t="s">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="AN335" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="AO335" t="s">
+        <v>1759</v>
+      </c>
+      <c r="AP335" t="s">
+        <v>1760</v>
+      </c>
+      <c r="AS335" t="s">
         <v>1761</v>
-      </c>
-      <c r="AP335" t="s">
-        <v>1762</v>
-      </c>
-      <c r="AQ335">
-        <v>2</v>
-      </c>
-      <c r="AS335" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="336" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B336" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C336" t="s">
-        <v>381</v>
-      </c>
-      <c r="D336">
-        <v>499</v>
+        <v>47</v>
       </c>
       <c r="E336">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F336">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G336">
-        <v>3</v>
-      </c>
-      <c r="H336">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N336">
         <v>2</v>
       </c>
+      <c r="O336">
+        <v>6</v>
+      </c>
       <c r="P336">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V336" t="s">
         <v>48</v>
       </c>
       <c r="W336">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="X336">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y336" t="s">
         <v>49</v>
       </c>
-      <c r="AA336" t="s">
+      <c r="Z336" t="s">
         <v>48</v>
       </c>
       <c r="AB336" t="s">
         <v>73</v>
       </c>
-      <c r="AC336" t="s">
-        <v>48</v>
+      <c r="AD336">
+        <v>64</v>
+      </c>
+      <c r="AF336">
+        <v>110</v>
+      </c>
+      <c r="AG336">
+        <v>106</v>
+      </c>
+      <c r="AJ336" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AL336">
+        <v>-126</v>
       </c>
       <c r="AM336" t="s">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="AN336" t="s">
-        <v>1764</v>
+        <v>1758</v>
       </c>
       <c r="AO336" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="AP336" t="s">
-        <v>1766</v>
-      </c>
-      <c r="AQ336">
-        <v>2</v>
+        <v>1760</v>
       </c>
       <c r="AS336" t="s">
-        <v>1767</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="337" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B337" t="s">
-        <v>1768</v>
+        <v>1764</v>
       </c>
       <c r="C337" t="s">
         <v>47</v>
       </c>
+      <c r="D337">
+        <v>280</v>
+      </c>
       <c r="E337">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F337">
         <v>4</v>
       </c>
       <c r="G337">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N337">
         <v>2</v>
       </c>
-      <c r="O337">
-        <v>6</v>
-      </c>
       <c r="P337">
         <v>1</v>
       </c>
@@ -32021,76 +31973,61 @@
         <v>48</v>
       </c>
       <c r="W337">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="X337">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y337" t="s">
         <v>49</v>
       </c>
-      <c r="Z337" t="s">
-        <v>48</v>
-      </c>
       <c r="AB337" t="s">
         <v>73</v>
       </c>
-      <c r="AD337">
-        <v>64</v>
-      </c>
-      <c r="AF337">
-        <v>110</v>
-      </c>
-      <c r="AG337">
-        <v>106</v>
-      </c>
-      <c r="AJ337" t="s">
-        <v>1085</v>
-      </c>
-      <c r="AL337">
-        <v>-126</v>
+      <c r="AC337" t="s">
+        <v>48</v>
       </c>
       <c r="AM337" t="s">
         <v>54</v>
       </c>
       <c r="AN337" t="s">
-        <v>1769</v>
+        <v>1753</v>
       </c>
       <c r="AO337" t="s">
-        <v>1770</v>
+        <v>1765</v>
       </c>
       <c r="AP337" t="s">
-        <v>1771</v>
+        <v>1766</v>
+      </c>
+      <c r="AQ337">
+        <v>4</v>
       </c>
       <c r="AS337" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="338" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B338" t="s">
-        <v>1773</v>
+        <v>1768</v>
       </c>
       <c r="C338" t="s">
         <v>47</v>
       </c>
       <c r="E338">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F338">
         <v>4</v>
       </c>
       <c r="G338">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N338">
         <v>2</v>
       </c>
-      <c r="O338">
-        <v>6</v>
-      </c>
       <c r="P338">
         <v>1</v>
       </c>
@@ -32098,74 +32035,65 @@
         <v>48</v>
       </c>
       <c r="W338">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="X338">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y338" t="s">
         <v>49</v>
       </c>
-      <c r="Z338" t="s">
-        <v>48</v>
-      </c>
       <c r="AB338" t="s">
         <v>73</v>
       </c>
-      <c r="AD338">
-        <v>64</v>
-      </c>
-      <c r="AF338">
-        <v>110</v>
-      </c>
-      <c r="AG338">
-        <v>106</v>
-      </c>
-      <c r="AJ338" t="s">
-        <v>1085</v>
-      </c>
-      <c r="AL338">
-        <v>-126</v>
+      <c r="AC338" t="s">
+        <v>48</v>
       </c>
       <c r="AM338" t="s">
         <v>54</v>
       </c>
       <c r="AN338" t="s">
+        <v>1753</v>
+      </c>
+      <c r="AO338" t="s">
         <v>1769</v>
       </c>
-      <c r="AO338" t="s">
-        <v>1774</v>
-      </c>
       <c r="AP338" t="s">
-        <v>1771</v>
+        <v>1766</v>
+      </c>
+      <c r="AQ338">
+        <v>4</v>
       </c>
       <c r="AS338" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="339" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B339" t="s">
-        <v>1775</v>
+        <v>1770</v>
       </c>
       <c r="C339" t="s">
         <v>47</v>
       </c>
       <c r="D339">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="E339">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F339">
         <v>4</v>
       </c>
       <c r="G339">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N339">
+        <v>2</v>
+      </c>
+      <c r="O339">
         <v>2</v>
       </c>
       <c r="P339">
@@ -32189,40 +32117,43 @@
       <c r="AC339" t="s">
         <v>48</v>
       </c>
+      <c r="AJ339" t="s">
+        <v>169</v>
+      </c>
+      <c r="AL339" t="s">
+        <v>266</v>
+      </c>
       <c r="AM339" t="s">
         <v>54</v>
       </c>
-      <c r="AN339" t="s">
-        <v>1764</v>
-      </c>
       <c r="AO339" t="s">
-        <v>1776</v>
+        <v>1771</v>
       </c>
       <c r="AP339" t="s">
-        <v>1777</v>
+        <v>1766</v>
       </c>
       <c r="AQ339">
         <v>4</v>
       </c>
       <c r="AS339" t="s">
-        <v>1778</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="340" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B340" t="s">
-        <v>1779</v>
+        <v>1773</v>
       </c>
       <c r="C340" t="s">
         <v>47</v>
       </c>
       <c r="E340">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F340">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G340">
         <v>6</v>
@@ -32230,6 +32161,9 @@
       <c r="N340">
         <v>2</v>
       </c>
+      <c r="O340">
+        <v>2</v>
+      </c>
       <c r="P340">
         <v>1</v>
       </c>
@@ -32251,43 +32185,46 @@
       <c r="AC340" t="s">
         <v>48</v>
       </c>
+      <c r="AJ340" t="s">
+        <v>169</v>
+      </c>
+      <c r="AL340">
+        <v>-128</v>
+      </c>
       <c r="AM340" t="s">
         <v>54</v>
       </c>
-      <c r="AN340" t="s">
-        <v>1764</v>
-      </c>
       <c r="AO340" t="s">
-        <v>1780</v>
+        <v>1774</v>
       </c>
       <c r="AP340" t="s">
-        <v>1777</v>
+        <v>1766</v>
       </c>
       <c r="AQ340">
         <v>4</v>
       </c>
       <c r="AS340" t="s">
-        <v>1778</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="341" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B341" t="s">
-        <v>1781</v>
+        <v>1775</v>
       </c>
       <c r="C341" t="s">
         <v>47</v>
       </c>
       <c r="D341">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E341">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F341">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G341">
         <v>8</v>
@@ -32296,7 +32233,7 @@
         <v>2</v>
       </c>
       <c r="O341">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P341">
         <v>1</v>
@@ -32319,52 +32256,55 @@
       <c r="AC341" t="s">
         <v>48</v>
       </c>
-      <c r="AJ341" t="s">
-        <v>169</v>
-      </c>
-      <c r="AL341" t="s">
+      <c r="AK341" t="s">
         <v>266</v>
       </c>
       <c r="AM341" t="s">
         <v>54</v>
       </c>
+      <c r="AN341" t="s">
+        <v>1753</v>
+      </c>
       <c r="AO341" t="s">
-        <v>1782</v>
+        <v>1776</v>
       </c>
       <c r="AP341" t="s">
-        <v>1777</v>
+        <v>1766</v>
       </c>
       <c r="AQ341">
         <v>4</v>
       </c>
       <c r="AS341" t="s">
-        <v>1783</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="342" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B342" t="s">
-        <v>1784</v>
+        <v>1778</v>
       </c>
       <c r="C342" t="s">
         <v>47</v>
       </c>
+      <c r="D342">
+        <v>650</v>
+      </c>
       <c r="E342">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F342">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G342">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N342">
         <v>2</v>
       </c>
       <c r="O342">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P342">
         <v>1</v>
@@ -32390,67 +32330,70 @@
       <c r="AJ342" t="s">
         <v>169</v>
       </c>
-      <c r="AL342">
-        <v>-128</v>
+      <c r="AL342" t="s">
+        <v>266</v>
       </c>
       <c r="AM342" t="s">
         <v>54</v>
       </c>
       <c r="AO342" t="s">
-        <v>1785</v>
+        <v>1779</v>
       </c>
       <c r="AP342" t="s">
-        <v>1777</v>
+        <v>1766</v>
       </c>
       <c r="AQ342">
         <v>4</v>
       </c>
       <c r="AS342" t="s">
-        <v>1783</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="343" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B343" t="s">
-        <v>1786</v>
+        <v>1780</v>
       </c>
       <c r="C343" t="s">
         <v>47</v>
       </c>
       <c r="D343">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E343">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F343">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G343">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N343">
         <v>2</v>
       </c>
       <c r="O343">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P343">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V343" t="s">
         <v>48</v>
       </c>
       <c r="W343">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="X343">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y343" t="s">
-        <v>49</v>
+        <v>345</v>
+      </c>
+      <c r="AA343" t="s">
+        <v>48</v>
       </c>
       <c r="AB343" t="s">
         <v>73</v>
@@ -32458,46 +32401,55 @@
       <c r="AC343" t="s">
         <v>48</v>
       </c>
-      <c r="AK343" t="s">
+      <c r="AD343" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AG343" t="s">
+        <v>1190</v>
+      </c>
+      <c r="AJ343" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL343" t="s">
         <v>266</v>
       </c>
       <c r="AM343" t="s">
         <v>54</v>
       </c>
       <c r="AN343" t="s">
-        <v>1764</v>
+        <v>1782</v>
       </c>
       <c r="AO343" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="AP343" t="s">
-        <v>1777</v>
+        <v>1784</v>
       </c>
       <c r="AQ343">
         <v>4</v>
       </c>
       <c r="AS343" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="344" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B344" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="C344" t="s">
         <v>47</v>
       </c>
       <c r="D344">
-        <v>650</v>
+        <v>1100</v>
       </c>
       <c r="E344">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F344">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G344">
         <v>4</v>
@@ -32506,22 +32458,25 @@
         <v>2</v>
       </c>
       <c r="O344">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P344">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V344" t="s">
         <v>48</v>
       </c>
       <c r="W344">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="X344">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y344" t="s">
-        <v>49</v>
+        <v>345</v>
+      </c>
+      <c r="AA344" t="s">
+        <v>48</v>
       </c>
       <c r="AB344" t="s">
         <v>73</v>
@@ -32529,46 +32484,52 @@
       <c r="AC344" t="s">
         <v>48</v>
       </c>
+      <c r="AD344" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AF344" t="s">
+        <v>1190</v>
+      </c>
       <c r="AJ344" t="s">
-        <v>169</v>
-      </c>
-      <c r="AL344" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK344" t="s">
         <v>266</v>
       </c>
       <c r="AM344" t="s">
         <v>54</v>
       </c>
       <c r="AO344" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
       <c r="AP344" t="s">
-        <v>1777</v>
+        <v>1788</v>
       </c>
       <c r="AQ344">
         <v>4</v>
       </c>
       <c r="AS344" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="345" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B345" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="C345" t="s">
         <v>47</v>
       </c>
       <c r="D345">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E345">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F345">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G345">
         <v>4</v>
@@ -32577,7 +32538,7 @@
         <v>2</v>
       </c>
       <c r="O345">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P345">
         <v>4</v>
@@ -32604,7 +32565,7 @@
         <v>48</v>
       </c>
       <c r="AD345" t="s">
-        <v>1792</v>
+        <v>1781</v>
       </c>
       <c r="AG345" t="s">
         <v>1190</v>
@@ -32618,40 +32579,37 @@
       <c r="AM345" t="s">
         <v>54</v>
       </c>
-      <c r="AN345" t="s">
-        <v>1793</v>
-      </c>
       <c r="AO345" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="AP345" t="s">
-        <v>1795</v>
+        <v>1791</v>
       </c>
       <c r="AQ345">
         <v>4</v>
       </c>
       <c r="AS345" t="s">
-        <v>1796</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="346" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B346" t="s">
-        <v>1797</v>
+        <v>1792</v>
       </c>
       <c r="C346" t="s">
         <v>47</v>
       </c>
       <c r="D346">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="E346">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F346">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G346">
         <v>4</v>
@@ -32660,7 +32618,7 @@
         <v>2</v>
       </c>
       <c r="O346">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P346">
         <v>4</v>
@@ -32687,7 +32645,7 @@
         <v>48</v>
       </c>
       <c r="AD346" t="s">
-        <v>1792</v>
+        <v>1781</v>
       </c>
       <c r="AF346" t="s">
         <v>1190</v>
@@ -32701,49 +32659,46 @@
       <c r="AM346" t="s">
         <v>54</v>
       </c>
+      <c r="AN346" t="s">
+        <v>1793</v>
+      </c>
       <c r="AO346" t="s">
-        <v>1798</v>
+        <v>1794</v>
       </c>
       <c r="AP346" t="s">
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="AQ346">
         <v>4</v>
       </c>
       <c r="AS346" t="s">
-        <v>1796</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="347" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B347" t="s">
-        <v>1800</v>
+        <v>1796</v>
       </c>
       <c r="C347" t="s">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="D347">
-        <v>1100</v>
-      </c>
-      <c r="E347">
-        <v>8</v>
-      </c>
-      <c r="F347">
-        <v>8</v>
+        <v>1200</v>
+      </c>
+      <c r="E347" t="s">
+        <v>65</v>
       </c>
       <c r="G347">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N347">
         <v>2</v>
       </c>
-      <c r="O347">
-        <v>8</v>
-      </c>
-      <c r="P347">
-        <v>4</v>
+      <c r="P347" t="s">
+        <v>237</v>
       </c>
       <c r="V347" t="s">
         <v>48</v>
@@ -32752,208 +32707,208 @@
         <v>96</v>
       </c>
       <c r="X347">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y347" t="s">
-        <v>345</v>
-      </c>
-      <c r="AA347" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB347" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC347" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD347" t="s">
-        <v>1792</v>
-      </c>
-      <c r="AG347" t="s">
-        <v>1190</v>
-      </c>
-      <c r="AJ347" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL347" t="s">
+        <v>1797</v>
+      </c>
+      <c r="AF347" t="s">
+        <v>362</v>
+      </c>
+      <c r="AK347" t="s">
         <v>266</v>
       </c>
       <c r="AM347" t="s">
         <v>54</v>
       </c>
+      <c r="AN347" t="s">
+        <v>1798</v>
+      </c>
       <c r="AO347" t="s">
+        <v>1799</v>
+      </c>
+      <c r="AP347" t="s">
+        <v>1800</v>
+      </c>
+      <c r="AS347" t="s">
         <v>1801</v>
-      </c>
-      <c r="AP347" t="s">
-        <v>1802</v>
-      </c>
-      <c r="AQ347">
-        <v>4</v>
-      </c>
-      <c r="AS347" t="s">
-        <v>1796</v>
       </c>
     </row>
     <row r="348" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B348" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="C348" t="s">
-        <v>47</v>
+        <v>297</v>
       </c>
       <c r="D348">
-        <v>1400</v>
+        <v>120</v>
       </c>
       <c r="E348">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F348">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G348">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="H348">
+        <v>1</v>
       </c>
       <c r="N348">
         <v>2</v>
       </c>
-      <c r="O348">
-        <v>8</v>
-      </c>
       <c r="P348">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V348" t="s">
         <v>48</v>
       </c>
       <c r="W348">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="X348">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y348" t="s">
-        <v>345</v>
+        <v>49</v>
       </c>
       <c r="AA348" t="s">
         <v>48</v>
       </c>
-      <c r="AB348" t="s">
-        <v>73</v>
-      </c>
       <c r="AC348" t="s">
         <v>48</v>
       </c>
-      <c r="AD348" t="s">
-        <v>1792</v>
-      </c>
-      <c r="AF348" t="s">
-        <v>1190</v>
-      </c>
-      <c r="AJ348" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK348" t="s">
-        <v>266</v>
+      <c r="AD348">
+        <v>54</v>
+      </c>
+      <c r="AE348">
+        <v>106</v>
+      </c>
+      <c r="AF348">
+        <v>107</v>
+      </c>
+      <c r="AH348" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI348" t="s">
+        <v>217</v>
       </c>
       <c r="AM348" t="s">
         <v>54</v>
       </c>
       <c r="AN348" t="s">
+        <v>1803</v>
+      </c>
+      <c r="AO348" t="s">
         <v>1804</v>
       </c>
-      <c r="AO348" t="s">
+      <c r="AP348" t="s">
         <v>1805</v>
       </c>
-      <c r="AP348" t="s">
+      <c r="AS348" t="s">
         <v>1806</v>
-      </c>
-      <c r="AQ348">
-        <v>4</v>
-      </c>
-      <c r="AS348" t="s">
-        <v>1796</v>
       </c>
     </row>
     <row r="349" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B349" t="s">
         <v>1807</v>
       </c>
       <c r="C349" t="s">
-        <v>205</v>
+        <v>297</v>
       </c>
       <c r="D349">
-        <v>1200</v>
-      </c>
-      <c r="E349" t="s">
-        <v>65</v>
-      </c>
-      <c r="G349">
-        <v>2</v>
+        <v>170</v>
+      </c>
+      <c r="E349">
+        <v>2</v>
+      </c>
+      <c r="F349">
+        <v>2</v>
+      </c>
+      <c r="H349">
+        <v>1</v>
       </c>
       <c r="N349">
         <v>2</v>
       </c>
-      <c r="P349" t="s">
-        <v>237</v>
+      <c r="P349">
+        <v>1</v>
       </c>
       <c r="V349" t="s">
         <v>48</v>
       </c>
       <c r="W349">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="X349">
         <v>24</v>
       </c>
       <c r="Y349" t="s">
-        <v>1808</v>
-      </c>
-      <c r="AF349" t="s">
-        <v>362</v>
-      </c>
-      <c r="AK349" t="s">
-        <v>266</v>
+        <v>49</v>
+      </c>
+      <c r="AA349" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC349" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD349">
+        <v>54</v>
+      </c>
+      <c r="AE349">
+        <v>106</v>
+      </c>
+      <c r="AF349">
+        <v>107</v>
+      </c>
+      <c r="AH349" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI349" t="s">
+        <v>217</v>
       </c>
       <c r="AM349" t="s">
         <v>54</v>
       </c>
       <c r="AN349" t="s">
+        <v>1803</v>
+      </c>
+      <c r="AO349" t="s">
+        <v>1804</v>
+      </c>
+      <c r="AP349" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AS349" t="s">
         <v>1809</v>
-      </c>
-      <c r="AO349" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AP349" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AS349" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="350" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B350" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="C350" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="D350">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G350">
         <v>1</v>
@@ -32965,7 +32920,7 @@
         <v>2</v>
       </c>
       <c r="P350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V350" t="s">
         <v>48</v>
@@ -32974,60 +32929,60 @@
         <v>192</v>
       </c>
       <c r="X350">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y350" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA350" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC350" t="s">
-        <v>48</v>
+        <v>1811</v>
+      </c>
+      <c r="AB350" t="s">
+        <v>73</v>
       </c>
       <c r="AD350">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="AE350">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="AF350">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="AH350" t="s">
-        <v>217</v>
+        <v>1366</v>
       </c>
       <c r="AI350" t="s">
-        <v>217</v>
+        <v>1812</v>
+      </c>
+      <c r="AK350" t="s">
+        <v>266</v>
       </c>
       <c r="AM350" t="s">
         <v>54</v>
       </c>
       <c r="AN350" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AO350" t="s">
         <v>1814</v>
       </c>
-      <c r="AO350" t="s">
+      <c r="AP350" t="s">
         <v>1815</v>
       </c>
-      <c r="AP350" t="s">
+      <c r="AS350" t="s">
         <v>1816</v>
-      </c>
-      <c r="AS350" t="s">
-        <v>1817</v>
       </c>
     </row>
     <row r="351" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B351" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="C351" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="D351">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="E351">
         <v>2</v>
@@ -33051,75 +33006,78 @@
         <v>192</v>
       </c>
       <c r="X351">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y351" t="s">
-        <v>49</v>
+        <v>1818</v>
+      </c>
+      <c r="Z351" t="s">
+        <v>272</v>
       </c>
       <c r="AA351" t="s">
         <v>48</v>
       </c>
-      <c r="AC351" t="s">
-        <v>48</v>
+      <c r="AB351" t="s">
+        <v>73</v>
       </c>
       <c r="AD351">
         <v>54</v>
       </c>
       <c r="AE351">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AF351">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AH351" t="s">
-        <v>217</v>
+        <v>452</v>
       </c>
       <c r="AI351" t="s">
-        <v>217</v>
+        <v>53</v>
       </c>
       <c r="AM351" t="s">
         <v>54</v>
       </c>
       <c r="AN351" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="AO351" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="AP351" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="AS351" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="352" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B352" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="C352" t="s">
         <v>271</v>
       </c>
       <c r="D352">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E352">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F352">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G352">
         <v>1</v>
       </c>
       <c r="H352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N352">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P352">
         <v>2</v>
@@ -33134,7 +33092,7 @@
         <v>32</v>
       </c>
       <c r="Y352" t="s">
-        <v>1822</v>
+        <v>1811</v>
       </c>
       <c r="AB352" t="s">
         <v>73</v>
@@ -33152,7 +33110,7 @@
         <v>1366</v>
       </c>
       <c r="AI352" t="s">
-        <v>1823</v>
+        <v>1812</v>
       </c>
       <c r="AK352" t="s">
         <v>266</v>
@@ -33161,45 +33119,48 @@
         <v>54</v>
       </c>
       <c r="AN352" t="s">
+        <v>1813</v>
+      </c>
+      <c r="AO352" t="s">
         <v>1824</v>
       </c>
-      <c r="AO352" t="s">
+      <c r="AP352" t="s">
         <v>1825</v>
       </c>
-      <c r="AP352" t="s">
+      <c r="AS352" t="s">
         <v>1826</v>
-      </c>
-      <c r="AS352" t="s">
-        <v>1827</v>
       </c>
     </row>
     <row r="353" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B353" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="C353" t="s">
         <v>271</v>
       </c>
       <c r="D353">
-        <v>219</v>
+        <v>330</v>
       </c>
       <c r="E353">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F353">
+        <v>4</v>
+      </c>
+      <c r="G353">
         <v>2</v>
       </c>
       <c r="H353">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N353">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P353">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V353" t="s">
         <v>48</v>
@@ -33211,7 +33172,7 @@
         <v>32</v>
       </c>
       <c r="Y353" t="s">
-        <v>1829</v>
+        <v>1818</v>
       </c>
       <c r="Z353" t="s">
         <v>272</v>
@@ -33222,6 +33183,9 @@
       <c r="AB353" t="s">
         <v>73</v>
       </c>
+      <c r="AC353" t="s">
+        <v>1828</v>
+      </c>
       <c r="AD353">
         <v>54</v>
       </c>
@@ -33241,30 +33205,30 @@
         <v>54</v>
       </c>
       <c r="AN353" t="s">
+        <v>1819</v>
+      </c>
+      <c r="AO353" t="s">
+        <v>1829</v>
+      </c>
+      <c r="AP353" t="s">
         <v>1830</v>
       </c>
-      <c r="AO353" t="s">
+      <c r="AS353" t="s">
         <v>1831</v>
-      </c>
-      <c r="AP353" t="s">
-        <v>1832</v>
-      </c>
-      <c r="AS353" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="354" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B354" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="C354" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D354">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E354">
         <v>4</v>
@@ -33294,7 +33258,7 @@
         <v>32</v>
       </c>
       <c r="Y354" t="s">
-        <v>1822</v>
+        <v>1811</v>
       </c>
       <c r="AB354" t="s">
         <v>73</v>
@@ -33312,7 +33276,7 @@
         <v>1366</v>
       </c>
       <c r="AI354" t="s">
-        <v>1823</v>
+        <v>1812</v>
       </c>
       <c r="AK354" t="s">
         <v>266</v>
@@ -33321,63 +33285,60 @@
         <v>54</v>
       </c>
       <c r="AN354" t="s">
-        <v>1824</v>
+        <v>1813</v>
       </c>
       <c r="AO354" t="s">
+        <v>1833</v>
+      </c>
+      <c r="AP354" t="s">
+        <v>1834</v>
+      </c>
+      <c r="AS354" t="s">
         <v>1835</v>
-      </c>
-      <c r="AP354" t="s">
-        <v>1836</v>
-      </c>
-      <c r="AS354" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="355" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B355" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="C355" t="s">
-        <v>271</v>
+        <v>381</v>
       </c>
       <c r="D355">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="E355">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F355">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G355">
-        <v>2</v>
-      </c>
-      <c r="H355">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N355">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="O355">
+        <v>1</v>
       </c>
       <c r="P355">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V355" t="s">
         <v>48</v>
       </c>
       <c r="W355">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="X355">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y355" t="s">
-        <v>1829</v>
-      </c>
-      <c r="Z355" t="s">
-        <v>272</v>
+        <v>49</v>
       </c>
       <c r="AA355" t="s">
         <v>48</v>
@@ -33386,131 +33347,89 @@
         <v>73</v>
       </c>
       <c r="AC355" t="s">
-        <v>1839</v>
-      </c>
-      <c r="AD355">
-        <v>54</v>
-      </c>
-      <c r="AE355">
-        <v>102</v>
-      </c>
-      <c r="AF355">
-        <v>105</v>
-      </c>
-      <c r="AH355" t="s">
-        <v>452</v>
-      </c>
-      <c r="AI355" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="AM355" t="s">
         <v>54</v>
       </c>
       <c r="AN355" t="s">
-        <v>1830</v>
+        <v>1837</v>
       </c>
       <c r="AO355" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="AP355" t="s">
-        <v>1841</v>
-      </c>
-      <c r="AS355" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="356" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1754</v>
+        <v>1743</v>
       </c>
       <c r="B356" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="C356" t="s">
-        <v>257</v>
+        <v>381</v>
       </c>
       <c r="D356">
-        <v>800</v>
-      </c>
-      <c r="E356">
-        <v>4</v>
-      </c>
-      <c r="F356">
-        <v>4</v>
-      </c>
-      <c r="G356">
-        <v>1</v>
-      </c>
-      <c r="H356">
-        <v>2</v>
+        <v>249</v>
+      </c>
+      <c r="E356" t="s">
+        <v>237</v>
+      </c>
+      <c r="F356" t="s">
+        <v>237</v>
       </c>
       <c r="N356">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P356">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V356" t="s">
         <v>48</v>
       </c>
       <c r="W356">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="X356">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y356" t="s">
-        <v>1822</v>
+        <v>49</v>
+      </c>
+      <c r="AA356" t="s">
+        <v>48</v>
       </c>
       <c r="AB356" t="s">
         <v>73</v>
       </c>
-      <c r="AD356">
-        <v>78</v>
-      </c>
-      <c r="AE356">
-        <v>115</v>
-      </c>
-      <c r="AF356">
-        <v>125</v>
-      </c>
-      <c r="AH356" t="s">
-        <v>1366</v>
-      </c>
-      <c r="AI356" t="s">
-        <v>1823</v>
-      </c>
-      <c r="AK356" t="s">
-        <v>266</v>
+      <c r="AC356" t="s">
+        <v>48</v>
       </c>
       <c r="AM356" t="s">
         <v>54</v>
       </c>
-      <c r="AN356" t="s">
-        <v>1824</v>
-      </c>
       <c r="AO356" t="s">
+        <v>1841</v>
+      </c>
+      <c r="AP356" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="357" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B357" t="s">
         <v>1844</v>
       </c>
-      <c r="AP356" t="s">
-        <v>1845</v>
-      </c>
-      <c r="AS356" t="s">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="357" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
-        <v>1754</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1847</v>
-      </c>
       <c r="C357" t="s">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="D357">
-        <v>349</v>
+        <v>99.99</v>
       </c>
       <c r="E357">
         <v>1</v>
@@ -33518,14 +33437,14 @@
       <c r="F357">
         <v>1</v>
       </c>
-      <c r="G357">
+      <c r="G357" t="s">
+        <v>237</v>
+      </c>
+      <c r="H357">
         <v>1</v>
       </c>
       <c r="N357">
-        <v>1</v>
-      </c>
-      <c r="O357">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P357">
         <v>1</v>
@@ -33534,7 +33453,7 @@
         <v>48</v>
       </c>
       <c r="W357">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="X357">
         <v>24</v>
@@ -33545,111 +33464,120 @@
       <c r="AA357" t="s">
         <v>48</v>
       </c>
-      <c r="AB357" t="s">
-        <v>73</v>
-      </c>
       <c r="AC357" t="s">
         <v>48</v>
       </c>
+      <c r="AD357" t="s">
+        <v>1845</v>
+      </c>
+      <c r="AK357" t="s">
+        <v>1846</v>
+      </c>
       <c r="AM357" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN357" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO357" t="s">
+        <v>742</v>
+      </c>
+      <c r="AP357" t="s">
+        <v>1847</v>
+      </c>
+      <c r="AS357" t="s">
         <v>1848</v>
       </c>
-      <c r="AO357" t="s">
+    </row>
+    <row r="358" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B358" t="s">
         <v>1849</v>
       </c>
-      <c r="AP357" t="s">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="358" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
-        <v>1754</v>
-      </c>
-      <c r="B358" t="s">
-        <v>1851</v>
-      </c>
       <c r="C358" t="s">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="D358">
-        <v>249</v>
-      </c>
-      <c r="E358" t="s">
-        <v>237</v>
-      </c>
-      <c r="F358" t="s">
-        <v>237</v>
+        <v>149.99</v>
+      </c>
+      <c r="E358">
+        <v>2</v>
+      </c>
+      <c r="F358">
+        <v>2</v>
+      </c>
+      <c r="H358">
+        <v>1</v>
       </c>
       <c r="N358">
         <v>2</v>
       </c>
       <c r="P358">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V358" t="s">
         <v>48</v>
       </c>
       <c r="W358">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="X358">
         <v>24</v>
       </c>
       <c r="Y358" t="s">
-        <v>49</v>
+        <v>345</v>
       </c>
       <c r="AA358" t="s">
         <v>48</v>
       </c>
-      <c r="AB358" t="s">
-        <v>73</v>
-      </c>
       <c r="AC358" t="s">
         <v>48</v>
       </c>
+      <c r="AD358" t="s">
+        <v>1850</v>
+      </c>
+      <c r="AK358">
+        <v>-120</v>
+      </c>
       <c r="AM358" t="s">
-        <v>54</v>
+        <v>763</v>
       </c>
       <c r="AO358" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="AP358" t="s">
-        <v>1853</v>
+        <v>1847</v>
+      </c>
+      <c r="AS358" t="s">
+        <v>1848</v>
       </c>
     </row>
     <row r="359" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B359" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="C359" t="s">
         <v>297</v>
       </c>
       <c r="D359">
-        <v>99.99</v>
+        <v>149</v>
       </c>
       <c r="E359">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F359">
-        <v>1</v>
-      </c>
-      <c r="G359" t="s">
+        <v>4</v>
+      </c>
+      <c r="H359" t="s">
         <v>237</v>
       </c>
-      <c r="H359">
-        <v>1</v>
-      </c>
       <c r="N359">
         <v>2</v>
       </c>
       <c r="P359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V359" t="s">
         <v>48</v>
@@ -33670,116 +33598,131 @@
         <v>48</v>
       </c>
       <c r="AD359" t="s">
-        <v>1856</v>
+        <v>1850</v>
       </c>
       <c r="AK359" t="s">
-        <v>1857</v>
+        <v>1846</v>
       </c>
       <c r="AM359" t="s">
         <v>260</v>
       </c>
       <c r="AO359" t="s">
-        <v>742</v>
+        <v>1853</v>
       </c>
       <c r="AP359" t="s">
-        <v>1858</v>
+        <v>1847</v>
       </c>
       <c r="AS359" t="s">
-        <v>1859</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="360" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B360" t="s">
         <v>1854</v>
       </c>
-      <c r="B360" t="s">
-        <v>1860</v>
-      </c>
       <c r="C360" t="s">
-        <v>297</v>
+        <v>47</v>
       </c>
       <c r="D360">
-        <v>149.99</v>
+        <v>599</v>
       </c>
       <c r="E360">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F360">
-        <v>2</v>
-      </c>
-      <c r="H360">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="G360">
+        <v>4</v>
+      </c>
+      <c r="H360" t="s">
+        <v>65</v>
       </c>
       <c r="N360">
         <v>2</v>
       </c>
+      <c r="O360">
+        <v>2</v>
+      </c>
       <c r="P360">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V360" t="s">
         <v>48</v>
       </c>
       <c r="W360">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="X360">
         <v>24</v>
       </c>
       <c r="Y360" t="s">
-        <v>345</v>
+        <v>49</v>
       </c>
       <c r="AA360" t="s">
         <v>48</v>
       </c>
-      <c r="AC360" t="s">
-        <v>48</v>
+      <c r="AB360" t="s">
+        <v>73</v>
       </c>
       <c r="AD360" t="s">
-        <v>1861</v>
-      </c>
-      <c r="AK360">
-        <v>-120</v>
+        <v>1855</v>
+      </c>
+      <c r="AK360" t="s">
+        <v>266</v>
       </c>
       <c r="AM360" t="s">
-        <v>763</v>
+        <v>54</v>
       </c>
       <c r="AO360" t="s">
-        <v>1862</v>
+        <v>1856</v>
       </c>
       <c r="AP360" t="s">
+        <v>1857</v>
+      </c>
+      <c r="AQ360">
+        <v>4</v>
+      </c>
+      <c r="AS360" t="s">
         <v>1858</v>
-      </c>
-      <c r="AS360" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="361" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B361" t="s">
-        <v>1863</v>
+        <v>1859</v>
       </c>
       <c r="C361" t="s">
-        <v>297</v>
+        <v>47</v>
       </c>
       <c r="D361">
-        <v>149</v>
+        <v>999.99</v>
       </c>
       <c r="E361">
+        <v>16</v>
+      </c>
+      <c r="F361">
+        <v>16</v>
+      </c>
+      <c r="G361">
         <v>4</v>
       </c>
-      <c r="F361">
-        <v>4</v>
-      </c>
-      <c r="H361" t="s">
-        <v>237</v>
+      <c r="H361">
+        <v>2</v>
       </c>
       <c r="N361">
         <v>2</v>
       </c>
+      <c r="O361">
+        <v>6</v>
+      </c>
       <c r="P361">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V361" t="s">
         <v>48</v>
@@ -33793,70 +33736,73 @@
       <c r="Y361" t="s">
         <v>49</v>
       </c>
-      <c r="AA361" t="s">
-        <v>48</v>
+      <c r="AB361" t="s">
+        <v>73</v>
       </c>
       <c r="AC361" t="s">
         <v>48</v>
       </c>
-      <c r="AD361" t="s">
+      <c r="AD361">
+        <v>60</v>
+      </c>
+      <c r="AK361">
+        <v>-128</v>
+      </c>
+      <c r="AM361" t="s">
+        <v>282</v>
+      </c>
+      <c r="AO361" t="s">
+        <v>1860</v>
+      </c>
+      <c r="AP361" t="s">
         <v>1861</v>
       </c>
-      <c r="AK361" t="s">
-        <v>1857</v>
-      </c>
-      <c r="AM361" t="s">
-        <v>260</v>
-      </c>
-      <c r="AO361" t="s">
-        <v>1864</v>
-      </c>
-      <c r="AP361" t="s">
-        <v>1858</v>
+      <c r="AQ361">
+        <v>4</v>
       </c>
       <c r="AS361" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="362" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B362" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="C362" t="s">
         <v>47</v>
       </c>
       <c r="D362">
-        <v>599</v>
+        <v>799.99</v>
       </c>
       <c r="E362">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F362">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G362">
         <v>4</v>
       </c>
-      <c r="H362" t="s">
-        <v>65</v>
+      <c r="H362">
+        <v>2</v>
       </c>
       <c r="N362">
         <v>2</v>
       </c>
       <c r="O362">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P362">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V362" t="s">
         <v>48</v>
       </c>
       <c r="W362">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="X362">
         <v>24</v>
@@ -33864,141 +33810,135 @@
       <c r="Y362" t="s">
         <v>49</v>
       </c>
-      <c r="AA362" t="s">
-        <v>48</v>
-      </c>
       <c r="AB362" t="s">
         <v>73</v>
       </c>
+      <c r="AC362" t="s">
+        <v>48</v>
+      </c>
       <c r="AD362" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AK362">
+        <v>-128</v>
+      </c>
+      <c r="AM362" t="s">
+        <v>1864</v>
+      </c>
+      <c r="AO362" t="s">
+        <v>1865</v>
+      </c>
+      <c r="AP362" t="s">
         <v>1866</v>
-      </c>
-      <c r="AK362" t="s">
-        <v>266</v>
-      </c>
-      <c r="AM362" t="s">
-        <v>54</v>
-      </c>
-      <c r="AO362" t="s">
-        <v>1867</v>
-      </c>
-      <c r="AP362" t="s">
-        <v>1868</v>
       </c>
       <c r="AQ362">
         <v>4</v>
       </c>
       <c r="AS362" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="363" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B363" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="C363" t="s">
         <v>47</v>
       </c>
       <c r="D363">
-        <v>999.99</v>
+        <v>399.99</v>
       </c>
       <c r="E363">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F363">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G363">
-        <v>4</v>
-      </c>
-      <c r="H363">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H363" t="s">
+        <v>65</v>
       </c>
       <c r="N363">
         <v>2</v>
       </c>
-      <c r="O363">
-        <v>6</v>
-      </c>
-      <c r="P363">
-        <v>7</v>
+      <c r="P363" t="s">
+        <v>65</v>
       </c>
       <c r="V363" t="s">
         <v>48</v>
       </c>
       <c r="W363">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="X363">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y363" t="s">
         <v>49</v>
       </c>
+      <c r="Z363" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA363" t="s">
+        <v>48</v>
+      </c>
       <c r="AB363" t="s">
         <v>73</v>
       </c>
       <c r="AC363" t="s">
         <v>48</v>
       </c>
-      <c r="AD363">
-        <v>60</v>
-      </c>
-      <c r="AK363">
-        <v>-128</v>
+      <c r="AK363" t="s">
+        <v>1846</v>
       </c>
       <c r="AM363" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="AO363" t="s">
+        <v>1869</v>
+      </c>
+      <c r="AP363" t="s">
+        <v>1870</v>
+      </c>
+      <c r="AS363" t="s">
         <v>1871</v>
-      </c>
-      <c r="AP363" t="s">
-        <v>1872</v>
-      </c>
-      <c r="AQ363">
-        <v>4</v>
-      </c>
-      <c r="AS363" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="364" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B364" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="C364" t="s">
         <v>47</v>
       </c>
       <c r="D364">
-        <v>799.99</v>
+        <v>499</v>
       </c>
       <c r="E364">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F364">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G364">
+        <v>2</v>
+      </c>
+      <c r="H364" t="s">
+        <v>65</v>
+      </c>
+      <c r="N364">
+        <v>2</v>
+      </c>
+      <c r="P364">
         <v>4</v>
-      </c>
-      <c r="H364">
-        <v>2</v>
-      </c>
-      <c r="N364">
-        <v>2</v>
-      </c>
-      <c r="O364">
-        <v>6</v>
-      </c>
-      <c r="P364">
-        <v>1</v>
       </c>
       <c r="V364" t="s">
         <v>48</v>
@@ -34012,82 +33952,73 @@
       <c r="Y364" t="s">
         <v>49</v>
       </c>
+      <c r="AA364" t="s">
+        <v>48</v>
+      </c>
       <c r="AB364" t="s">
         <v>73</v>
       </c>
-      <c r="AC364" t="s">
-        <v>48</v>
-      </c>
       <c r="AD364" t="s">
-        <v>1866</v>
-      </c>
-      <c r="AK364">
-        <v>-128</v>
+        <v>1873</v>
+      </c>
+      <c r="AK364" t="s">
+        <v>1874</v>
       </c>
       <c r="AM364" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO364" t="s">
         <v>1875</v>
       </c>
-      <c r="AO364" t="s">
+      <c r="AP364" t="s">
         <v>1876</v>
       </c>
-      <c r="AP364" t="s">
+      <c r="AS364" t="s">
         <v>1877</v>
-      </c>
-      <c r="AQ364">
-        <v>4</v>
-      </c>
-      <c r="AS364" t="s">
-        <v>1878</v>
       </c>
     </row>
     <row r="365" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B365" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="C365" t="s">
         <v>47</v>
       </c>
       <c r="D365">
-        <v>399.99</v>
+        <v>699.99</v>
       </c>
       <c r="E365">
+        <v>8</v>
+      </c>
+      <c r="F365">
+        <v>8</v>
+      </c>
+      <c r="G365">
         <v>4</v>
       </c>
-      <c r="F365">
-        <v>4</v>
-      </c>
-      <c r="G365">
-        <v>8</v>
-      </c>
-      <c r="H365" t="s">
-        <v>65</v>
+      <c r="H365">
+        <v>2</v>
       </c>
       <c r="N365">
         <v>2</v>
       </c>
-      <c r="P365" t="s">
-        <v>65</v>
+      <c r="P365">
+        <v>5</v>
       </c>
       <c r="V365" t="s">
         <v>48</v>
       </c>
       <c r="W365">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="X365">
         <v>32</v>
       </c>
       <c r="Y365" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z365" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA365" t="s">
-        <v>48</v>
+        <v>345</v>
       </c>
       <c r="AB365" t="s">
         <v>73</v>
@@ -34095,238 +34026,199 @@
       <c r="AC365" t="s">
         <v>48</v>
       </c>
-      <c r="AK365" t="s">
-        <v>1857</v>
+      <c r="AD365" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AK365">
+        <v>-128</v>
       </c>
       <c r="AM365" t="s">
-        <v>260</v>
+        <v>1864</v>
       </c>
       <c r="AO365" t="s">
+        <v>1879</v>
+      </c>
+      <c r="AP365" t="s">
         <v>1880</v>
       </c>
-      <c r="AP365" t="s">
+      <c r="AS365" t="s">
         <v>1881</v>
-      </c>
-      <c r="AS365" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="366" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B366" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="C366" t="s">
         <v>47</v>
       </c>
       <c r="D366">
-        <v>499</v>
+        <v>249.99</v>
       </c>
       <c r="E366">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F366">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G366">
-        <v>2</v>
-      </c>
-      <c r="H366" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="N366">
         <v>2</v>
       </c>
+      <c r="O366">
+        <v>2</v>
+      </c>
       <c r="P366">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V366" t="s">
         <v>48</v>
       </c>
       <c r="W366">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="X366">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y366" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA366" t="s">
+        <v>345</v>
+      </c>
+      <c r="Z366" t="s">
         <v>48</v>
       </c>
       <c r="AB366" t="s">
         <v>73</v>
       </c>
-      <c r="AD366" t="s">
+      <c r="AC366" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK366">
+        <v>-120</v>
+      </c>
+      <c r="AM366" t="s">
+        <v>763</v>
+      </c>
+      <c r="AO366" t="s">
+        <v>1883</v>
+      </c>
+      <c r="AP366" t="s">
         <v>1884</v>
       </c>
-      <c r="AK366" t="s">
+      <c r="AS366" t="s">
         <v>1885</v>
-      </c>
-      <c r="AM366" t="s">
-        <v>291</v>
-      </c>
-      <c r="AO366" t="s">
-        <v>1886</v>
-      </c>
-      <c r="AP366" t="s">
-        <v>1887</v>
-      </c>
-      <c r="AS366" t="s">
-        <v>1888</v>
       </c>
     </row>
     <row r="367" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B367" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="C367" t="s">
-        <v>47</v>
-      </c>
-      <c r="D367">
-        <v>699.99</v>
-      </c>
-      <c r="E367">
-        <v>8</v>
-      </c>
-      <c r="F367">
-        <v>8</v>
-      </c>
-      <c r="G367">
-        <v>4</v>
-      </c>
-      <c r="H367">
-        <v>2</v>
-      </c>
-      <c r="N367">
-        <v>2</v>
+        <v>381</v>
       </c>
       <c r="P367">
-        <v>5</v>
-      </c>
-      <c r="V367" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="W367">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="X367">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y367" t="s">
-        <v>345</v>
+        <v>49</v>
       </c>
       <c r="AB367" t="s">
         <v>73</v>
       </c>
-      <c r="AC367" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD367" t="s">
-        <v>1866</v>
-      </c>
-      <c r="AK367">
-        <v>-128</v>
-      </c>
       <c r="AM367" t="s">
-        <v>1875</v>
+        <v>54</v>
+      </c>
+      <c r="AN367" t="s">
+        <v>1887</v>
       </c>
       <c r="AO367" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="AP367" t="s">
-        <v>1891</v>
-      </c>
-      <c r="AS367" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="368" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B368" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C368" t="s">
+        <v>381</v>
+      </c>
+      <c r="D368">
+        <v>200</v>
+      </c>
+      <c r="E368">
+        <v>4</v>
+      </c>
+      <c r="P368">
+        <v>4</v>
+      </c>
+      <c r="V368" t="s">
+        <v>48</v>
+      </c>
+      <c r="W368">
+        <v>44.1</v>
+      </c>
+      <c r="X368">
+        <v>16</v>
+      </c>
+      <c r="Y368" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC368" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD368">
+        <v>70</v>
+      </c>
+      <c r="AM368" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO368" t="s">
+        <v>1891</v>
+      </c>
+      <c r="AP368" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="369" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B369" t="s">
         <v>1893</v>
-      </c>
-      <c r="C368" t="s">
-        <v>47</v>
-      </c>
-      <c r="D368">
-        <v>249.99</v>
-      </c>
-      <c r="E368">
-        <v>2</v>
-      </c>
-      <c r="F368">
-        <v>2</v>
-      </c>
-      <c r="G368">
-        <v>8</v>
-      </c>
-      <c r="N368">
-        <v>2</v>
-      </c>
-      <c r="O368">
-        <v>2</v>
-      </c>
-      <c r="P368">
-        <v>1</v>
-      </c>
-      <c r="V368" t="s">
-        <v>48</v>
-      </c>
-      <c r="W368">
-        <v>48</v>
-      </c>
-      <c r="X368">
-        <v>32</v>
-      </c>
-      <c r="Y368" t="s">
-        <v>345</v>
-      </c>
-      <c r="Z368" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB368" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC368" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK368">
-        <v>-120</v>
-      </c>
-      <c r="AM368" t="s">
-        <v>763</v>
-      </c>
-      <c r="AO368" t="s">
-        <v>1894</v>
-      </c>
-      <c r="AP368" t="s">
-        <v>1895</v>
-      </c>
-      <c r="AS368" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="369" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1897</v>
       </c>
       <c r="C369" t="s">
         <v>381</v>
       </c>
+      <c r="D369">
+        <v>179.99</v>
+      </c>
+      <c r="E369">
+        <v>4</v>
+      </c>
       <c r="P369">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="V369" t="s">
+        <v>48</v>
       </c>
       <c r="W369">
         <v>48</v>
@@ -34335,42 +34227,57 @@
         <v>24</v>
       </c>
       <c r="Y369" t="s">
-        <v>49</v>
+        <v>345</v>
       </c>
       <c r="AB369" t="s">
         <v>73</v>
       </c>
+      <c r="AC369" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD369" t="s">
+        <v>1894</v>
+      </c>
+      <c r="AK369">
+        <v>-125</v>
+      </c>
       <c r="AM369" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN369" t="s">
+        <v>763</v>
+      </c>
+      <c r="AO369" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AP369" t="s">
+        <v>1896</v>
+      </c>
+      <c r="AS369" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="370" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B370" t="s">
         <v>1898</v>
-      </c>
-      <c r="AO369" t="s">
-        <v>1899</v>
-      </c>
-      <c r="AP369" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="370" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A370" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1901</v>
       </c>
       <c r="C370" t="s">
         <v>381</v>
       </c>
       <c r="D370">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E370">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="G370">
+        <v>1</v>
+      </c>
+      <c r="N370">
+        <v>2</v>
       </c>
       <c r="P370">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V370" t="s">
         <v>48</v>
@@ -34390,143 +34297,188 @@
       <c r="AD370">
         <v>70</v>
       </c>
+      <c r="AK370" t="s">
+        <v>1899</v>
+      </c>
       <c r="AM370" t="s">
-        <v>260</v>
+        <v>54</v>
       </c>
       <c r="AO370" t="s">
+        <v>1900</v>
+      </c>
+      <c r="AP370" t="s">
+        <v>1901</v>
+      </c>
+      <c r="AS370" t="s">
         <v>1902</v>
-      </c>
-      <c r="AP370" t="s">
-        <v>1903</v>
       </c>
     </row>
     <row r="371" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B371" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="C371" t="s">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="D371">
-        <v>179.99</v>
+        <v>159.99</v>
       </c>
       <c r="E371">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F371">
+        <v>2</v>
+      </c>
+      <c r="H371">
+        <v>1</v>
+      </c>
+      <c r="N371">
+        <v>2</v>
       </c>
       <c r="P371">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V371" t="s">
         <v>48</v>
       </c>
       <c r="W371">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="X371">
         <v>24</v>
       </c>
       <c r="Y371" t="s">
-        <v>345</v>
-      </c>
-      <c r="AB371" t="s">
-        <v>73</v>
+        <v>49</v>
+      </c>
+      <c r="Z371" t="s">
+        <v>48</v>
       </c>
       <c r="AC371" t="s">
         <v>48</v>
       </c>
       <c r="AD371" t="s">
+        <v>1904</v>
+      </c>
+      <c r="AK371">
+        <v>-119.5</v>
+      </c>
+      <c r="AM371" t="s">
+        <v>291</v>
+      </c>
+      <c r="AN371" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AO371" t="s">
         <v>1905</v>
       </c>
-      <c r="AK371">
-        <v>-125</v>
-      </c>
-      <c r="AM371" t="s">
-        <v>763</v>
-      </c>
-      <c r="AO371" t="s">
+      <c r="AP371" t="s">
         <v>1906</v>
       </c>
-      <c r="AP371" t="s">
+      <c r="AR371">
+        <v>2</v>
+      </c>
+      <c r="AS371" t="s">
         <v>1907</v>
-      </c>
-      <c r="AS371" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="372" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B372" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="C372" t="s">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="D372">
-        <v>500</v>
+        <v>189.99</v>
       </c>
       <c r="E372">
-        <v>6</v>
-      </c>
-      <c r="G372">
+        <v>2</v>
+      </c>
+      <c r="F372">
+        <v>2</v>
+      </c>
+      <c r="H372">
+        <v>1</v>
+      </c>
+      <c r="K372">
+        <v>1</v>
+      </c>
+      <c r="L372">
         <v>1</v>
       </c>
       <c r="N372">
         <v>2</v>
       </c>
       <c r="P372">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="S372">
+        <v>1</v>
+      </c>
+      <c r="T372">
+        <v>1</v>
       </c>
       <c r="V372" t="s">
         <v>48</v>
       </c>
       <c r="W372">
-        <v>44.1</v>
+        <v>96</v>
       </c>
       <c r="X372">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Y372" t="s">
         <v>49</v>
       </c>
+      <c r="Z372" t="s">
+        <v>48</v>
+      </c>
       <c r="AC372" t="s">
         <v>48</v>
       </c>
-      <c r="AD372">
-        <v>70</v>
-      </c>
-      <c r="AK372" t="s">
+      <c r="AD372" t="s">
+        <v>1904</v>
+      </c>
+      <c r="AK372">
+        <v>-119.5</v>
+      </c>
+      <c r="AM372" t="s">
+        <v>291</v>
+      </c>
+      <c r="AN372" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AO372" t="s">
+        <v>1909</v>
+      </c>
+      <c r="AP372" t="s">
         <v>1910</v>
       </c>
-      <c r="AM372" t="s">
-        <v>54</v>
-      </c>
-      <c r="AO372" t="s">
+      <c r="AR372">
+        <v>2</v>
+      </c>
+      <c r="AS372" t="s">
         <v>1911</v>
-      </c>
-      <c r="AP372" t="s">
-        <v>1912</v>
-      </c>
-      <c r="AS372" t="s">
-        <v>1913</v>
       </c>
     </row>
     <row r="373" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1854</v>
+        <v>1843</v>
       </c>
       <c r="B373" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="C373" t="s">
         <v>297</v>
       </c>
       <c r="D373">
-        <v>159.99</v>
+        <v>200</v>
       </c>
       <c r="E373">
         <v>2</v>
@@ -34547,191 +34499,37 @@
         <v>48</v>
       </c>
       <c r="W373">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="X373">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y373" t="s">
         <v>49</v>
       </c>
       <c r="Z373" t="s">
+        <v>272</v>
+      </c>
+      <c r="AA373" t="s">
         <v>48</v>
       </c>
       <c r="AC373" t="s">
         <v>48</v>
       </c>
-      <c r="AD373" t="s">
+      <c r="AL373">
+        <v>-127</v>
+      </c>
+      <c r="AM373" t="s">
+        <v>282</v>
+      </c>
+      <c r="AO373" t="s">
+        <v>1913</v>
+      </c>
+      <c r="AP373" t="s">
+        <v>1914</v>
+      </c>
+      <c r="AS373" t="s">
         <v>1915</v>
-      </c>
-      <c r="AK373">
-        <v>-119.5</v>
-      </c>
-      <c r="AM373" t="s">
-        <v>291</v>
-      </c>
-      <c r="AN373" t="s">
-        <v>1429</v>
-      </c>
-      <c r="AO373" t="s">
-        <v>1916</v>
-      </c>
-      <c r="AP373" t="s">
-        <v>1917</v>
-      </c>
-      <c r="AR373">
-        <v>2</v>
-      </c>
-      <c r="AS373" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="374" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A374" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1919</v>
-      </c>
-      <c r="C374" t="s">
-        <v>297</v>
-      </c>
-      <c r="D374">
-        <v>189.99</v>
-      </c>
-      <c r="E374">
-        <v>2</v>
-      </c>
-      <c r="F374">
-        <v>2</v>
-      </c>
-      <c r="H374">
-        <v>1</v>
-      </c>
-      <c r="K374">
-        <v>1</v>
-      </c>
-      <c r="L374">
-        <v>1</v>
-      </c>
-      <c r="N374">
-        <v>2</v>
-      </c>
-      <c r="P374">
-        <v>1</v>
-      </c>
-      <c r="S374">
-        <v>1</v>
-      </c>
-      <c r="T374">
-        <v>1</v>
-      </c>
-      <c r="V374" t="s">
-        <v>48</v>
-      </c>
-      <c r="W374">
-        <v>96</v>
-      </c>
-      <c r="X374">
-        <v>24</v>
-      </c>
-      <c r="Y374" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z374" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC374" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD374" t="s">
-        <v>1915</v>
-      </c>
-      <c r="AK374">
-        <v>-119.5</v>
-      </c>
-      <c r="AM374" t="s">
-        <v>291</v>
-      </c>
-      <c r="AN374" t="s">
-        <v>1429</v>
-      </c>
-      <c r="AO374" t="s">
-        <v>1920</v>
-      </c>
-      <c r="AP374" t="s">
-        <v>1921</v>
-      </c>
-      <c r="AR374">
-        <v>2</v>
-      </c>
-      <c r="AS374" t="s">
-        <v>1922</v>
-      </c>
-    </row>
-    <row r="375" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A375" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B375" t="s">
-        <v>1923</v>
-      </c>
-      <c r="C375" t="s">
-        <v>297</v>
-      </c>
-      <c r="D375">
-        <v>200</v>
-      </c>
-      <c r="E375">
-        <v>2</v>
-      </c>
-      <c r="F375">
-        <v>2</v>
-      </c>
-      <c r="H375">
-        <v>1</v>
-      </c>
-      <c r="N375">
-        <v>2</v>
-      </c>
-      <c r="P375">
-        <v>1</v>
-      </c>
-      <c r="V375" t="s">
-        <v>48</v>
-      </c>
-      <c r="W375">
-        <v>192</v>
-      </c>
-      <c r="X375">
-        <v>32</v>
-      </c>
-      <c r="Y375" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z375" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA375" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC375" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL375">
-        <v>-127</v>
-      </c>
-      <c r="AM375" t="s">
-        <v>282</v>
-      </c>
-      <c r="AO375" t="s">
-        <v>1924</v>
-      </c>
-      <c r="AP375" t="s">
-        <v>1925</v>
-      </c>
-      <c r="AS375" t="s">
-        <v>1926</v>
       </c>
     </row>
   </sheetData>
@@ -34753,7 +34551,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1927</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -34806,7 +34604,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1928</v>
+        <v>1917</v>
       </c>
       <c r="B8">
         <v>216</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5269" uniqueCount="1918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="1918">
   <si>
     <t>Brand</t>
   </si>
@@ -845,7 +845,7 @@
     <t>-108.0dB (0.00040%)</t>
   </si>
   <si>
-    <t>Synergy Core DSP plug-insbundle</t>
+    <t>Bitwig Studio Essentials / Lifeline Lite Bundle (Excite Audio) / Hawk Phaser, Time Machine (Safari Audio) / Antelope Cosmos (3 months) / Loopcloud (3 months)</t>
   </si>
   <si>
     <t>bus-powered compatible 2ch compact I/O. Synergy Core viareal-time effects. 5-pin DIN MIDI equipped. 2025/12release.</t>
@@ -3800,13 +3800,13 @@
     <t>-81.9dB (0.00800%)</t>
   </si>
   <si>
-    <t>Studio One Artist</t>
+    <t>Fender Studio Pro (6-month trial)</t>
   </si>
   <si>
     <t>2x2, Bus-powered, USB class-compliant, Mix control for direct monitoring</t>
   </si>
   <si>
-    <t>https://www.presonus.com/products/audiobox-usb-96-black</t>
+    <t>https://www.presonus.com/products/audiobox-usb-96-25th-anniversary</t>
   </si>
   <si>
     <t>[ProSound](https://prosound.ixbt.com/interfaces/presonus-audiobox-usb96.shtml) / [ProSound (2)](https://prosound.ixbt.com/interfaces/presonus/usb96/line.shtml) / [ProSound (3)](https://prosound.ixbt.com/interfaces/presonus/usb96/hp.shtml)</t>
@@ -3818,9 +3818,6 @@
     <t>-83.1dB (0.00700%)</t>
   </si>
   <si>
-    <t>Fender Studio Pro (6-month trial)</t>
-  </si>
-  <si>
     <t>2x2 USB-C interface with built-in 100mm touch-sensitive motorized fader and Session Navigator DAW transport/mix control (Mackie Control/HUI protocol); footswitch input for hands-free start/stop (footswitch not included); ADC/DAC converters rated 115dB dynamic range (A-weighted)</t>
   </si>
   <si>
@@ -4349,7 +4346,7 @@
     <t>7 assignable channels, 4 physical + 3 virtual faders, 5.5-inch touchscreen, APHEX processing, SMART pad s (6), 3.5mm TRRS input, Wireless receiver, microSD recording, Quad-core engine, Compact portable design, phones out 250mW, line out max +4dBu</t>
   </si>
   <si>
-    <t>https://rode.com/en/interfaces-mixers/rodecaster-series/rodecaster-duo</t>
+    <t>https://rode.com/en-us/products/rodecaster-duo</t>
   </si>
   <si>
     <t>[Manufacturer](https://rode.com/en-us/products/rodecaster-duo)</t>
@@ -4364,7 +4361,7 @@
     <t>9 assignable channels, 6 physical + 3 virtual faders, 5.5-inch touchscreen, APHEX processing, SMART pad s (8), Wireless receiver, microSD recording, Quad-core engine</t>
   </si>
   <si>
-    <t>https://rode.com/en/interfaces-mixers/rodecaster-series/rodecaster-pro-ii</t>
+    <t>https://rode.com/en-us/products/rodecaster-pro-ii</t>
   </si>
   <si>
     <t>[Manufacturer](https://edge.rode.com/pdf/products/931/RODECaster%20Pro%20II_DataSheet_V02.pdf)</t>
@@ -5153,42 +5150,48 @@
     <t>-102.5dB (0.00075%)</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>610 preamp</t>
+  </si>
+  <si>
+    <t>https://www.uaudio.com/products/volt-1-usb-audio-interface</t>
+  </si>
+  <si>
+    <t>[Manufacturer](https://www.liveforsound.com/product/wp-content/uploads/2022/01/Volt-Specifications.pdf)</t>
+  </si>
+  <si>
+    <t>Volt 176</t>
+  </si>
+  <si>
+    <t>1176compressor built-in</t>
+  </si>
+  <si>
+    <t>https://www.uaudio.com/products/volt-176-usb-audio-interface</t>
+  </si>
+  <si>
+    <t>Volt 2</t>
+  </si>
+  <si>
+    <t>-103.1dB (0.00070%)</t>
+  </si>
+  <si>
+    <t>LUNA, UA plugin bundle (13 titles), Melodyne Essential, Ampeg SVT-VR Classic Bass Bundle, UJAM Virtual Drummer DEEP, UJAM Virtual Bassist DANDY, Splice INSTRUMENT</t>
+  </si>
+  <si>
+    <t>610 preamp mode (1176 as bundled plugin)</t>
+  </si>
+  <si>
+    <t>https://www.uaudio.com/products/volt-2-usb-audio-interface</t>
+  </si>
+  <si>
+    <t>Volt 276</t>
+  </si>
+  <si>
     <t>Ableton Live Lite, LUNA</t>
   </si>
   <si>
-    <t>610 preamp</t>
-  </si>
-  <si>
-    <t>https://www.uaudio.com/products/volt-1-usb-audio-interface</t>
-  </si>
-  <si>
-    <t>[Manufacturer](https://www.liveforsound.com/product/wp-content/uploads/2022/01/Volt-Specifications.pdf)</t>
-  </si>
-  <si>
-    <t>Volt 176</t>
-  </si>
-  <si>
-    <t>1176compressor built-in</t>
-  </si>
-  <si>
-    <t>https://www.uaudio.com/products/volt-176-usb-audio-interface</t>
-  </si>
-  <si>
-    <t>Volt 2</t>
-  </si>
-  <si>
-    <t>-103.1dB (0.00070%)</t>
-  </si>
-  <si>
-    <t>610 preamp mode (1176 as bundled plugin)</t>
-  </si>
-  <si>
-    <t>https://www.uaudio.com/products/volt-2-usb-audio-interface</t>
-  </si>
-  <si>
-    <t>Volt 276</t>
-  </si>
-  <si>
     <t>dual 1176</t>
   </si>
   <si>
@@ -5199,9 +5202,6 @@
   </si>
   <si>
     <t>Volt 4</t>
-  </si>
-  <si>
-    <t>LUNA, UA plugin bundle (9 titles), Ableton Live Lite, Melodyne Essential, UJAM Virtual Drummer DEEP, Ampeg SVT-VR, Softube Marshall Plexi Classic</t>
   </si>
   <si>
     <t>4in/4out, Vintage Mic Preamp mode, MIDI I/O, loopback</t>
@@ -7803,7 +7803,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>279</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>352</v>
       </c>
       <c r="AE57">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AF57" t="s">
         <v>353</v>
@@ -10610,7 +10610,7 @@
         <v>257</v>
       </c>
       <c r="D58">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="E58">
         <v>4</v>
@@ -12251,7 +12251,7 @@
         <v>60</v>
       </c>
       <c r="AE76">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="AF76">
         <v>126.5</v>
@@ -12281,7 +12281,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="77" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>472</v>
       </c>
@@ -12779,7 +12779,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="83" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>509</v>
       </c>
@@ -12906,7 +12906,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="85" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>509</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="86" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>509</v>
       </c>
@@ -15064,7 +15064,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="117" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>659</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="118" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>659</v>
       </c>
@@ -15700,7 +15700,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>685</v>
       </c>
@@ -16040,7 +16040,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="131" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>685</v>
       </c>
@@ -16244,7 +16244,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="134" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>738</v>
       </c>
@@ -17192,7 +17192,7 @@
         <v>205</v>
       </c>
       <c r="D145">
-        <v>2499</v>
+        <v>3329.99</v>
       </c>
       <c r="K145" t="s">
         <v>237</v>
@@ -17239,7 +17239,7 @@
         <v>230</v>
       </c>
       <c r="D146">
-        <v>2999</v>
+        <v>4709.99</v>
       </c>
       <c r="E146">
         <v>8</v>
@@ -18263,7 +18263,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="158" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>879</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="166" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>884</v>
       </c>
@@ -18845,7 +18845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>884</v>
       </c>
@@ -19636,7 +19636,10 @@
         <v>237</v>
       </c>
       <c r="N179">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="O179">
+        <v>2</v>
       </c>
       <c r="P179">
         <v>1</v>
@@ -20842,7 +20845,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="195" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1044</v>
       </c>
@@ -22189,7 +22192,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="213" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1138</v>
       </c>
@@ -22444,7 +22447,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="216" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1158</v>
       </c>
@@ -22984,7 +22987,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="222" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1158</v>
       </c>
@@ -23055,7 +23058,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="223" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1158</v>
       </c>
@@ -23724,7 +23727,7 @@
         <v>297</v>
       </c>
       <c r="D231">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="E231">
         <v>1</v>
@@ -23795,7 +23798,7 @@
         <v>271</v>
       </c>
       <c r="D232">
-        <v>199</v>
+        <v>300</v>
       </c>
       <c r="E232">
         <v>2</v>
@@ -24000,16 +24003,16 @@
         <v>54</v>
       </c>
       <c r="AN234" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AO234" t="s">
         <v>1266</v>
       </c>
-      <c r="AO234" t="s">
+      <c r="AP234" t="s">
         <v>1267</v>
       </c>
-      <c r="AP234" t="s">
+      <c r="AS234" t="s">
         <v>1268</v>
-      </c>
-      <c r="AS234" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="235" spans="1:45" x14ac:dyDescent="0.25">
@@ -24017,7 +24020,7 @@
         <v>1255</v>
       </c>
       <c r="B235" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C235" t="s">
         <v>205</v>
@@ -24095,16 +24098,16 @@
         <v>54</v>
       </c>
       <c r="AN235" t="s">
+        <v>1270</v>
+      </c>
+      <c r="AO235" t="s">
         <v>1271</v>
       </c>
-      <c r="AO235" t="s">
+      <c r="AP235" t="s">
         <v>1272</v>
       </c>
-      <c r="AP235" t="s">
+      <c r="AS235" t="s">
         <v>1273</v>
-      </c>
-      <c r="AS235" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="236" spans="1:45" x14ac:dyDescent="0.25">
@@ -24112,13 +24115,13 @@
         <v>1255</v>
       </c>
       <c r="B236" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C236" t="s">
         <v>297</v>
       </c>
       <c r="D236">
-        <v>262.99</v>
+        <v>199.99</v>
       </c>
       <c r="E236">
         <v>2</v>
@@ -24151,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="Z236" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="AA236" t="s">
         <v>48</v>
@@ -24181,13 +24184,13 @@
         <v>752</v>
       </c>
       <c r="AO236" t="s">
+        <v>1276</v>
+      </c>
+      <c r="AP236" t="s">
         <v>1277</v>
       </c>
-      <c r="AP236" t="s">
+      <c r="AS236" t="s">
         <v>1278</v>
-      </c>
-      <c r="AS236" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="237" spans="1:45" x14ac:dyDescent="0.25">
@@ -24195,7 +24198,7 @@
         <v>1255</v>
       </c>
       <c r="B237" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C237" t="s">
         <v>271</v>
@@ -24261,13 +24264,13 @@
         <v>752</v>
       </c>
       <c r="AO237" t="s">
+        <v>1280</v>
+      </c>
+      <c r="AP237" t="s">
         <v>1281</v>
       </c>
-      <c r="AP237" t="s">
+      <c r="AS237" t="s">
         <v>1282</v>
-      </c>
-      <c r="AS237" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="238" spans="1:45" x14ac:dyDescent="0.25">
@@ -24275,13 +24278,13 @@
         <v>1255</v>
       </c>
       <c r="B238" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C238" t="s">
         <v>381</v>
       </c>
       <c r="D238">
-        <v>99</v>
+        <v>79.99</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -24323,7 +24326,7 @@
         <v>48</v>
       </c>
       <c r="AD238" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="AE238">
         <v>96</v>
@@ -24341,13 +24344,13 @@
         <v>741</v>
       </c>
       <c r="AO238" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AP238" t="s">
         <v>1286</v>
       </c>
-      <c r="AP238" t="s">
+      <c r="AS238" t="s">
         <v>1287</v>
-      </c>
-      <c r="AS238" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="239" spans="1:45" x14ac:dyDescent="0.25">
@@ -24355,7 +24358,7 @@
         <v>1255</v>
       </c>
       <c r="B239" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C239" t="s">
         <v>271</v>
@@ -24418,7 +24421,7 @@
         <v>48</v>
       </c>
       <c r="AD239" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="AE239">
         <v>110</v>
@@ -24442,16 +24445,16 @@
         <v>54</v>
       </c>
       <c r="AN239" t="s">
+        <v>1290</v>
+      </c>
+      <c r="AO239" t="s">
         <v>1291</v>
       </c>
-      <c r="AO239" t="s">
+      <c r="AP239" t="s">
         <v>1292</v>
       </c>
-      <c r="AP239" t="s">
+      <c r="AS239" t="s">
         <v>1293</v>
-      </c>
-      <c r="AS239" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="240" spans="1:45" x14ac:dyDescent="0.25">
@@ -24459,7 +24462,7 @@
         <v>1255</v>
       </c>
       <c r="B240" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C240" t="s">
         <v>271</v>
@@ -24525,7 +24528,7 @@
         <v>48</v>
       </c>
       <c r="AD240" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="AE240">
         <v>110</v>
@@ -24549,16 +24552,16 @@
         <v>54</v>
       </c>
       <c r="AN240" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="AO240" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AP240" t="s">
         <v>1296</v>
       </c>
-      <c r="AP240" t="s">
+      <c r="AS240" t="s">
         <v>1297</v>
-      </c>
-      <c r="AS240" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="241" spans="1:45" x14ac:dyDescent="0.25">
@@ -24566,7 +24569,7 @@
         <v>1255</v>
       </c>
       <c r="B241" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C241" t="s">
         <v>297</v>
@@ -24611,7 +24614,7 @@
         <v>48</v>
       </c>
       <c r="AD241" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="AE241">
         <v>106</v>
@@ -24632,13 +24635,13 @@
         <v>741</v>
       </c>
       <c r="AO241" t="s">
+        <v>1300</v>
+      </c>
+      <c r="AP241" t="s">
         <v>1301</v>
       </c>
-      <c r="AP241" t="s">
+      <c r="AS241" t="s">
         <v>1302</v>
-      </c>
-      <c r="AS241" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="242" spans="1:45" x14ac:dyDescent="0.25">
@@ -24646,7 +24649,7 @@
         <v>1255</v>
       </c>
       <c r="B242" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C242" t="s">
         <v>47</v>
@@ -24691,7 +24694,7 @@
         <v>48</v>
       </c>
       <c r="AD242" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="AF242" t="s">
         <v>516</v>
@@ -24709,19 +24712,19 @@
         <v>54</v>
       </c>
       <c r="AN242" t="s">
+        <v>1305</v>
+      </c>
+      <c r="AO242" t="s">
         <v>1306</v>
       </c>
-      <c r="AO242" t="s">
+      <c r="AP242" t="s">
         <v>1307</v>
       </c>
-      <c r="AP242" t="s">
+      <c r="AQ242">
+        <v>2</v>
+      </c>
+      <c r="AS242" t="s">
         <v>1308</v>
-      </c>
-      <c r="AQ242">
-        <v>2</v>
-      </c>
-      <c r="AS242" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="243" spans="1:45" x14ac:dyDescent="0.25">
@@ -24729,7 +24732,7 @@
         <v>1255</v>
       </c>
       <c r="B243" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C243" t="s">
         <v>47</v>
@@ -24789,19 +24792,19 @@
         <v>54</v>
       </c>
       <c r="AN243" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="AO243" t="s">
+        <v>1310</v>
+      </c>
+      <c r="AP243" t="s">
         <v>1311</v>
       </c>
-      <c r="AP243" t="s">
+      <c r="AQ243">
+        <v>2</v>
+      </c>
+      <c r="AS243" t="s">
         <v>1312</v>
-      </c>
-      <c r="AQ243">
-        <v>2</v>
-      </c>
-      <c r="AS243" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="244" spans="1:45" x14ac:dyDescent="0.25">
@@ -24809,7 +24812,7 @@
         <v>1255</v>
       </c>
       <c r="B244" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C244" t="s">
         <v>47</v>
@@ -24851,7 +24854,7 @@
         <v>48</v>
       </c>
       <c r="AD244" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="AF244" t="s">
         <v>516</v>
@@ -24866,27 +24869,27 @@
         <v>54</v>
       </c>
       <c r="AN244" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="AO244" t="s">
+        <v>1314</v>
+      </c>
+      <c r="AP244" t="s">
         <v>1315</v>
       </c>
-      <c r="AP244" t="s">
+      <c r="AQ244">
+        <v>2</v>
+      </c>
+      <c r="AS244" t="s">
         <v>1316</v>
-      </c>
-      <c r="AQ244">
-        <v>2</v>
-      </c>
-      <c r="AS244" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="245" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B245" t="s">
         <v>1318</v>
-      </c>
-      <c r="B245" t="s">
-        <v>1319</v>
       </c>
       <c r="C245" t="s">
         <v>230</v>
@@ -24976,21 +24979,21 @@
         <v>54</v>
       </c>
       <c r="AO245" t="s">
+        <v>1319</v>
+      </c>
+      <c r="AP245" t="s">
         <v>1320</v>
       </c>
-      <c r="AP245" t="s">
+      <c r="AS245" t="s">
         <v>1321</v>
-      </c>
-      <c r="AS245" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="246" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B246" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C246" t="s">
         <v>230</v>
@@ -25062,21 +25065,21 @@
         <v>54</v>
       </c>
       <c r="AO246" t="s">
+        <v>1323</v>
+      </c>
+      <c r="AP246" t="s">
         <v>1324</v>
       </c>
-      <c r="AP246" t="s">
+      <c r="AS246" t="s">
         <v>1325</v>
-      </c>
-      <c r="AS246" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="247" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B247" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C247" t="s">
         <v>230</v>
@@ -25163,21 +25166,21 @@
         <v>54</v>
       </c>
       <c r="AO247" t="s">
+        <v>1327</v>
+      </c>
+      <c r="AP247" t="s">
         <v>1328</v>
       </c>
-      <c r="AP247" t="s">
-        <v>1329</v>
-      </c>
       <c r="AS247" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="248" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B248" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C248" t="s">
         <v>230</v>
@@ -25264,21 +25267,21 @@
         <v>54</v>
       </c>
       <c r="AO248" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AP248" t="s">
         <v>1331</v>
       </c>
-      <c r="AP248" t="s">
-        <v>1332</v>
-      </c>
       <c r="AS248" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="249" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B249" t="s">
         <v>1333</v>
-      </c>
-      <c r="B249" t="s">
-        <v>1334</v>
       </c>
       <c r="C249" t="s">
         <v>257</v>
@@ -25314,21 +25317,21 @@
         <v>54</v>
       </c>
       <c r="AO249" t="s">
+        <v>1334</v>
+      </c>
+      <c r="AP249" t="s">
         <v>1335</v>
       </c>
-      <c r="AP249" t="s">
+      <c r="AS249" t="s">
         <v>1336</v>
-      </c>
-      <c r="AS249" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="250" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B250" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C250" t="s">
         <v>47</v>
@@ -25367,27 +25370,27 @@
         <v>102</v>
       </c>
       <c r="AJ250" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="AM250" t="s">
         <v>54</v>
       </c>
       <c r="AO250" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AP250" t="s">
         <v>1340</v>
       </c>
-      <c r="AP250" t="s">
+      <c r="AS250" t="s">
         <v>1341</v>
-      </c>
-      <c r="AS250" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="251" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B251" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C251" t="s">
         <v>297</v>
@@ -25423,18 +25426,18 @@
         <v>59</v>
       </c>
       <c r="AO251" t="s">
+        <v>1343</v>
+      </c>
+      <c r="AP251" t="s">
         <v>1344</v>
       </c>
-      <c r="AP251" t="s">
+      <c r="AS251" t="s">
         <v>1345</v>
       </c>
-      <c r="AS251" t="s">
+    </row>
+    <row r="252" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
         <v>1346</v>
-      </c>
-    </row>
-    <row r="252" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>1347</v>
       </c>
       <c r="B252" t="s">
         <v>880</v>
@@ -25476,30 +25479,30 @@
         <v>73</v>
       </c>
       <c r="AD252" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="AG252">
         <v>110</v>
       </c>
       <c r="AM252" t="s">
+        <v>1348</v>
+      </c>
+      <c r="AN252" t="s">
         <v>1349</v>
       </c>
-      <c r="AN252" t="s">
+      <c r="AO252" t="s">
         <v>1350</v>
       </c>
-      <c r="AO252" t="s">
+      <c r="AP252" t="s">
         <v>1351</v>
-      </c>
-      <c r="AP252" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="253" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B253" t="s">
         <v>1353</v>
-      </c>
-      <c r="B253" t="s">
-        <v>1354</v>
       </c>
       <c r="C253" t="s">
         <v>257</v>
@@ -25568,21 +25571,21 @@
         <v>54</v>
       </c>
       <c r="AO253" t="s">
+        <v>1354</v>
+      </c>
+      <c r="AP253" t="s">
         <v>1355</v>
       </c>
-      <c r="AP253" t="s">
+      <c r="AS253" t="s">
         <v>1356</v>
-      </c>
-      <c r="AS253" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="254" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B254" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C254" t="s">
         <v>205</v>
@@ -25657,24 +25660,24 @@
         <v>54</v>
       </c>
       <c r="AN254" t="s">
+        <v>1358</v>
+      </c>
+      <c r="AO254" t="s">
         <v>1359</v>
       </c>
-      <c r="AO254" t="s">
+      <c r="AP254" t="s">
         <v>1360</v>
       </c>
-      <c r="AP254" t="s">
+      <c r="AS254" t="s">
         <v>1361</v>
-      </c>
-      <c r="AS254" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="255" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B255" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C255" t="s">
         <v>257</v>
@@ -25737,7 +25740,7 @@
         <v>48</v>
       </c>
       <c r="AD255" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="AE255">
         <v>117</v>
@@ -25746,10 +25749,10 @@
         <v>118</v>
       </c>
       <c r="AH255" t="s">
+        <v>1364</v>
+      </c>
+      <c r="AI255" t="s">
         <v>1365</v>
-      </c>
-      <c r="AI255" t="s">
-        <v>1366</v>
       </c>
       <c r="AK255">
         <v>-117</v>
@@ -25758,21 +25761,21 @@
         <v>54</v>
       </c>
       <c r="AO255" t="s">
+        <v>1366</v>
+      </c>
+      <c r="AP255" t="s">
         <v>1367</v>
       </c>
-      <c r="AP255" t="s">
+      <c r="AS255" t="s">
         <v>1368</v>
-      </c>
-      <c r="AS255" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="256" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B256" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="C256" t="s">
         <v>230</v>
@@ -25787,7 +25790,7 @@
         <v>2</v>
       </c>
       <c r="I256">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J256">
         <v>2</v>
@@ -25838,10 +25841,10 @@
         <v>48</v>
       </c>
       <c r="AB256" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AC256" t="s">
         <v>1371</v>
-      </c>
-      <c r="AC256" t="s">
-        <v>1372</v>
       </c>
       <c r="AD256">
         <v>75</v>
@@ -25853,10 +25856,10 @@
         <v>123</v>
       </c>
       <c r="AH256" t="s">
+        <v>1372</v>
+      </c>
+      <c r="AI256" t="s">
         <v>1373</v>
-      </c>
-      <c r="AI256" t="s">
-        <v>1374</v>
       </c>
       <c r="AK256">
         <v>-129</v>
@@ -25865,24 +25868,24 @@
         <v>54</v>
       </c>
       <c r="AN256" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AO256" t="s">
         <v>1375</v>
       </c>
-      <c r="AO256" t="s">
+      <c r="AP256" t="s">
         <v>1376</v>
       </c>
-      <c r="AP256" t="s">
+      <c r="AS256" t="s">
         <v>1377</v>
-      </c>
-      <c r="AS256" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="257" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B257" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C257" t="s">
         <v>257</v>
@@ -25900,30 +25903,30 @@
         <v>24</v>
       </c>
       <c r="Y257" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="AM257" t="s">
         <v>54</v>
       </c>
       <c r="AN257" t="s">
+        <v>1380</v>
+      </c>
+      <c r="AO257" t="s">
         <v>1381</v>
       </c>
-      <c r="AO257" t="s">
+      <c r="AP257" t="s">
         <v>1382</v>
       </c>
-      <c r="AP257" t="s">
+      <c r="AS257" t="s">
         <v>1383</v>
-      </c>
-      <c r="AS257" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="258" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B258" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C258" t="s">
         <v>257</v>
@@ -25956,36 +25959,36 @@
         <v>49</v>
       </c>
       <c r="AC258" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="AF258">
         <v>113</v>
       </c>
       <c r="AI258" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="AM258" t="s">
         <v>54</v>
       </c>
       <c r="AN258" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AO258" t="s">
         <v>1387</v>
       </c>
-      <c r="AO258" t="s">
+      <c r="AP258" t="s">
         <v>1388</v>
       </c>
-      <c r="AP258" t="s">
+      <c r="AS258" t="s">
         <v>1389</v>
-      </c>
-      <c r="AS258" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="259" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B259" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C259" t="s">
         <v>230</v>
@@ -26045,7 +26048,7 @@
         <v>49</v>
       </c>
       <c r="Z259" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="AA259" t="s">
         <v>48</v>
@@ -26057,13 +26060,13 @@
         <v>48</v>
       </c>
       <c r="AD259" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="AE259">
         <v>118</v>
       </c>
       <c r="AF259" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="AI259" t="s">
         <v>289</v>
@@ -26072,24 +26075,24 @@
         <v>54</v>
       </c>
       <c r="AN259" t="s">
+        <v>1394</v>
+      </c>
+      <c r="AO259" t="s">
         <v>1395</v>
       </c>
-      <c r="AO259" t="s">
+      <c r="AP259" t="s">
         <v>1396</v>
       </c>
-      <c r="AP259" t="s">
+      <c r="AS259" t="s">
         <v>1397</v>
-      </c>
-      <c r="AS259" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="260" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B260" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C260" t="s">
         <v>205</v>
@@ -26185,21 +26188,21 @@
         <v>54</v>
       </c>
       <c r="AO260" t="s">
+        <v>1399</v>
+      </c>
+      <c r="AP260" t="s">
         <v>1400</v>
       </c>
-      <c r="AP260" t="s">
+      <c r="AS260" t="s">
         <v>1401</v>
-      </c>
-      <c r="AS260" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="261" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B261" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C261" t="s">
         <v>230</v>
@@ -26259,7 +26262,7 @@
         <v>49</v>
       </c>
       <c r="Z261" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="AA261" t="s">
         <v>48</v>
@@ -26274,36 +26277,36 @@
         <v>75</v>
       </c>
       <c r="AE261" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="AF261" t="s">
         <v>362</v>
       </c>
       <c r="AK261" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="AM261" t="s">
         <v>54</v>
       </c>
       <c r="AN261" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="AO261" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AP261" t="s">
         <v>1406</v>
       </c>
-      <c r="AP261" t="s">
+      <c r="AS261" t="s">
         <v>1407</v>
-      </c>
-      <c r="AS261" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="262" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B262" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C262" t="s">
         <v>230</v>
@@ -26384,27 +26387,27 @@
         <v>289</v>
       </c>
       <c r="AK262" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="AM262" t="s">
         <v>54</v>
       </c>
       <c r="AO262" t="s">
+        <v>1409</v>
+      </c>
+      <c r="AP262" t="s">
         <v>1410</v>
       </c>
-      <c r="AP262" t="s">
+      <c r="AS262" t="s">
         <v>1411</v>
       </c>
-      <c r="AS262" t="s">
+    </row>
+    <row r="263" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B263" t="s">
         <v>1412</v>
-      </c>
-    </row>
-    <row r="263" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B263" t="s">
-        <v>1413</v>
       </c>
       <c r="C263" t="s">
         <v>257</v>
@@ -26419,33 +26422,33 @@
         <v>24</v>
       </c>
       <c r="Y263" t="s">
+        <v>1413</v>
+      </c>
+      <c r="Z263" t="s">
         <v>1414</v>
       </c>
-      <c r="Z263" t="s">
+      <c r="AC263" t="s">
         <v>1415</v>
-      </c>
-      <c r="AC263" t="s">
-        <v>1416</v>
       </c>
       <c r="AM263" t="s">
         <v>54</v>
       </c>
       <c r="AN263" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="AO263" t="s">
+        <v>1416</v>
+      </c>
+      <c r="AP263" t="s">
         <v>1417</v>
-      </c>
-      <c r="AP263" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="264" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B264" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C264" t="s">
         <v>230</v>
@@ -26484,16 +26487,16 @@
         <v>24</v>
       </c>
       <c r="Y264" t="s">
+        <v>1419</v>
+      </c>
+      <c r="Z264" t="s">
         <v>1420</v>
       </c>
-      <c r="Z264" t="s">
+      <c r="AB264" t="s">
         <v>1421</v>
       </c>
-      <c r="AB264" t="s">
-        <v>1422</v>
-      </c>
       <c r="AC264" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="AD264">
         <v>75</v>
@@ -26514,24 +26517,24 @@
         <v>54</v>
       </c>
       <c r="AN264" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="AO264" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AP264" t="s">
         <v>1423</v>
       </c>
-      <c r="AP264" t="s">
+      <c r="AS264" t="s">
         <v>1424</v>
-      </c>
-      <c r="AS264" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="265" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B265" t="s">
         <v>1426</v>
-      </c>
-      <c r="B265" t="s">
-        <v>1427</v>
       </c>
       <c r="C265" t="s">
         <v>297</v>
@@ -26570,7 +26573,7 @@
         <v>48</v>
       </c>
       <c r="AD265" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="AE265">
         <v>104</v>
@@ -26579,7 +26582,7 @@
         <v>112</v>
       </c>
       <c r="AH265" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="AK265">
         <v>-128</v>
@@ -26588,24 +26591,24 @@
         <v>54</v>
       </c>
       <c r="AN265" t="s">
+        <v>1428</v>
+      </c>
+      <c r="AO265" t="s">
         <v>1429</v>
       </c>
-      <c r="AO265" t="s">
+      <c r="AP265" t="s">
         <v>1430</v>
       </c>
-      <c r="AP265" t="s">
+      <c r="AS265" t="s">
         <v>1431</v>
-      </c>
-      <c r="AS265" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="266" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B266" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C266" t="s">
         <v>297</v>
@@ -26632,7 +26635,7 @@
         <v>48</v>
       </c>
       <c r="AD266" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="AE266">
         <v>100</v>
@@ -26641,30 +26644,30 @@
         <v>654</v>
       </c>
       <c r="AN266" t="s">
+        <v>1434</v>
+      </c>
+      <c r="AO266" t="s">
         <v>1435</v>
       </c>
-      <c r="AO266" t="s">
+      <c r="AP266" t="s">
         <v>1436</v>
       </c>
-      <c r="AP266" t="s">
+      <c r="AS266" t="s">
         <v>1437</v>
-      </c>
-      <c r="AS266" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="267" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B267" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="C267" t="s">
         <v>381</v>
       </c>
       <c r="D267">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="E267">
         <v>2</v>
@@ -26700,7 +26703,7 @@
         <v>48</v>
       </c>
       <c r="AD267" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AL267">
         <v>-131.5</v>
@@ -26709,24 +26712,24 @@
         <v>54</v>
       </c>
       <c r="AN267" t="s">
+        <v>1440</v>
+      </c>
+      <c r="AO267" t="s">
         <v>1441</v>
       </c>
-      <c r="AO267" t="s">
+      <c r="AP267" t="s">
         <v>1442</v>
       </c>
-      <c r="AP267" t="s">
+      <c r="AS267" t="s">
         <v>1443</v>
-      </c>
-      <c r="AS267" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="268" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B268" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C268" t="s">
         <v>381</v>
@@ -26771,7 +26774,7 @@
         <v>48</v>
       </c>
       <c r="AD268" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AL268">
         <v>-131.5</v>
@@ -26780,24 +26783,24 @@
         <v>54</v>
       </c>
       <c r="AN268" t="s">
+        <v>1445</v>
+      </c>
+      <c r="AO268" t="s">
         <v>1446</v>
       </c>
-      <c r="AO268" t="s">
+      <c r="AP268" t="s">
         <v>1447</v>
       </c>
-      <c r="AP268" t="s">
+      <c r="AS268" t="s">
         <v>1448</v>
-      </c>
-      <c r="AS268" t="s">
-        <v>1449</v>
       </c>
     </row>
     <row r="269" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B269" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C269" t="s">
         <v>381</v>
@@ -26839,7 +26842,7 @@
         <v>48</v>
       </c>
       <c r="AD269" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AK269">
         <v>-131.5</v>
@@ -26848,24 +26851,24 @@
         <v>54</v>
       </c>
       <c r="AN269" t="s">
+        <v>1450</v>
+      </c>
+      <c r="AO269" t="s">
         <v>1451</v>
       </c>
-      <c r="AO269" t="s">
+      <c r="AP269" t="s">
         <v>1452</v>
       </c>
-      <c r="AP269" t="s">
+      <c r="AS269" t="s">
         <v>1453</v>
-      </c>
-      <c r="AS269" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="270" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B270" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="C270" t="s">
         <v>381</v>
@@ -26904,7 +26907,7 @@
         <v>48</v>
       </c>
       <c r="AD270" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AK270">
         <v>-131.5</v>
@@ -26913,24 +26916,24 @@
         <v>54</v>
       </c>
       <c r="AN270" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="AO270" t="s">
+        <v>1455</v>
+      </c>
+      <c r="AP270" t="s">
         <v>1456</v>
       </c>
-      <c r="AP270" t="s">
+      <c r="AS270" t="s">
         <v>1457</v>
-      </c>
-      <c r="AS270" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="271" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B271" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C271" t="s">
         <v>381</v>
@@ -26969,7 +26972,7 @@
         <v>48</v>
       </c>
       <c r="AD271" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AK271">
         <v>-131.5</v>
@@ -26978,24 +26981,24 @@
         <v>54</v>
       </c>
       <c r="AN271" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="AO271" t="s">
+        <v>1459</v>
+      </c>
+      <c r="AP271" t="s">
         <v>1460</v>
       </c>
-      <c r="AP271" t="s">
+      <c r="AS271" t="s">
         <v>1461</v>
-      </c>
-      <c r="AS271" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="272" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B272" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="C272" t="s">
         <v>381</v>
@@ -27037,36 +27040,36 @@
         <v>48</v>
       </c>
       <c r="AD272" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="AG272" t="s">
         <v>398</v>
       </c>
       <c r="AK272" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="AM272" t="s">
         <v>54</v>
       </c>
       <c r="AN272" t="s">
+        <v>1464</v>
+      </c>
+      <c r="AO272" t="s">
         <v>1465</v>
       </c>
-      <c r="AO272" t="s">
+      <c r="AP272" t="s">
         <v>1466</v>
       </c>
-      <c r="AP272" t="s">
+      <c r="AS272" t="s">
         <v>1467</v>
       </c>
-      <c r="AS272" t="s">
+    </row>
+    <row r="273" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
         <v>1468</v>
       </c>
-    </row>
-    <row r="273" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
+      <c r="B273" t="s">
         <v>1469</v>
-      </c>
-      <c r="B273" t="s">
-        <v>1470</v>
       </c>
       <c r="C273" t="s">
         <v>381</v>
@@ -27105,27 +27108,27 @@
         <v>48</v>
       </c>
       <c r="AM273" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AN273" t="s">
         <v>1471</v>
       </c>
-      <c r="AN273" t="s">
+      <c r="AO273" t="s">
         <v>1472</v>
       </c>
-      <c r="AO273" t="s">
+      <c r="AP273" t="s">
         <v>1473</v>
       </c>
-      <c r="AP273" t="s">
+      <c r="AR273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B274" t="s">
         <v>1474</v>
-      </c>
-      <c r="AR273">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="274" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B274" t="s">
-        <v>1475</v>
       </c>
       <c r="C274" t="s">
         <v>381</v>
@@ -27170,21 +27173,21 @@
         <v>282</v>
       </c>
       <c r="AN274" t="s">
+        <v>1475</v>
+      </c>
+      <c r="AO274" t="s">
         <v>1476</v>
       </c>
-      <c r="AO274" t="s">
+      <c r="AP274" t="s">
         <v>1477</v>
       </c>
-      <c r="AP274" t="s">
+    </row>
+    <row r="275" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B275" t="s">
         <v>1478</v>
-      </c>
-    </row>
-    <row r="275" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B275" t="s">
-        <v>1479</v>
       </c>
       <c r="C275" t="s">
         <v>381</v>
@@ -27235,21 +27238,21 @@
         <v>54</v>
       </c>
       <c r="AN275" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="AO275" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AP275" t="s">
         <v>1480</v>
       </c>
-      <c r="AP275" t="s">
+    </row>
+    <row r="276" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B276" t="s">
         <v>1481</v>
-      </c>
-    </row>
-    <row r="276" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B276" t="s">
-        <v>1482</v>
       </c>
       <c r="C276" t="s">
         <v>381</v>
@@ -27279,7 +27282,7 @@
         <v>24</v>
       </c>
       <c r="Y276" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="Z276" t="s">
         <v>72</v>
@@ -27297,18 +27300,18 @@
         <v>54</v>
       </c>
       <c r="AO276" t="s">
+        <v>1483</v>
+      </c>
+      <c r="AP276" t="s">
         <v>1484</v>
       </c>
-      <c r="AP276" t="s">
+    </row>
+    <row r="277" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B277" t="s">
         <v>1485</v>
-      </c>
-    </row>
-    <row r="277" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B277" t="s">
-        <v>1486</v>
       </c>
       <c r="C277" t="s">
         <v>381</v>
@@ -27329,7 +27332,7 @@
         <v>48</v>
       </c>
       <c r="Y277" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="AB277" t="s">
         <v>73</v>
@@ -27338,24 +27341,24 @@
         <v>48</v>
       </c>
       <c r="AM277" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="AN277" t="s">
+        <v>1487</v>
+      </c>
+      <c r="AO277" t="s">
         <v>1488</v>
       </c>
-      <c r="AO277" t="s">
+      <c r="AP277" t="s">
         <v>1489</v>
       </c>
-      <c r="AP277" t="s">
+    </row>
+    <row r="278" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B278" t="s">
         <v>1490</v>
-      </c>
-    </row>
-    <row r="278" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B278" t="s">
-        <v>1491</v>
       </c>
       <c r="C278" t="s">
         <v>381</v>
@@ -27397,21 +27400,21 @@
         <v>48</v>
       </c>
       <c r="AM278" t="s">
+        <v>1491</v>
+      </c>
+      <c r="AO278" t="s">
         <v>1492</v>
       </c>
-      <c r="AO278" t="s">
+      <c r="AP278" t="s">
         <v>1493</v>
       </c>
-      <c r="AP278" t="s">
+    </row>
+    <row r="279" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B279" t="s">
         <v>1494</v>
-      </c>
-    </row>
-    <row r="279" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B279" t="s">
-        <v>1495</v>
       </c>
       <c r="C279" t="s">
         <v>381</v>
@@ -27462,21 +27465,21 @@
         <v>291</v>
       </c>
       <c r="AN279" t="s">
+        <v>1495</v>
+      </c>
+      <c r="AO279" t="s">
         <v>1496</v>
       </c>
-      <c r="AO279" t="s">
+      <c r="AP279" t="s">
         <v>1497</v>
-      </c>
-      <c r="AP279" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="280" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B280" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C280" t="s">
         <v>297</v>
@@ -27524,24 +27527,24 @@
         <v>282</v>
       </c>
       <c r="AN280" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AO280" t="s">
         <v>1500</v>
       </c>
-      <c r="AO280" t="s">
+      <c r="AP280" t="s">
         <v>1501</v>
       </c>
-      <c r="AP280" t="s">
+      <c r="AS280" t="s">
         <v>1502</v>
-      </c>
-      <c r="AS280" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="281" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B281" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="C281" t="s">
         <v>271</v>
@@ -27595,24 +27598,24 @@
         <v>282</v>
       </c>
       <c r="AN281" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="AO281" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AP281" t="s">
         <v>1505</v>
       </c>
-      <c r="AP281" t="s">
+      <c r="AS281" t="s">
         <v>1506</v>
-      </c>
-      <c r="AS281" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="282" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B282" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C282" t="s">
         <v>271</v>
@@ -27666,24 +27669,24 @@
         <v>282</v>
       </c>
       <c r="AN282" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="AO282" t="s">
+        <v>1508</v>
+      </c>
+      <c r="AP282" t="s">
         <v>1509</v>
       </c>
-      <c r="AP282" t="s">
+      <c r="AS282" t="s">
         <v>1510</v>
-      </c>
-      <c r="AS282" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="283" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B283" t="s">
         <v>1512</v>
-      </c>
-      <c r="B283" t="s">
-        <v>1513</v>
       </c>
       <c r="C283" t="s">
         <v>381</v>
@@ -27716,27 +27719,27 @@
         <v>48</v>
       </c>
       <c r="AD283" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="AM283" t="s">
         <v>382</v>
       </c>
       <c r="AO283" t="s">
+        <v>1513</v>
+      </c>
+      <c r="AP283" t="s">
         <v>1514</v>
       </c>
-      <c r="AP283" t="s">
+      <c r="AS283" t="s">
         <v>1515</v>
-      </c>
-      <c r="AS283" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="284" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B284" t="s">
         <v>1517</v>
-      </c>
-      <c r="B284" t="s">
-        <v>1518</v>
       </c>
       <c r="C284" t="s">
         <v>47</v>
@@ -27784,7 +27787,7 @@
         <v>48</v>
       </c>
       <c r="AD284" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="AH284" t="s">
         <v>130</v>
@@ -27799,24 +27802,24 @@
         <v>54</v>
       </c>
       <c r="AO284" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AP284" t="s">
         <v>1520</v>
       </c>
-      <c r="AP284" t="s">
+      <c r="AQ284">
+        <v>2</v>
+      </c>
+      <c r="AS284" t="s">
         <v>1521</v>
-      </c>
-      <c r="AQ284">
-        <v>2</v>
-      </c>
-      <c r="AS284" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="285" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B285" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C285" t="s">
         <v>47</v>
@@ -27861,7 +27864,7 @@
         <v>48</v>
       </c>
       <c r="AD285" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="AL285" t="s">
         <v>821</v>
@@ -27870,24 +27873,24 @@
         <v>54</v>
       </c>
       <c r="AO285" t="s">
+        <v>1523</v>
+      </c>
+      <c r="AP285" t="s">
         <v>1524</v>
       </c>
-      <c r="AP285" t="s">
+      <c r="AQ285">
+        <v>2</v>
+      </c>
+      <c r="AS285" t="s">
         <v>1525</v>
-      </c>
-      <c r="AQ285">
-        <v>2</v>
-      </c>
-      <c r="AS285" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="286" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B286" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C286" t="s">
         <v>47</v>
@@ -27935,7 +27938,7 @@
         <v>48</v>
       </c>
       <c r="AD286" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="AH286" t="s">
         <v>59</v>
@@ -27947,24 +27950,24 @@
         <v>54</v>
       </c>
       <c r="AO286" t="s">
+        <v>1527</v>
+      </c>
+      <c r="AP286" t="s">
         <v>1528</v>
       </c>
-      <c r="AP286" t="s">
-        <v>1529</v>
-      </c>
       <c r="AQ286">
         <v>2</v>
       </c>
       <c r="AS286" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="287" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B287" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C287" t="s">
         <v>47</v>
@@ -28009,10 +28012,10 @@
         <v>48</v>
       </c>
       <c r="AD287" t="s">
+        <v>1530</v>
+      </c>
+      <c r="AH287" t="s">
         <v>1531</v>
-      </c>
-      <c r="AH287" t="s">
-        <v>1532</v>
       </c>
       <c r="AL287">
         <v>-128</v>
@@ -28021,24 +28024,24 @@
         <v>54</v>
       </c>
       <c r="AO287" t="s">
+        <v>1532</v>
+      </c>
+      <c r="AP287" t="s">
         <v>1533</v>
       </c>
-      <c r="AP287" t="s">
+      <c r="AQ287">
+        <v>2</v>
+      </c>
+      <c r="AS287" t="s">
         <v>1534</v>
-      </c>
-      <c r="AQ287">
-        <v>2</v>
-      </c>
-      <c r="AS287" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="288" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B288" t="s">
         <v>1536</v>
-      </c>
-      <c r="B288" t="s">
-        <v>1537</v>
       </c>
       <c r="C288" t="s">
         <v>205</v>
@@ -28098,24 +28101,24 @@
         <v>54</v>
       </c>
       <c r="AN288" t="s">
+        <v>1537</v>
+      </c>
+      <c r="AO288" t="s">
         <v>1538</v>
       </c>
-      <c r="AO288" t="s">
+      <c r="AP288" t="s">
         <v>1539</v>
       </c>
-      <c r="AP288" t="s">
+      <c r="AS288" t="s">
         <v>1540</v>
-      </c>
-      <c r="AS288" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="289" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B289" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C289" t="s">
         <v>47</v>
@@ -28154,7 +28157,7 @@
         <v>48</v>
       </c>
       <c r="AD289" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="AE289">
         <v>117</v>
@@ -28175,21 +28178,21 @@
         <v>54</v>
       </c>
       <c r="AO289" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AP289" t="s">
         <v>1544</v>
       </c>
-      <c r="AP289" t="s">
+      <c r="AS289" t="s">
         <v>1545</v>
-      </c>
-      <c r="AS289" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="290" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B290" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C290" t="s">
         <v>297</v>
@@ -28231,7 +28234,7 @@
         <v>48</v>
       </c>
       <c r="AD290" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="AE290">
         <v>113</v>
@@ -28246,24 +28249,24 @@
         <v>282</v>
       </c>
       <c r="AN290" t="s">
+        <v>1548</v>
+      </c>
+      <c r="AO290" t="s">
         <v>1549</v>
       </c>
-      <c r="AO290" t="s">
+      <c r="AP290" t="s">
         <v>1550</v>
       </c>
-      <c r="AP290" t="s">
+      <c r="AS290" t="s">
         <v>1551</v>
-      </c>
-      <c r="AS290" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="291" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B291" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="C291" t="s">
         <v>271</v>
@@ -28305,7 +28308,7 @@
         <v>32</v>
       </c>
       <c r="Y291" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="Z291" t="s">
         <v>48</v>
@@ -28320,7 +28323,7 @@
         <v>48</v>
       </c>
       <c r="AD291" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="AG291" t="s">
         <v>835</v>
@@ -28332,24 +28335,24 @@
         <v>54</v>
       </c>
       <c r="AN291" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="AO291" t="s">
+        <v>1555</v>
+      </c>
+      <c r="AP291" t="s">
         <v>1556</v>
       </c>
-      <c r="AP291" t="s">
+      <c r="AS291" t="s">
         <v>1557</v>
-      </c>
-      <c r="AS291" t="s">
-        <v>1558</v>
       </c>
     </row>
     <row r="292" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B292" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C292" t="s">
         <v>230</v>
@@ -28445,24 +28448,24 @@
         <v>54</v>
       </c>
       <c r="AN292" t="s">
+        <v>1559</v>
+      </c>
+      <c r="AO292" t="s">
         <v>1560</v>
       </c>
-      <c r="AO292" t="s">
+      <c r="AP292" t="s">
         <v>1561</v>
       </c>
-      <c r="AP292" t="s">
+      <c r="AS292" t="s">
         <v>1562</v>
-      </c>
-      <c r="AS292" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="293" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B293" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C293" t="s">
         <v>271</v>
@@ -28504,7 +28507,7 @@
         <v>48</v>
       </c>
       <c r="AD293" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="AE293">
         <v>116.5</v>
@@ -28519,24 +28522,24 @@
         <v>54</v>
       </c>
       <c r="AN293" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="AO293" t="s">
+        <v>1565</v>
+      </c>
+      <c r="AP293" t="s">
         <v>1566</v>
       </c>
-      <c r="AP293" t="s">
+      <c r="AS293" t="s">
         <v>1567</v>
-      </c>
-      <c r="AS293" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="294" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B294" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="C294" t="s">
         <v>271</v>
@@ -28584,7 +28587,7 @@
         <v>48</v>
       </c>
       <c r="AD294" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="AE294">
         <v>116.5</v>
@@ -28605,24 +28608,24 @@
         <v>54</v>
       </c>
       <c r="AN294" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="AO294" t="s">
+        <v>1569</v>
+      </c>
+      <c r="AP294" t="s">
         <v>1570</v>
       </c>
-      <c r="AP294" t="s">
+      <c r="AS294" t="s">
         <v>1571</v>
       </c>
-      <c r="AS294" t="s">
+    </row>
+    <row r="295" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B295" t="s">
         <v>1572</v>
-      </c>
-    </row>
-    <row r="295" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>1536</v>
-      </c>
-      <c r="B295" t="s">
-        <v>1573</v>
       </c>
       <c r="C295" t="s">
         <v>230</v>
@@ -28643,18 +28646,18 @@
         <v>54</v>
       </c>
       <c r="AO295" t="s">
+        <v>1573</v>
+      </c>
+      <c r="AP295" t="s">
         <v>1574</v>
-      </c>
-      <c r="AP295" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="296" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B296" t="s">
         <v>1576</v>
-      </c>
-      <c r="B296" t="s">
-        <v>1577</v>
       </c>
       <c r="C296" t="s">
         <v>381</v>
@@ -28672,7 +28675,7 @@
         <v>2</v>
       </c>
       <c r="P296">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V296" t="s">
         <v>48</v>
@@ -28711,27 +28714,27 @@
         <v>282</v>
       </c>
       <c r="AN296" t="s">
+        <v>1577</v>
+      </c>
+      <c r="AO296" t="s">
         <v>1578</v>
       </c>
-      <c r="AO296" t="s">
+      <c r="AP296" t="s">
         <v>1579</v>
       </c>
-      <c r="AP296" t="s">
+      <c r="AR296">
+        <v>2</v>
+      </c>
+      <c r="AS296" t="s">
         <v>1580</v>
-      </c>
-      <c r="AR296">
-        <v>2</v>
-      </c>
-      <c r="AS296" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="297" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B297" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="C297" t="s">
         <v>381</v>
@@ -28791,24 +28794,24 @@
         <v>475</v>
       </c>
       <c r="AN297" t="s">
+        <v>1582</v>
+      </c>
+      <c r="AO297" t="s">
         <v>1583</v>
       </c>
-      <c r="AO297" t="s">
+      <c r="AP297" t="s">
         <v>1584</v>
       </c>
-      <c r="AP297" t="s">
+      <c r="AS297" t="s">
         <v>1585</v>
-      </c>
-      <c r="AS297" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="298" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B298" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="C298" t="s">
         <v>47</v>
@@ -28856,7 +28859,7 @@
         <v>48</v>
       </c>
       <c r="AB298" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="AC298" t="s">
         <v>48</v>
@@ -28877,21 +28880,21 @@
         <v>54</v>
       </c>
       <c r="AO298" t="s">
+        <v>1588</v>
+      </c>
+      <c r="AP298" t="s">
         <v>1589</v>
       </c>
-      <c r="AP298" t="s">
+      <c r="AS298" t="s">
         <v>1590</v>
-      </c>
-      <c r="AS298" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="299" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B299" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="C299" t="s">
         <v>47</v>
@@ -28933,7 +28936,7 @@
         <v>48</v>
       </c>
       <c r="AB299" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="AC299" t="s">
         <v>48</v>
@@ -28951,24 +28954,24 @@
         <v>54</v>
       </c>
       <c r="AO299" t="s">
+        <v>1593</v>
+      </c>
+      <c r="AP299" t="s">
         <v>1594</v>
       </c>
-      <c r="AP299" t="s">
+      <c r="AQ299">
+        <v>2</v>
+      </c>
+      <c r="AS299" t="s">
         <v>1595</v>
-      </c>
-      <c r="AQ299">
-        <v>2</v>
-      </c>
-      <c r="AS299" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="300" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B300" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="C300" t="s">
         <v>47</v>
@@ -28989,7 +28992,7 @@
         <v>2</v>
       </c>
       <c r="O300" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="P300">
         <v>1</v>
@@ -29025,24 +29028,24 @@
         <v>54</v>
       </c>
       <c r="AO300" t="s">
+        <v>1598</v>
+      </c>
+      <c r="AP300" t="s">
         <v>1599</v>
       </c>
-      <c r="AP300" t="s">
+      <c r="AQ300">
+        <v>2</v>
+      </c>
+      <c r="AS300" t="s">
         <v>1600</v>
-      </c>
-      <c r="AQ300">
-        <v>2</v>
-      </c>
-      <c r="AS300" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="301" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B301" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="C301" t="s">
         <v>47</v>
@@ -29096,7 +29099,7 @@
         <v>740</v>
       </c>
       <c r="AH301" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="AK301">
         <v>-128</v>
@@ -29105,21 +29108,21 @@
         <v>291</v>
       </c>
       <c r="AO301" t="s">
+        <v>1603</v>
+      </c>
+      <c r="AP301" t="s">
         <v>1604</v>
       </c>
-      <c r="AP301" t="s">
+      <c r="AS301" t="s">
         <v>1605</v>
-      </c>
-      <c r="AS301" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="302" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B302" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="C302" t="s">
         <v>47</v>
@@ -29170,24 +29173,24 @@
         <v>54</v>
       </c>
       <c r="AO302" t="s">
+        <v>1607</v>
+      </c>
+      <c r="AP302" t="s">
         <v>1608</v>
-      </c>
-      <c r="AP302" t="s">
-        <v>1609</v>
       </c>
       <c r="AQ302">
         <v>4</v>
       </c>
       <c r="AS302" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="303" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B303" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="C303" t="s">
         <v>47</v>
@@ -29238,24 +29241,24 @@
         <v>54</v>
       </c>
       <c r="AO303" t="s">
+        <v>1611</v>
+      </c>
+      <c r="AP303" t="s">
         <v>1612</v>
-      </c>
-      <c r="AP303" t="s">
-        <v>1613</v>
       </c>
       <c r="AQ303">
         <v>4</v>
       </c>
       <c r="AS303" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="304" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B304" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="C304" t="s">
         <v>257</v>
@@ -29297,21 +29300,21 @@
         <v>291</v>
       </c>
       <c r="AO304" t="s">
+        <v>1615</v>
+      </c>
+      <c r="AP304" t="s">
         <v>1616</v>
       </c>
-      <c r="AP304" t="s">
+      <c r="AS304" t="s">
         <v>1617</v>
-      </c>
-      <c r="AS304" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="305" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B305" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="C305" t="s">
         <v>271</v>
@@ -29368,21 +29371,21 @@
         <v>282</v>
       </c>
       <c r="AO305" t="s">
+        <v>1619</v>
+      </c>
+      <c r="AP305" t="s">
         <v>1620</v>
       </c>
-      <c r="AP305" t="s">
+      <c r="AS305" t="s">
         <v>1621</v>
-      </c>
-      <c r="AS305" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="306" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B306" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="C306" t="s">
         <v>297</v>
@@ -29430,7 +29433,7 @@
         <v>368</v>
       </c>
       <c r="AH306" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="AI306" t="s">
         <v>446</v>
@@ -29442,24 +29445,24 @@
         <v>282</v>
       </c>
       <c r="AN306" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AO306" t="s">
         <v>1625</v>
       </c>
-      <c r="AO306" t="s">
+      <c r="AP306" t="s">
         <v>1626</v>
       </c>
-      <c r="AP306" t="s">
+      <c r="AS306" t="s">
         <v>1627</v>
-      </c>
-      <c r="AS306" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="307" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B307" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="C307" t="s">
         <v>297</v>
@@ -29516,7 +29519,7 @@
         <v>52</v>
       </c>
       <c r="AH307" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="AI307" t="s">
         <v>446</v>
@@ -29528,24 +29531,24 @@
         <v>54</v>
       </c>
       <c r="AN307" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AO307" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AP307" t="s">
         <v>1630</v>
       </c>
-      <c r="AP307" t="s">
+      <c r="AS307" t="s">
         <v>1631</v>
-      </c>
-      <c r="AS307" t="s">
-        <v>1632</v>
       </c>
     </row>
     <row r="308" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B308" t="s">
         <v>1633</v>
-      </c>
-      <c r="B308" t="s">
-        <v>1634</v>
       </c>
       <c r="C308" t="s">
         <v>381</v>
@@ -29608,21 +29611,21 @@
         <v>260</v>
       </c>
       <c r="AO308" t="s">
+        <v>1634</v>
+      </c>
+      <c r="AP308" t="s">
         <v>1635</v>
       </c>
-      <c r="AP308" t="s">
+      <c r="AS308" t="s">
         <v>1636</v>
-      </c>
-      <c r="AS308" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="309" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B309" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="C309" t="s">
         <v>297</v>
@@ -29685,21 +29688,21 @@
         <v>260</v>
       </c>
       <c r="AO309" t="s">
+        <v>1638</v>
+      </c>
+      <c r="AP309" t="s">
         <v>1639</v>
       </c>
-      <c r="AP309" t="s">
+      <c r="AS309" t="s">
         <v>1640</v>
-      </c>
-      <c r="AS309" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="310" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B310" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="C310" t="s">
         <v>381</v>
@@ -29768,21 +29771,21 @@
         <v>260</v>
       </c>
       <c r="AO310" t="s">
+        <v>1642</v>
+      </c>
+      <c r="AP310" t="s">
         <v>1643</v>
       </c>
-      <c r="AP310" t="s">
+      <c r="AS310" t="s">
         <v>1644</v>
-      </c>
-      <c r="AS310" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="311" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B311" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="C311" t="s">
         <v>271</v>
@@ -29848,21 +29851,21 @@
         <v>260</v>
       </c>
       <c r="AO311" t="s">
+        <v>1646</v>
+      </c>
+      <c r="AP311" t="s">
         <v>1647</v>
       </c>
-      <c r="AP311" t="s">
+      <c r="AS311" t="s">
         <v>1648</v>
-      </c>
-      <c r="AS311" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="312" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B312" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="C312" t="s">
         <v>271</v>
@@ -29937,21 +29940,21 @@
         <v>260</v>
       </c>
       <c r="AO312" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AP312" t="s">
         <v>1651</v>
       </c>
-      <c r="AP312" t="s">
+      <c r="AS312" t="s">
         <v>1652</v>
-      </c>
-      <c r="AS312" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="313" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B313" t="s">
         <v>1654</v>
-      </c>
-      <c r="B313" t="s">
-        <v>1655</v>
       </c>
       <c r="C313" t="s">
         <v>271</v>
@@ -29987,7 +29990,7 @@
         <v>408</v>
       </c>
       <c r="AB313" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC313" t="s">
         <v>48</v>
@@ -30011,24 +30014,24 @@
         <v>54</v>
       </c>
       <c r="AN313" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AO313" t="s">
         <v>1657</v>
       </c>
-      <c r="AO313" t="s">
+      <c r="AP313" t="s">
         <v>1658</v>
       </c>
-      <c r="AP313" t="s">
+      <c r="AS313" t="s">
         <v>1659</v>
-      </c>
-      <c r="AS313" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="314" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B314" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="C314" t="s">
         <v>271</v>
@@ -30064,7 +30067,7 @@
         <v>216</v>
       </c>
       <c r="AB314" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC314" t="s">
         <v>48</v>
@@ -30085,27 +30088,27 @@
         <v>244</v>
       </c>
       <c r="AM314" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="AN314" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="AO314" t="s">
+        <v>1661</v>
+      </c>
+      <c r="AP314" t="s">
         <v>1662</v>
       </c>
-      <c r="AP314" t="s">
+      <c r="AS314" t="s">
         <v>1663</v>
-      </c>
-      <c r="AS314" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="315" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B315" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="C315" t="s">
         <v>205</v>
@@ -30156,7 +30159,7 @@
         <v>48</v>
       </c>
       <c r="AB315" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC315" t="s">
         <v>48</v>
@@ -30165,7 +30168,7 @@
         <v>812</v>
       </c>
       <c r="AE315" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="AF315">
         <v>129</v>
@@ -30180,24 +30183,24 @@
         <v>54</v>
       </c>
       <c r="AN315" t="s">
+        <v>1666</v>
+      </c>
+      <c r="AO315" t="s">
         <v>1667</v>
       </c>
-      <c r="AO315" t="s">
+      <c r="AP315" t="s">
         <v>1668</v>
       </c>
-      <c r="AP315" t="s">
+      <c r="AS315" t="s">
         <v>1669</v>
-      </c>
-      <c r="AS315" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="316" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B316" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="C316" t="s">
         <v>205</v>
@@ -30248,7 +30251,7 @@
         <v>48</v>
       </c>
       <c r="AB316" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC316" t="s">
         <v>48</v>
@@ -30257,7 +30260,7 @@
         <v>812</v>
       </c>
       <c r="AE316" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="AF316">
         <v>129</v>
@@ -30272,24 +30275,24 @@
         <v>54</v>
       </c>
       <c r="AN316" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="AO316" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="AP316" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AS316" t="s">
         <v>1669</v>
-      </c>
-      <c r="AS316" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="317" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B317" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="C317" t="s">
         <v>205</v>
@@ -30334,10 +30337,10 @@
         <v>24</v>
       </c>
       <c r="Y317" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="AB317" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AC317" t="s">
         <v>48</v>
@@ -30358,27 +30361,27 @@
         <v>985</v>
       </c>
       <c r="AM317" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="AN317" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AO317" t="s">
         <v>1675</v>
       </c>
-      <c r="AO317" t="s">
+      <c r="AP317" t="s">
         <v>1676</v>
       </c>
-      <c r="AP317" t="s">
+      <c r="AS317" t="s">
         <v>1677</v>
-      </c>
-      <c r="AS317" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="318" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B318" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="C318" t="s">
         <v>230</v>
@@ -30411,7 +30414,7 @@
         <v>408</v>
       </c>
       <c r="AB318" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC318" t="s">
         <v>48</v>
@@ -30429,24 +30432,24 @@
         <v>54</v>
       </c>
       <c r="AN318" t="s">
+        <v>1679</v>
+      </c>
+      <c r="AO318" t="s">
         <v>1680</v>
       </c>
-      <c r="AO318" t="s">
+      <c r="AP318" t="s">
         <v>1681</v>
       </c>
-      <c r="AP318" t="s">
+      <c r="AS318" t="s">
         <v>1682</v>
-      </c>
-      <c r="AS318" t="s">
-        <v>1683</v>
       </c>
     </row>
     <row r="319" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B319" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="C319" t="s">
         <v>230</v>
@@ -30470,10 +30473,10 @@
         <v>24</v>
       </c>
       <c r="Y319" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="AB319" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC319" t="s">
         <v>48</v>
@@ -30488,24 +30491,24 @@
         <v>54</v>
       </c>
       <c r="AN319" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="AO319" t="s">
+        <v>1685</v>
+      </c>
+      <c r="AP319" t="s">
         <v>1686</v>
       </c>
-      <c r="AP319" t="s">
+      <c r="AS319" t="s">
         <v>1687</v>
-      </c>
-      <c r="AS319" t="s">
-        <v>1688</v>
       </c>
     </row>
     <row r="320" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B320" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="C320" t="s">
         <v>205</v>
@@ -30562,7 +30565,7 @@
         <v>408</v>
       </c>
       <c r="AB320" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC320" t="s">
         <v>48</v>
@@ -30574,30 +30577,30 @@
         <v>129</v>
       </c>
       <c r="AI320" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="AM320" t="s">
         <v>54</v>
       </c>
       <c r="AN320" t="s">
+        <v>1690</v>
+      </c>
+      <c r="AO320" t="s">
         <v>1691</v>
       </c>
-      <c r="AO320" t="s">
+      <c r="AP320" t="s">
         <v>1692</v>
       </c>
-      <c r="AP320" t="s">
+      <c r="AS320" t="s">
         <v>1693</v>
-      </c>
-      <c r="AS320" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="321" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B321" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="C321" t="s">
         <v>205</v>
@@ -30657,7 +30660,7 @@
         <v>408</v>
       </c>
       <c r="AB321" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC321" t="s">
         <v>48</v>
@@ -30666,7 +30669,7 @@
         <v>812</v>
       </c>
       <c r="AE321" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="AF321">
         <v>130</v>
@@ -30675,30 +30678,30 @@
         <v>245</v>
       </c>
       <c r="AI321" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="AM321" t="s">
         <v>54</v>
       </c>
       <c r="AN321" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="AO321" t="s">
+        <v>1695</v>
+      </c>
+      <c r="AP321" t="s">
         <v>1696</v>
       </c>
-      <c r="AP321" t="s">
+      <c r="AS321" t="s">
         <v>1697</v>
-      </c>
-      <c r="AS321" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="322" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B322" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="C322" t="s">
         <v>230</v>
@@ -30755,7 +30758,7 @@
         <v>408</v>
       </c>
       <c r="AB322" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC322" t="s">
         <v>48</v>
@@ -30764,7 +30767,7 @@
         <v>812</v>
       </c>
       <c r="AE322" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="AF322">
         <v>130</v>
@@ -30773,30 +30776,30 @@
         <v>245</v>
       </c>
       <c r="AI322" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="AM322" t="s">
         <v>54</v>
       </c>
       <c r="AN322" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="AO322" t="s">
+        <v>1699</v>
+      </c>
+      <c r="AP322" t="s">
         <v>1700</v>
       </c>
-      <c r="AP322" t="s">
+      <c r="AS322" t="s">
         <v>1701</v>
-      </c>
-      <c r="AS322" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="323" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B323" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C323" t="s">
         <v>230</v>
@@ -30856,7 +30859,7 @@
         <v>408</v>
       </c>
       <c r="AB323" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="AC323" t="s">
         <v>48</v>
@@ -30865,7 +30868,7 @@
         <v>812</v>
       </c>
       <c r="AE323" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="AF323">
         <v>130</v>
@@ -30874,30 +30877,30 @@
         <v>245</v>
       </c>
       <c r="AI323" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="AM323" t="s">
         <v>54</v>
       </c>
       <c r="AN323" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AO323" t="s">
         <v>1704</v>
       </c>
-      <c r="AO323" t="s">
+      <c r="AP323" t="s">
         <v>1705</v>
       </c>
-      <c r="AP323" t="s">
+      <c r="AS323" t="s">
         <v>1706</v>
-      </c>
-      <c r="AS323" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="324" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B324" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C324" t="s">
         <v>297</v>
@@ -30945,10 +30948,10 @@
         <v>124</v>
       </c>
       <c r="AH324" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AI324" t="s">
         <v>1709</v>
-      </c>
-      <c r="AI324" t="s">
-        <v>1710</v>
       </c>
       <c r="AK324" t="s">
         <v>821</v>
@@ -30957,30 +30960,30 @@
         <v>54</v>
       </c>
       <c r="AN324" t="s">
+        <v>1710</v>
+      </c>
+      <c r="AO324" t="s">
         <v>1711</v>
       </c>
-      <c r="AO324" t="s">
+      <c r="AP324" t="s">
         <v>1712</v>
       </c>
-      <c r="AP324" t="s">
+      <c r="AS324" t="s">
         <v>1713</v>
-      </c>
-      <c r="AS324" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="325" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B325" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C325" t="s">
         <v>271</v>
       </c>
       <c r="D325">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="E325">
         <v>1</v>
@@ -31028,10 +31031,10 @@
         <v>52</v>
       </c>
       <c r="AH325" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AI325" t="s">
         <v>1709</v>
-      </c>
-      <c r="AI325" t="s">
-        <v>1710</v>
       </c>
       <c r="AK325" t="s">
         <v>821</v>
@@ -31040,30 +31043,30 @@
         <v>282</v>
       </c>
       <c r="AN325" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="AO325" t="s">
+        <v>1715</v>
+      </c>
+      <c r="AP325" t="s">
         <v>1716</v>
       </c>
-      <c r="AP325" t="s">
-        <v>1717</v>
-      </c>
       <c r="AS325" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="326" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B326" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="C326" t="s">
         <v>297</v>
       </c>
       <c r="D326">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="E326">
         <v>2</v>
@@ -31095,9 +31098,6 @@
       <c r="AA326" t="s">
         <v>48</v>
       </c>
-      <c r="AB326" t="s">
-        <v>73</v>
-      </c>
       <c r="AC326" t="s">
         <v>48</v>
       </c>
@@ -31111,10 +31111,10 @@
         <v>110</v>
       </c>
       <c r="AH326" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="AI326" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AK326" t="s">
         <v>821</v>
@@ -31123,7 +31123,7 @@
         <v>282</v>
       </c>
       <c r="AN326" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="AO326" t="s">
         <v>1720</v>
@@ -31132,12 +31132,12 @@
         <v>1721</v>
       </c>
       <c r="AS326" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="327" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B327" t="s">
         <v>1722</v>
@@ -31191,10 +31191,10 @@
         <v>52</v>
       </c>
       <c r="AH327" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AI327" t="s">
         <v>1709</v>
-      </c>
-      <c r="AI327" t="s">
-        <v>1710</v>
       </c>
       <c r="AK327" t="s">
         <v>821</v>
@@ -31203,24 +31203,24 @@
         <v>282</v>
       </c>
       <c r="AN327" t="s">
-        <v>1711</v>
+        <v>1723</v>
       </c>
       <c r="AO327" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="AP327" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="AS327" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="328" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B328" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="C328" t="s">
         <v>271</v>
@@ -31277,10 +31277,10 @@
         <v>52</v>
       </c>
       <c r="AH328" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AI328" t="s">
         <v>1709</v>
-      </c>
-      <c r="AI328" t="s">
-        <v>1710</v>
       </c>
       <c r="AK328" t="s">
         <v>821</v>
@@ -31289,7 +31289,7 @@
         <v>282</v>
       </c>
       <c r="AN328" t="s">
-        <v>1727</v>
+        <v>1719</v>
       </c>
       <c r="AO328" t="s">
         <v>1728</v>
@@ -31303,7 +31303,7 @@
     </row>
     <row r="329" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B329" t="s">
         <v>1731</v>
@@ -31369,10 +31369,10 @@
         <v>52</v>
       </c>
       <c r="AH329" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AI329" t="s">
         <v>1709</v>
-      </c>
-      <c r="AI329" t="s">
-        <v>1710</v>
       </c>
       <c r="AK329" t="s">
         <v>821</v>
@@ -31381,7 +31381,7 @@
         <v>54</v>
       </c>
       <c r="AN329" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="AO329" t="s">
         <v>387</v>
@@ -31395,7 +31395,7 @@
     </row>
     <row r="330" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B330" t="s">
         <v>1733</v>
@@ -31452,10 +31452,10 @@
         <v>110</v>
       </c>
       <c r="AH330" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AI330" t="s">
         <v>1709</v>
-      </c>
-      <c r="AI330" t="s">
-        <v>1710</v>
       </c>
       <c r="AK330" t="s">
         <v>821</v>
@@ -31475,7 +31475,7 @@
     </row>
     <row r="331" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B331" t="s">
         <v>1736</v>
@@ -32947,7 +32947,7 @@
         <v>125</v>
       </c>
       <c r="AH350" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="AI350" t="s">
         <v>1812</v>
@@ -33107,7 +33107,7 @@
         <v>125</v>
       </c>
       <c r="AH352" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="AI352" t="s">
         <v>1812</v>
@@ -33273,7 +33273,7 @@
         <v>125</v>
       </c>
       <c r="AH354" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="AI354" t="s">
         <v>1812</v>
@@ -33297,7 +33297,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="355" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1743</v>
       </c>
@@ -33320,7 +33320,7 @@
         <v>1</v>
       </c>
       <c r="N355">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O355">
         <v>1</v>
@@ -33362,7 +33362,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="356" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1743</v>
       </c>
@@ -33944,7 +33944,7 @@
         <v>48</v>
       </c>
       <c r="W364">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="X364">
         <v>24</v>
@@ -34113,7 +34113,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="367" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1843</v>
       </c>
@@ -34151,7 +34151,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="368" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1843</v>
       </c>
@@ -34369,7 +34369,7 @@
         <v>291</v>
       </c>
       <c r="AN371" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="AO371" t="s">
         <v>1905</v>
@@ -34452,7 +34452,7 @@
         <v>291</v>
       </c>
       <c r="AN372" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="AO372" t="s">
         <v>1909</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="1918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="1917">
   <si>
     <t>Brand</t>
   </si>
@@ -4145,7 +4145,7 @@
     <t>TotalMix FX, DigiCheck NG, TotalMix Remote</t>
   </si>
   <si>
-    <t>14 input / 16 output total channels (analog+digital). 2 XLR combo mic/line inputs (75dB gain, individually switchable 48V phantom + PAD). 2 balanced XLR line outputs + 1 TRS phones output. ADAT is asymmetric: 2x TOSLINK input ports (16ch@48kHz) but only 1x TOSLINK output port (8ch@48kHz). SteadyClock FS, built-in sample rate converter, full standalone operation, bus-powered or external 12V supply.</t>
+    <t>14 input / 16 output total channels (analog+digital). 2 XLR combo mic/line inputs (75dB gain, individually switchable 48V phantom + PAD). 2 balanced XLR line outputs + 1 TRS phones output. 1x TOSLINK optical input and 1x TOSLINK optical output (ADAT 8ch@48kHz, or optical S/PDIF). SteadyClock FS, built-in sample rate converter, full standalone operation, bus-powered or external 12V supply.</t>
   </si>
   <si>
     <t>https://rme-audio.de/digiface-aes.html</t>
@@ -5150,7 +5150,7 @@
     <t>-102.5dB (0.00075%)</t>
   </si>
   <si>
-    <t>LUNA</t>
+    <t>LUNA, UA plugin bundle (13 titles), Melodyne Essential, Ampeg SVT-VR Classic Bass Bundle, UJAM Virtual Drummer DEEP, UJAM Virtual Bassist DANDY, Splice INSTRUMENT</t>
   </si>
   <si>
     <t>610 preamp</t>
@@ -5175,9 +5175,6 @@
   </si>
   <si>
     <t>-103.1dB (0.00070%)</t>
-  </si>
-  <si>
-    <t>LUNA, UA plugin bundle (13 titles), Melodyne Essential, Ampeg SVT-VR Classic Bass Bundle, UJAM Virtual Drummer DEEP, UJAM Virtual Bassist DANDY, Splice INSTRUMENT</t>
   </si>
   <si>
     <t>610 preamp mode (1176 as bundled plugin)</t>
@@ -10610,7 +10607,7 @@
         <v>257</v>
       </c>
       <c r="D58">
-        <v>1199</v>
+        <v>999</v>
       </c>
       <c r="E58">
         <v>4</v>
@@ -25793,7 +25790,7 @@
         <v>8</v>
       </c>
       <c r="J256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K256">
         <v>1</v>
@@ -31123,13 +31120,13 @@
         <v>282</v>
       </c>
       <c r="AN326" t="s">
+        <v>1710</v>
+      </c>
+      <c r="AO326" t="s">
         <v>1719</v>
       </c>
-      <c r="AO326" t="s">
+      <c r="AP326" t="s">
         <v>1720</v>
-      </c>
-      <c r="AP326" t="s">
-        <v>1721</v>
       </c>
       <c r="AS326" t="s">
         <v>1713</v>
@@ -31140,7 +31137,7 @@
         <v>1653</v>
       </c>
       <c r="B327" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="C327" t="s">
         <v>271</v>
@@ -31203,16 +31200,16 @@
         <v>282</v>
       </c>
       <c r="AN327" t="s">
+        <v>1722</v>
+      </c>
+      <c r="AO327" t="s">
         <v>1723</v>
       </c>
-      <c r="AO327" t="s">
+      <c r="AP327" t="s">
         <v>1724</v>
       </c>
-      <c r="AP327" t="s">
+      <c r="AS327" t="s">
         <v>1725</v>
-      </c>
-      <c r="AS327" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="328" spans="1:45" x14ac:dyDescent="0.25">
@@ -31220,7 +31217,7 @@
         <v>1653</v>
       </c>
       <c r="B328" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="C328" t="s">
         <v>271</v>
@@ -31289,16 +31286,16 @@
         <v>282</v>
       </c>
       <c r="AN328" t="s">
-        <v>1719</v>
+        <v>1710</v>
       </c>
       <c r="AO328" t="s">
+        <v>1727</v>
+      </c>
+      <c r="AP328" t="s">
         <v>1728</v>
       </c>
-      <c r="AP328" t="s">
+      <c r="AS328" t="s">
         <v>1729</v>
-      </c>
-      <c r="AS328" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="329" spans="1:45" x14ac:dyDescent="0.25">
@@ -31306,7 +31303,7 @@
         <v>1653</v>
       </c>
       <c r="B329" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="C329" t="s">
         <v>271</v>
@@ -31381,16 +31378,16 @@
         <v>54</v>
       </c>
       <c r="AN329" t="s">
-        <v>1719</v>
+        <v>1710</v>
       </c>
       <c r="AO329" t="s">
         <v>387</v>
       </c>
       <c r="AP329" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="AS329" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="330" spans="1:45" x14ac:dyDescent="0.25">
@@ -31398,7 +31395,7 @@
         <v>1653</v>
       </c>
       <c r="B330" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="C330" t="s">
         <v>271</v>
@@ -31464,13 +31461,13 @@
         <v>282</v>
       </c>
       <c r="AO330" t="s">
+        <v>1733</v>
+      </c>
+      <c r="AP330" t="s">
         <v>1734</v>
       </c>
-      <c r="AP330" t="s">
-        <v>1735</v>
-      </c>
       <c r="AS330" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="331" spans="1:45" x14ac:dyDescent="0.25">
@@ -31478,7 +31475,7 @@
         <v>1653</v>
       </c>
       <c r="B331" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="C331" t="s">
         <v>257</v>
@@ -31523,7 +31520,7 @@
         <v>237</v>
       </c>
       <c r="V331" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="W331">
         <v>192</v>
@@ -31559,30 +31556,30 @@
         <v>487</v>
       </c>
       <c r="AI331" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="AM331" t="s">
         <v>291</v>
       </c>
       <c r="AN331" t="s">
+        <v>1738</v>
+      </c>
+      <c r="AO331" t="s">
         <v>1739</v>
       </c>
-      <c r="AO331" t="s">
+      <c r="AP331" t="s">
         <v>1740</v>
       </c>
-      <c r="AP331" t="s">
+      <c r="AS331" t="s">
         <v>1741</v>
-      </c>
-      <c r="AS331" t="s">
-        <v>1742</v>
       </c>
     </row>
     <row r="332" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B332" t="s">
         <v>1743</v>
-      </c>
-      <c r="B332" t="s">
-        <v>1744</v>
       </c>
       <c r="C332" t="s">
         <v>381</v>
@@ -31633,24 +31630,24 @@
         <v>282</v>
       </c>
       <c r="AN332" t="s">
+        <v>1744</v>
+      </c>
+      <c r="AO332" t="s">
         <v>1745</v>
       </c>
-      <c r="AO332" t="s">
+      <c r="AP332" t="s">
         <v>1746</v>
       </c>
-      <c r="AP332" t="s">
+      <c r="AS332" t="s">
         <v>1747</v>
-      </c>
-      <c r="AS332" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="333" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B333" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="C333" t="s">
         <v>381</v>
@@ -31701,27 +31698,27 @@
         <v>282</v>
       </c>
       <c r="AN333" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="AO333" t="s">
+        <v>1749</v>
+      </c>
+      <c r="AP333" t="s">
         <v>1750</v>
       </c>
-      <c r="AP333" t="s">
-        <v>1751</v>
-      </c>
       <c r="AQ333">
         <v>2</v>
       </c>
       <c r="AS333" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="334" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B334" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="C334" t="s">
         <v>381</v>
@@ -31772,27 +31769,27 @@
         <v>282</v>
       </c>
       <c r="AN334" t="s">
+        <v>1752</v>
+      </c>
+      <c r="AO334" t="s">
         <v>1753</v>
       </c>
-      <c r="AO334" t="s">
+      <c r="AP334" t="s">
         <v>1754</v>
       </c>
-      <c r="AP334" t="s">
+      <c r="AQ334">
+        <v>2</v>
+      </c>
+      <c r="AS334" t="s">
         <v>1755</v>
-      </c>
-      <c r="AQ334">
-        <v>2</v>
-      </c>
-      <c r="AS334" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="335" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B335" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="C335" t="s">
         <v>47</v>
@@ -31852,24 +31849,24 @@
         <v>54</v>
       </c>
       <c r="AN335" t="s">
+        <v>1757</v>
+      </c>
+      <c r="AO335" t="s">
         <v>1758</v>
       </c>
-      <c r="AO335" t="s">
+      <c r="AP335" t="s">
         <v>1759</v>
       </c>
-      <c r="AP335" t="s">
+      <c r="AS335" t="s">
         <v>1760</v>
-      </c>
-      <c r="AS335" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="336" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B336" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="C336" t="s">
         <v>47</v>
@@ -31929,24 +31926,24 @@
         <v>54</v>
       </c>
       <c r="AN336" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AO336" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="AP336" t="s">
+        <v>1759</v>
+      </c>
+      <c r="AS336" t="s">
         <v>1760</v>
-      </c>
-      <c r="AS336" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="337" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B337" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="C337" t="s">
         <v>47</v>
@@ -31991,27 +31988,27 @@
         <v>54</v>
       </c>
       <c r="AN337" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="AO337" t="s">
+        <v>1764</v>
+      </c>
+      <c r="AP337" t="s">
         <v>1765</v>
-      </c>
-      <c r="AP337" t="s">
-        <v>1766</v>
       </c>
       <c r="AQ337">
         <v>4</v>
       </c>
       <c r="AS337" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="338" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B338" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="C338" t="s">
         <v>47</v>
@@ -32053,27 +32050,27 @@
         <v>54</v>
       </c>
       <c r="AN338" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="AO338" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="AP338" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AQ338">
         <v>4</v>
       </c>
       <c r="AS338" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="339" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B339" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C339" t="s">
         <v>47</v>
@@ -32127,24 +32124,24 @@
         <v>54</v>
       </c>
       <c r="AO339" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="AP339" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AQ339">
         <v>4</v>
       </c>
       <c r="AS339" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="340" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B340" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="C340" t="s">
         <v>47</v>
@@ -32195,24 +32192,24 @@
         <v>54</v>
       </c>
       <c r="AO340" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="AP340" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AQ340">
         <v>4</v>
       </c>
       <c r="AS340" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="341" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B341" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C341" t="s">
         <v>47</v>
@@ -32263,27 +32260,27 @@
         <v>54</v>
       </c>
       <c r="AN341" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="AO341" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="AP341" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AQ341">
         <v>4</v>
       </c>
       <c r="AS341" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="342" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B342" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="C342" t="s">
         <v>47</v>
@@ -32337,24 +32334,24 @@
         <v>54</v>
       </c>
       <c r="AO342" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="AP342" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AQ342">
         <v>4</v>
       </c>
       <c r="AS342" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="343" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B343" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C343" t="s">
         <v>47</v>
@@ -32402,7 +32399,7 @@
         <v>48</v>
       </c>
       <c r="AD343" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AG343" t="s">
         <v>1190</v>
@@ -32417,27 +32414,27 @@
         <v>54</v>
       </c>
       <c r="AN343" t="s">
+        <v>1781</v>
+      </c>
+      <c r="AO343" t="s">
         <v>1782</v>
       </c>
-      <c r="AO343" t="s">
+      <c r="AP343" t="s">
         <v>1783</v>
-      </c>
-      <c r="AP343" t="s">
-        <v>1784</v>
       </c>
       <c r="AQ343">
         <v>4</v>
       </c>
       <c r="AS343" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="344" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B344" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="C344" t="s">
         <v>47</v>
@@ -32485,7 +32482,7 @@
         <v>48</v>
       </c>
       <c r="AD344" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AF344" t="s">
         <v>1190</v>
@@ -32500,24 +32497,24 @@
         <v>54</v>
       </c>
       <c r="AO344" t="s">
+        <v>1786</v>
+      </c>
+      <c r="AP344" t="s">
         <v>1787</v>
-      </c>
-      <c r="AP344" t="s">
-        <v>1788</v>
       </c>
       <c r="AQ344">
         <v>4</v>
       </c>
       <c r="AS344" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="345" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B345" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="C345" t="s">
         <v>47</v>
@@ -32565,7 +32562,7 @@
         <v>48</v>
       </c>
       <c r="AD345" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AG345" t="s">
         <v>1190</v>
@@ -32580,24 +32577,24 @@
         <v>54</v>
       </c>
       <c r="AO345" t="s">
+        <v>1789</v>
+      </c>
+      <c r="AP345" t="s">
         <v>1790</v>
-      </c>
-      <c r="AP345" t="s">
-        <v>1791</v>
       </c>
       <c r="AQ345">
         <v>4</v>
       </c>
       <c r="AS345" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="346" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B346" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C346" t="s">
         <v>47</v>
@@ -32645,7 +32642,7 @@
         <v>48</v>
       </c>
       <c r="AD346" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="AF346" t="s">
         <v>1190</v>
@@ -32660,27 +32657,27 @@
         <v>54</v>
       </c>
       <c r="AN346" t="s">
+        <v>1792</v>
+      </c>
+      <c r="AO346" t="s">
         <v>1793</v>
       </c>
-      <c r="AO346" t="s">
+      <c r="AP346" t="s">
         <v>1794</v>
-      </c>
-      <c r="AP346" t="s">
-        <v>1795</v>
       </c>
       <c r="AQ346">
         <v>4</v>
       </c>
       <c r="AS346" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="347" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B347" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="C347" t="s">
         <v>205</v>
@@ -32710,7 +32707,7 @@
         <v>24</v>
       </c>
       <c r="Y347" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="AF347" t="s">
         <v>362</v>
@@ -32722,24 +32719,24 @@
         <v>54</v>
       </c>
       <c r="AN347" t="s">
+        <v>1797</v>
+      </c>
+      <c r="AO347" t="s">
         <v>1798</v>
       </c>
-      <c r="AO347" t="s">
+      <c r="AP347" t="s">
         <v>1799</v>
       </c>
-      <c r="AP347" t="s">
+      <c r="AS347" t="s">
         <v>1800</v>
-      </c>
-      <c r="AS347" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="348" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B348" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="C348" t="s">
         <v>297</v>
@@ -32802,24 +32799,24 @@
         <v>54</v>
       </c>
       <c r="AN348" t="s">
+        <v>1802</v>
+      </c>
+      <c r="AO348" t="s">
         <v>1803</v>
       </c>
-      <c r="AO348" t="s">
+      <c r="AP348" t="s">
         <v>1804</v>
       </c>
-      <c r="AP348" t="s">
+      <c r="AS348" t="s">
         <v>1805</v>
-      </c>
-      <c r="AS348" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="349" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B349" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="C349" t="s">
         <v>297</v>
@@ -32879,24 +32876,24 @@
         <v>54</v>
       </c>
       <c r="AN349" t="s">
+        <v>1802</v>
+      </c>
+      <c r="AO349" t="s">
         <v>1803</v>
       </c>
-      <c r="AO349" t="s">
-        <v>1804</v>
-      </c>
       <c r="AP349" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AS349" t="s">
         <v>1808</v>
-      </c>
-      <c r="AS349" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="350" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B350" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="C350" t="s">
         <v>271</v>
@@ -32932,7 +32929,7 @@
         <v>32</v>
       </c>
       <c r="Y350" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="AB350" t="s">
         <v>73</v>
@@ -32950,7 +32947,7 @@
         <v>1365</v>
       </c>
       <c r="AI350" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="AK350" t="s">
         <v>266</v>
@@ -32959,24 +32956,24 @@
         <v>54</v>
       </c>
       <c r="AN350" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AO350" t="s">
         <v>1813</v>
       </c>
-      <c r="AO350" t="s">
+      <c r="AP350" t="s">
         <v>1814</v>
       </c>
-      <c r="AP350" t="s">
+      <c r="AS350" t="s">
         <v>1815</v>
-      </c>
-      <c r="AS350" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="351" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B351" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="C351" t="s">
         <v>271</v>
@@ -33009,7 +33006,7 @@
         <v>32</v>
       </c>
       <c r="Y351" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="Z351" t="s">
         <v>272</v>
@@ -33039,24 +33036,24 @@
         <v>54</v>
       </c>
       <c r="AN351" t="s">
+        <v>1818</v>
+      </c>
+      <c r="AO351" t="s">
         <v>1819</v>
       </c>
-      <c r="AO351" t="s">
+      <c r="AP351" t="s">
         <v>1820</v>
       </c>
-      <c r="AP351" t="s">
+      <c r="AS351" t="s">
         <v>1821</v>
-      </c>
-      <c r="AS351" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="352" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B352" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="C352" t="s">
         <v>271</v>
@@ -33092,7 +33089,7 @@
         <v>32</v>
       </c>
       <c r="Y352" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="AB352" t="s">
         <v>73</v>
@@ -33110,7 +33107,7 @@
         <v>1365</v>
       </c>
       <c r="AI352" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="AK352" t="s">
         <v>266</v>
@@ -33119,24 +33116,24 @@
         <v>54</v>
       </c>
       <c r="AN352" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="AO352" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AP352" t="s">
         <v>1824</v>
       </c>
-      <c r="AP352" t="s">
+      <c r="AS352" t="s">
         <v>1825</v>
-      </c>
-      <c r="AS352" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="353" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B353" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="C353" t="s">
         <v>271</v>
@@ -33172,7 +33169,7 @@
         <v>32</v>
       </c>
       <c r="Y353" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="Z353" t="s">
         <v>272</v>
@@ -33184,7 +33181,7 @@
         <v>73</v>
       </c>
       <c r="AC353" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="AD353">
         <v>54</v>
@@ -33205,24 +33202,24 @@
         <v>54</v>
       </c>
       <c r="AN353" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="AO353" t="s">
+        <v>1828</v>
+      </c>
+      <c r="AP353" t="s">
         <v>1829</v>
       </c>
-      <c r="AP353" t="s">
+      <c r="AS353" t="s">
         <v>1830</v>
-      </c>
-      <c r="AS353" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="354" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B354" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="C354" t="s">
         <v>257</v>
@@ -33258,7 +33255,7 @@
         <v>32</v>
       </c>
       <c r="Y354" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="AB354" t="s">
         <v>73</v>
@@ -33276,7 +33273,7 @@
         <v>1365</v>
       </c>
       <c r="AI354" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="AK354" t="s">
         <v>266</v>
@@ -33285,24 +33282,24 @@
         <v>54</v>
       </c>
       <c r="AN354" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="AO354" t="s">
+        <v>1832</v>
+      </c>
+      <c r="AP354" t="s">
         <v>1833</v>
       </c>
-      <c r="AP354" t="s">
+      <c r="AS354" t="s">
         <v>1834</v>
-      </c>
-      <c r="AS354" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="355" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B355" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C355" t="s">
         <v>381</v>
@@ -33353,21 +33350,21 @@
         <v>54</v>
       </c>
       <c r="AN355" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AO355" t="s">
         <v>1837</v>
       </c>
-      <c r="AO355" t="s">
+      <c r="AP355" t="s">
         <v>1838</v>
-      </c>
-      <c r="AP355" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="356" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B356" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="C356" t="s">
         <v>381</v>
@@ -33412,18 +33409,18 @@
         <v>54</v>
       </c>
       <c r="AO356" t="s">
+        <v>1840</v>
+      </c>
+      <c r="AP356" t="s">
         <v>1841</v>
-      </c>
-      <c r="AP356" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="357" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B357" t="s">
         <v>1843</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1844</v>
       </c>
       <c r="C357" t="s">
         <v>297</v>
@@ -33468,10 +33465,10 @@
         <v>48</v>
       </c>
       <c r="AD357" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AK357" t="s">
         <v>1845</v>
-      </c>
-      <c r="AK357" t="s">
-        <v>1846</v>
       </c>
       <c r="AM357" t="s">
         <v>260</v>
@@ -33480,18 +33477,18 @@
         <v>742</v>
       </c>
       <c r="AP357" t="s">
+        <v>1846</v>
+      </c>
+      <c r="AS357" t="s">
         <v>1847</v>
-      </c>
-      <c r="AS357" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="358" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B358" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="C358" t="s">
         <v>297</v>
@@ -33533,7 +33530,7 @@
         <v>48</v>
       </c>
       <c r="AD358" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="AK358">
         <v>-120</v>
@@ -33542,21 +33539,21 @@
         <v>763</v>
       </c>
       <c r="AO358" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="AP358" t="s">
+        <v>1846</v>
+      </c>
+      <c r="AS358" t="s">
         <v>1847</v>
-      </c>
-      <c r="AS358" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="359" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B359" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="C359" t="s">
         <v>297</v>
@@ -33598,30 +33595,30 @@
         <v>48</v>
       </c>
       <c r="AD359" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="AK359" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="AM359" t="s">
         <v>260</v>
       </c>
       <c r="AO359" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="AP359" t="s">
+        <v>1846</v>
+      </c>
+      <c r="AS359" t="s">
         <v>1847</v>
-      </c>
-      <c r="AS359" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="360" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B360" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="C360" t="s">
         <v>47</v>
@@ -33669,7 +33666,7 @@
         <v>73</v>
       </c>
       <c r="AD360" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="AK360" t="s">
         <v>266</v>
@@ -33678,24 +33675,24 @@
         <v>54</v>
       </c>
       <c r="AO360" t="s">
+        <v>1855</v>
+      </c>
+      <c r="AP360" t="s">
         <v>1856</v>
-      </c>
-      <c r="AP360" t="s">
-        <v>1857</v>
       </c>
       <c r="AQ360">
         <v>4</v>
       </c>
       <c r="AS360" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="361" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B361" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C361" t="s">
         <v>47</v>
@@ -33752,24 +33749,24 @@
         <v>282</v>
       </c>
       <c r="AO361" t="s">
+        <v>1859</v>
+      </c>
+      <c r="AP361" t="s">
         <v>1860</v>
-      </c>
-      <c r="AP361" t="s">
-        <v>1861</v>
       </c>
       <c r="AQ361">
         <v>4</v>
       </c>
       <c r="AS361" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="362" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B362" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="C362" t="s">
         <v>47</v>
@@ -33817,33 +33814,33 @@
         <v>48</v>
       </c>
       <c r="AD362" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="AK362">
         <v>-128</v>
       </c>
       <c r="AM362" t="s">
+        <v>1863</v>
+      </c>
+      <c r="AO362" t="s">
         <v>1864</v>
       </c>
-      <c r="AO362" t="s">
+      <c r="AP362" t="s">
         <v>1865</v>
-      </c>
-      <c r="AP362" t="s">
-        <v>1866</v>
       </c>
       <c r="AQ362">
         <v>4</v>
       </c>
       <c r="AS362" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="363" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B363" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="C363" t="s">
         <v>47</v>
@@ -33894,27 +33891,27 @@
         <v>48</v>
       </c>
       <c r="AK363" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="AM363" t="s">
         <v>260</v>
       </c>
       <c r="AO363" t="s">
+        <v>1868</v>
+      </c>
+      <c r="AP363" t="s">
         <v>1869</v>
       </c>
-      <c r="AP363" t="s">
+      <c r="AS363" t="s">
         <v>1870</v>
-      </c>
-      <c r="AS363" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="364" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B364" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="C364" t="s">
         <v>47</v>
@@ -33959,30 +33956,30 @@
         <v>73</v>
       </c>
       <c r="AD364" t="s">
+        <v>1872</v>
+      </c>
+      <c r="AK364" t="s">
         <v>1873</v>
-      </c>
-      <c r="AK364" t="s">
-        <v>1874</v>
       </c>
       <c r="AM364" t="s">
         <v>291</v>
       </c>
       <c r="AO364" t="s">
+        <v>1874</v>
+      </c>
+      <c r="AP364" t="s">
         <v>1875</v>
       </c>
-      <c r="AP364" t="s">
+      <c r="AS364" t="s">
         <v>1876</v>
-      </c>
-      <c r="AS364" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="365" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B365" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="C365" t="s">
         <v>47</v>
@@ -34027,30 +34024,30 @@
         <v>48</v>
       </c>
       <c r="AD365" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="AK365">
         <v>-128</v>
       </c>
       <c r="AM365" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="AO365" t="s">
+        <v>1878</v>
+      </c>
+      <c r="AP365" t="s">
         <v>1879</v>
       </c>
-      <c r="AP365" t="s">
+      <c r="AS365" t="s">
         <v>1880</v>
-      </c>
-      <c r="AS365" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="366" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B366" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="C366" t="s">
         <v>47</v>
@@ -34104,21 +34101,21 @@
         <v>763</v>
       </c>
       <c r="AO366" t="s">
+        <v>1882</v>
+      </c>
+      <c r="AP366" t="s">
         <v>1883</v>
       </c>
-      <c r="AP366" t="s">
+      <c r="AS366" t="s">
         <v>1884</v>
-      </c>
-      <c r="AS366" t="s">
-        <v>1885</v>
       </c>
     </row>
     <row r="367" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B367" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C367" t="s">
         <v>381</v>
@@ -34142,21 +34139,21 @@
         <v>54</v>
       </c>
       <c r="AN367" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AO367" t="s">
         <v>1887</v>
       </c>
-      <c r="AO367" t="s">
+      <c r="AP367" t="s">
         <v>1888</v>
-      </c>
-      <c r="AP367" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="368" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B368" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="C368" t="s">
         <v>381</v>
@@ -34192,18 +34189,18 @@
         <v>260</v>
       </c>
       <c r="AO368" t="s">
+        <v>1890</v>
+      </c>
+      <c r="AP368" t="s">
         <v>1891</v>
-      </c>
-      <c r="AP368" t="s">
-        <v>1892</v>
       </c>
     </row>
     <row r="369" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B369" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C369" t="s">
         <v>381</v>
@@ -34236,7 +34233,7 @@
         <v>48</v>
       </c>
       <c r="AD369" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="AK369">
         <v>-125</v>
@@ -34245,21 +34242,21 @@
         <v>763</v>
       </c>
       <c r="AO369" t="s">
+        <v>1894</v>
+      </c>
+      <c r="AP369" t="s">
         <v>1895</v>
       </c>
-      <c r="AP369" t="s">
+      <c r="AS369" t="s">
         <v>1896</v>
-      </c>
-      <c r="AS369" t="s">
-        <v>1897</v>
       </c>
     </row>
     <row r="370" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B370" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="C370" t="s">
         <v>381</v>
@@ -34298,27 +34295,27 @@
         <v>70</v>
       </c>
       <c r="AK370" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="AM370" t="s">
         <v>54</v>
       </c>
       <c r="AO370" t="s">
+        <v>1899</v>
+      </c>
+      <c r="AP370" t="s">
         <v>1900</v>
       </c>
-      <c r="AP370" t="s">
+      <c r="AS370" t="s">
         <v>1901</v>
-      </c>
-      <c r="AS370" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="371" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B371" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="C371" t="s">
         <v>297</v>
@@ -34360,7 +34357,7 @@
         <v>48</v>
       </c>
       <c r="AD371" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="AK371">
         <v>-119.5</v>
@@ -34372,24 +34369,24 @@
         <v>1428</v>
       </c>
       <c r="AO371" t="s">
+        <v>1904</v>
+      </c>
+      <c r="AP371" t="s">
         <v>1905</v>
       </c>
-      <c r="AP371" t="s">
+      <c r="AR371">
+        <v>2</v>
+      </c>
+      <c r="AS371" t="s">
         <v>1906</v>
-      </c>
-      <c r="AR371">
-        <v>2</v>
-      </c>
-      <c r="AS371" t="s">
-        <v>1907</v>
       </c>
     </row>
     <row r="372" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B372" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="C372" t="s">
         <v>297</v>
@@ -34443,7 +34440,7 @@
         <v>48</v>
       </c>
       <c r="AD372" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="AK372">
         <v>-119.5</v>
@@ -34455,24 +34452,24 @@
         <v>1428</v>
       </c>
       <c r="AO372" t="s">
+        <v>1908</v>
+      </c>
+      <c r="AP372" t="s">
         <v>1909</v>
       </c>
-      <c r="AP372" t="s">
+      <c r="AR372">
+        <v>2</v>
+      </c>
+      <c r="AS372" t="s">
         <v>1910</v>
-      </c>
-      <c r="AR372">
-        <v>2</v>
-      </c>
-      <c r="AS372" t="s">
-        <v>1911</v>
       </c>
     </row>
     <row r="373" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B373" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C373" t="s">
         <v>297</v>
@@ -34523,13 +34520,13 @@
         <v>282</v>
       </c>
       <c r="AO373" t="s">
+        <v>1912</v>
+      </c>
+      <c r="AP373" t="s">
         <v>1913</v>
       </c>
-      <c r="AP373" t="s">
+      <c r="AS373" t="s">
         <v>1914</v>
-      </c>
-      <c r="AS373" t="s">
-        <v>1915</v>
       </c>
     </row>
   </sheetData>
@@ -34551,7 +34548,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -34604,7 +34601,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B8">
         <v>216</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -1097,28 +1097,28 @@
     <t>[ProSound](https://prosound.ixbt.com/interfaces/arturia-8pre.shtml)</t>
   </si>
   <si>
-    <t>AudioFuse Studio</t>
+    <t>AudioFuse Studio Rev2</t>
   </si>
   <si>
     <t>USB-C (fully USB 2.0 compatible)</t>
   </si>
   <si>
-    <t>71</t>
+    <t>78</t>
   </si>
   <si>
     <t>118</t>
   </si>
   <si>
-    <t>AudioFuse Creative Suite (incl. Analog Lab Intro)</t>
-  </si>
-  <si>
-    <t>Bluetooth</t>
+    <t>AudioFuse Creative Suite (11 titles incl. Analog Lab Intro, Comp DIODE-609)</t>
+  </si>
+  <si>
+    <t>Rev2: optimized DiscretePRO preamps (mic max input +18dBu, boost +17dB); Bluetooth streaming (AAC, aptX, aptX HD, aptX Low Latency); inputs 5-6 switchable to phono/RIAA preamp; integrated 3-port USB 2 hub</t>
   </si>
   <si>
     <t>https://www.arturia.com/products/audio/audiofuse-studio/overview</t>
   </si>
   <si>
-    <t>[ProSound](https://prosound.ixbt.com/interfaces/arturia-studio.shtml)</t>
+    <t>[Manufacturer](https://www.arturia.com/products/audio/audiofuse-studio/details)</t>
   </si>
   <si>
     <t>MiniFuse 1</t>
@@ -10607,7 +10607,7 @@
         <v>257</v>
       </c>
       <c r="D58">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="E58">
         <v>4</v>

--- a/data/audio_interfaces.xlsx
+++ b/data/audio_interfaces.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="1917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5267" uniqueCount="1917">
   <si>
     <t>Brand</t>
   </si>
@@ -10681,8 +10681,8 @@
       <c r="AE58" t="s">
         <v>362</v>
       </c>
-      <c r="AG58" t="s">
-        <v>265</v>
+      <c r="AF58">
+        <v>121</v>
       </c>
       <c r="AH58" t="s">
         <v>281</v>
